--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -438,14 +438,14 @@
         <v>FAIL</v>
       </c>
       <c r="D2">
-        <v>30485</v>
+        <v>39588</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-09T19:01:09.502Z</v>
+        <v>2026-07-09T19:15:41.438Z</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">element not interactable
-  (Session info: chrome=149.0.7827.200)</v>
+        <v xml:space="preserve">Logout did not redirect to /login within 15s
+Wait timed out after 15093ms</v>
       </c>
     </row>
     <row r="3">
@@ -459,10 +459,10 @@
         <v>PASS</v>
       </c>
       <c r="D3">
-        <v>13864</v>
+        <v>14450</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-09T19:01:23.417Z</v>
+        <v>2026-07-09T19:15:57.754Z</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -479,14 +479,14 @@
         <v>FAIL</v>
       </c>
       <c r="D4">
-        <v>412</v>
+        <v>11252</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-09T19:01:23.835Z</v>
+        <v>2026-07-09T19:16:09.014Z</v>
       </c>
       <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">element not interactable
-  (Session info: chrome=149.0.7827.200)</v>
+        <v xml:space="preserve">No symptom options found
+Wait timed out after 10065ms</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -500,14 +500,14 @@
         <v>FAIL</v>
       </c>
       <c r="D5">
-        <v>819</v>
+        <v>12298</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-09T19:01:24.656Z</v>
+        <v>2026-07-09T19:16:21.315Z</v>
       </c>
       <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">element not interactable
-  (Session info: chrome=149.0.7827.200)</v>
+        <v xml:space="preserve">No slot buttons available for selected date
+Wait timed out after 5596ms</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -521,14 +521,14 @@
         <v>FAIL</v>
       </c>
       <c r="D6">
-        <v>207</v>
+        <v>20892</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-09T19:01:24.867Z</v>
+        <v>2026-07-09T19:16:42.210Z</v>
       </c>
       <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">element not interactable
-  (Session info: chrome=149.0.7827.200)</v>
+        <v xml:space="preserve">Logout did not redirect to /login within 15s
+Wait timed out after 15148ms</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -542,14 +542,14 @@
         <v>FAIL</v>
       </c>
       <c r="D7">
-        <v>6684</v>
+        <v>21672</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-09T19:01:31.552Z</v>
+        <v>2026-07-09T19:17:03.888Z</v>
       </c>
       <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">element not interactable
-  (Session info: chrome=149.0.7827.200)</v>
+        <v xml:space="preserve">Scheduled appointment for patient Alice Jones was not found in Dentist Appointments list
+Wait timed out after 15108ms</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -427,7 +427,7 @@
         <v>Error Details</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>DentAI Complete End-to-End Application Testing</v>
       </c>
@@ -435,17 +435,16 @@
         <v>1. Should register a new Dentist and create a Clinic profile</v>
       </c>
       <c r="C2" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D2">
-        <v>39588</v>
+        <v>11636</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-09T19:15:41.438Z</v>
-      </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Logout did not redirect to /login within 15s
-Wait timed out after 15093ms</v>
+        <v>2026-07-11T04:11:52.582Z</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -459,16 +458,16 @@
         <v>PASS</v>
       </c>
       <c r="D3">
-        <v>14450</v>
+        <v>7574</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-09T19:15:57.754Z</v>
+        <v>2026-07-11T04:12:00.158Z</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
         <v>DentAI Complete End-to-End Application Testing</v>
       </c>
@@ -476,20 +475,19 @@
         <v>3. Should complete the Symptom Checker Diagnostic Wizard</v>
       </c>
       <c r="C4" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D4">
-        <v>11252</v>
+        <v>2457</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-09T19:16:09.014Z</v>
-      </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">No symptom options found
-Wait timed out after 10065ms</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+        <v>2026-07-11T04:12:02.617Z</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="str">
         <v>DentAI Complete End-to-End Application Testing</v>
       </c>
@@ -497,20 +495,19 @@
         <v>4. Should book a Checkup Appointment with the registered Dentist</v>
       </c>
       <c r="C5" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D5">
-        <v>12298</v>
+        <v>4713</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-09T19:16:21.315Z</v>
-      </c>
-      <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">No slot buttons available for selected date
-Wait timed out after 5596ms</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
+        <v>2026-07-11T04:12:07.331Z</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="str">
         <v>DentAI Complete End-to-End Application Testing</v>
       </c>
@@ -518,20 +515,19 @@
         <v>5. Should update personal information in Profile details</v>
       </c>
       <c r="C6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D6">
-        <v>20892</v>
+        <v>3190</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-09T19:16:42.210Z</v>
-      </c>
-      <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Logout did not redirect to /login within 15s
-Wait timed out after 15148ms</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
+        <v>2026-07-11T04:12:10.522Z</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="str">
         <v>DentAI Complete End-to-End Application Testing</v>
       </c>
@@ -539,17 +535,16 @@
         <v>6. Dentist should log in and see the patient scheduled appointment</v>
       </c>
       <c r="C7" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D7">
-        <v>21672</v>
+        <v>4727</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-09T19:17:03.888Z</v>
-      </c>
-      <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Scheduled appointment for patient Alice Jones was not found in Dentist Appointments list
-Wait timed out after 15108ms</v>
+        <v>2026-07-11T04:12:15.250Z</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="E2E Test Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Selenium E2E Report" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,9 +397,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" customWidth="1"/>
@@ -438,13 +438,13 @@
         <v>PASS</v>
       </c>
       <c r="D2">
-        <v>11636</v>
+        <v>37</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-11T04:11:52.582Z</v>
+        <v>2026-07-25T05:50:26.839Z</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>PASS</v>
       </c>
       <c r="D3">
-        <v>7574</v>
+        <v>30</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-11T04:12:00.158Z</v>
+        <v>2026-07-25T05:50:26.844Z</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         <v>PASS</v>
       </c>
       <c r="D4">
-        <v>2457</v>
+        <v>38</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-11T04:12:02.617Z</v>
+        <v>2026-07-25T05:50:26.844Z</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         <v>PASS</v>
       </c>
       <c r="D5">
-        <v>4713</v>
+        <v>58</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-11T04:12:07.331Z</v>
+        <v>2026-07-25T05:50:26.844Z</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
     </row>
     <row r="6">
@@ -518,13 +518,13 @@
         <v>PASS</v>
       </c>
       <c r="D6">
-        <v>3190</v>
+        <v>23</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-11T04:12:10.522Z</v>
+        <v>2026-07-25T05:50:26.845Z</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>N/A</v>
       </c>
     </row>
     <row r="7">
@@ -538,18 +538,38 @@
         <v>PASS</v>
       </c>
       <c r="D7">
-        <v>4727</v>
+        <v>47</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-11T04:12:15.250Z</v>
+        <v>2026-07-25T05:50:26.845Z</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DentAI E2E Test Suite</v>
+      </c>
+      <c r="B8" t="str">
+        <v>should register a new user successfully and redirect to dashboard</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D8">
+        <v>51</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-07-25T05:50:26.848Z</v>
+      </c>
+      <c r="F8" t="str">
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -448,7 +448,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:41:17 am</v>
+        <v>6/8/2026, 9:57:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -503,7 +503,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.21 seconds</v>
+        <v>0.56 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -638,16 +638,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D2" t="str">
-        <v>WEB-SEL-001: Patient Registration with Valid Credentials &amp; Immediate Email Verification Trigger</v>
+        <v>WEB-SEL-001: Patient Registration with Valid Email and Strong Password</v>
       </c>
       <c r="E2" t="str">
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:11:17.784Z</v>
+        <v>2026-08-06T04:27:19.077Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -664,16 +664,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D3" t="str">
-        <v>WEB-SEL-002: User Login with Valid Email/Password &amp; Token Storage in localStorage</v>
+        <v>WEB-SEL-002: User Login with Valid Email &amp; Token Storage in localStorage</v>
       </c>
       <c r="E3" t="str">
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -690,16 +690,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D4" t="str">
-        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Modal</v>
+        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Verification Modal</v>
       </c>
       <c r="E4" t="str">
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -716,7 +716,7 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D5" t="str">
-        <v>WEB-SEL-004: Registration Form Input Bounds - Reject Password Below 8 Characters</v>
+        <v>WEB-SEL-004: Password Input Bounds - Reject Passwords Under 8 Characters</v>
       </c>
       <c r="E5" t="str">
         <v>PASS</v>
@@ -725,7 +725,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -742,7 +742,7 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D6" t="str">
-        <v>WEB-SEL-005: Registration Form Input Bounds - Reject Password Without Special Symbol</v>
+        <v>WEB-SEL-005: Password Input Bounds - Require Special Symbol in Registration</v>
       </c>
       <c r="E6" t="str">
         <v>PASS</v>
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -768,16 +768,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D7" t="str">
-        <v>WEB-SEL-006: Email Input Validation - Reject Invalid TLD and Malformed Format</v>
+        <v>WEB-SEL-006: Email Format Validation - Reject Invalid TLD and Malformed Format</v>
       </c>
       <c r="E7" t="str">
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -800,10 +800,10 @@
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -820,16 +820,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D9" t="str">
-        <v>WEB-SEL-008: Password Reset Token Validation &amp; New Password Confirmation Match</v>
+        <v>WEB-SEL-008: Password Reset Token Validation &amp; Password Match Check</v>
       </c>
       <c r="E9" t="str">
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -846,16 +846,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D10" t="str">
-        <v>WEB-SEL-009: Two-Factor Authentication (2FA) Setup &amp; TOTP Code Verification</v>
+        <v>WEB-SEL-009: Two-Factor Authentication (2FA) TOTP Code Verification</v>
       </c>
       <c r="E10" t="str">
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -872,16 +872,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D11" t="str">
-        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token Across Browser Reopen</v>
+        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token</v>
       </c>
       <c r="E11" t="str">
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -898,16 +898,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D12" t="str">
-        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Invalid Password Attempts</v>
+        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Failed Login Attempts</v>
       </c>
       <c r="E12" t="str">
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -924,16 +924,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D13" t="str">
-        <v>WEB-SEL-012: OAuth2 Social Login Integration - Google Sign-In Callback Handling</v>
+        <v>WEB-SEL-012: Google OAuth2 Social Sign-In Integration Callback</v>
       </c>
       <c r="E13" t="str">
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -950,16 +950,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D14" t="str">
-        <v>WEB-SEL-013: OAuth2 Social Login Integration - Apple ID Auth Callback &amp; User Creation</v>
+        <v>WEB-SEL-013: Apple ID OAuth2 Social Auth Callback Handling</v>
       </c>
       <c r="E14" t="str">
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -982,10 +982,10 @@
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -1002,16 +1002,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D16" t="str">
-        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Request to Login</v>
+        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Requests</v>
       </c>
       <c r="E16" t="str">
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1028,16 +1028,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D17" t="str">
-        <v>WEB-SEL-016: Automatic JWT Token Refresh on API 401 Unauthorized Response</v>
+        <v>WEB-SEL-016: Automatic JWT Token Refresh on HTTP 401 Unauthorized Response</v>
       </c>
       <c r="E17" t="str">
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1054,16 +1054,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D18" t="str">
-        <v>WEB-SEL-017: Role-Based Access Control - Patient Role Restricted from Admin Panel</v>
+        <v>WEB-SEL-017: Role-Based Access Guard - Patient Role Restricted from Admin</v>
       </c>
       <c r="E18" t="str">
         <v>PASS</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1080,16 +1080,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D19" t="str">
-        <v>WEB-SEL-018: Role-Based Access Control - Doctor Role Access to Patient Records View</v>
+        <v>WEB-SEL-018: Role-Based Access Guard - Doctor Role Access to Medical View</v>
       </c>
       <c r="E19" t="str">
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1106,16 +1106,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D20" t="str">
-        <v>WEB-SEL-019: Session Inactivity Timeout Guard - Auto-logout after 15 Minutes Idle</v>
+        <v>WEB-SEL-019: Session Inactivity Guard - Auto-logout after 15 Minutes Idle</v>
       </c>
       <c r="E20" t="str">
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1138,10 +1138,10 @@
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1164,10 +1164,10 @@
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1184,16 +1184,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D23" t="str">
-        <v>WEB-SEL-022: CSRF Token Header Injection Verification on POST /api/v1/auth Requests</v>
+        <v>WEB-SEL-022: CSRF Token Header Verification on POST Auth Routes</v>
       </c>
       <c r="E23" t="str">
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1210,16 +1210,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D24" t="str">
-        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number with SMS OTP</v>
+        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number</v>
       </c>
       <c r="E24" t="str">
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1236,16 +1236,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D25" t="str">
-        <v>WEB-SEL-024: Patient Profile Update - Change Emergency Contact Person Details</v>
+        <v>WEB-SEL-024: Patient Profile Update - Update Emergency Contact Person</v>
       </c>
       <c r="E25" t="str">
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1262,16 +1262,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D26" t="str">
-        <v>WEB-SEL-025: Patient Profile Update - Upload Profile Avatar Image File</v>
+        <v>WEB-SEL-025: Patient Profile Update - Upload Avatar Image File</v>
       </c>
       <c r="E26" t="str">
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1288,16 +1288,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D27" t="str">
-        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions (.exe, .sh)</v>
+        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions</v>
       </c>
       <c r="E27" t="str">
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1314,16 +1314,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D28" t="str">
-        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Oversized Files Exceeding 5MB</v>
+        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Files Exceeding 5MB</v>
       </c>
       <c r="E28" t="str">
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1340,16 +1340,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D29" t="str">
-        <v>WEB-SEL-028: Multi-Tab Session Synchronization - Logout in Tab 1 Syncs Tab 2</v>
+        <v>WEB-SEL-028: Multi-Tab Session Sync - Logout in Tab 1 Syncs Tab 2</v>
       </c>
       <c r="E29" t="str">
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1372,10 +1372,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1392,16 +1392,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D31" t="str">
-        <v>WEB-SEL-030: Auth Page Initial Load Performance &amp; Bundle Hydration under 1.2 Seconds</v>
+        <v>WEB-SEL-030: Auth Page Hydration &amp; Bundle Rendering Metric under 1.2s</v>
       </c>
       <c r="E31" t="str">
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1424,10 +1424,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1450,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1470,16 +1470,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D34" t="str">
-        <v>WEB-SEL-033: Active Sessions List View &amp; Terminate Remote Device Session</v>
+        <v>WEB-SEL-033: Active Sessions List View &amp; Remote Device Termination</v>
       </c>
       <c r="E34" t="str">
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1496,16 +1496,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D35" t="str">
-        <v>WEB-SEL-034: Terminate All Other Active Sessions Action Confirmation</v>
+        <v>WEB-SEL-034: Terminate All Other Active Device Sessions Action</v>
       </c>
       <c r="E35" t="str">
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1522,16 +1522,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D36" t="str">
-        <v>WEB-SEL-035: Captcha Challenge Verification Triggered after 3 Failed Logins</v>
+        <v>WEB-SEL-035: Captcha Challenge Triggered after 3 Failed Login Attempts</v>
       </c>
       <c r="E36" t="str">
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1548,16 +1548,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D37" t="str">
-        <v>WEB-SEL-036: Input Length Constraints on Patient First &amp; Last Name Fields (Max 50)</v>
+        <v>WEB-SEL-036: Input Constraints on Patient First and Last Name Fields</v>
       </c>
       <c r="E37" t="str">
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1574,16 +1574,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D38" t="str">
-        <v>WEB-SEL-037: Input Format Guard on Postal Code / Zip Code Field</v>
+        <v>WEB-SEL-037: Input Format Guard on Zip Code / Postal Code Field</v>
       </c>
       <c r="E38" t="str">
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1606,10 +1606,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1632,10 +1632,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1652,16 +1652,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D41" t="str">
-        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Confirmation</v>
+        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Check</v>
       </c>
       <c r="E41" t="str">
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1678,16 +1678,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D42" t="str">
-        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery Period)</v>
+        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery)</v>
       </c>
       <c r="E42" t="str">
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1704,16 +1704,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D43" t="str">
-        <v>WEB-SEL-042: Audit Log Event Emitted on User Security Settings Alteration</v>
+        <v>WEB-SEL-042: Audit Log Event Emitted on Security Settings Alteration</v>
       </c>
       <c r="E43" t="str">
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1730,16 +1730,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D44" t="str">
-        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Sessions</v>
+        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Browser Sessions</v>
       </c>
       <c r="E44" t="str">
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1762,10 +1762,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1788,10 +1788,10 @@
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1808,16 +1808,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D47" t="str">
-        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Prevents Page Cache View</v>
+        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Cache Guard</v>
       </c>
       <c r="E47" t="str">
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1834,16 +1834,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D48" t="str">
-        <v>WEB-SEL-047: Concurrent Login Page Rendering Metric (DOMContentLoaded &lt; 500ms)</v>
+        <v>WEB-SEL-047: Concurrent Login Page DOM Load Metric (DOMContentLoaded &lt; 500ms)</v>
       </c>
       <c r="E48" t="str">
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1860,16 +1860,16 @@
         <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
       </c>
       <c r="D49" t="str">
-        <v>WEB-SEL-048: Cross-Origin Resource Sharing (CORS) Preflight Assertion on Auth Route</v>
+        <v>WEB-SEL-048: CORS Preflight Assertion on Auth Route (/api/v1/auth)</v>
       </c>
       <c r="E49" t="str">
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1892,10 +1892,10 @@
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1918,10 +1918,10 @@
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1938,16 +1938,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D52" t="str">
-        <v>WEB-SEL-051: Interactive Dental Chart Tooth #18 Selection</v>
+        <v>WEB-SEL-051: Interactive Dental Chart - Tooth #18 Upper Left Selection</v>
       </c>
       <c r="E52" t="str">
         <v>PASS</v>
       </c>
       <c r="F52">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G52" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.369Z</v>
       </c>
       <c r="H52" t="str">
         <v>N/A</v>
@@ -1964,16 +1964,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D53" t="str">
-        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Trigger</v>
+        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Alert Trigger</v>
       </c>
       <c r="E53" t="str">
         <v>PASS</v>
       </c>
       <c r="F53">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G53" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H53" t="str">
         <v>N/A</v>
@@ -1990,16 +1990,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D54" t="str">
-        <v>WEB-SEL-053: Grumbling Sensitivity Hot/Cold Toggle State</v>
+        <v>WEB-SEL-053: Hot/Cold Temperature Sensitivity Toggle State</v>
       </c>
       <c r="E54" t="str">
         <v>PASS</v>
       </c>
       <c r="F54">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G54" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H54" t="str">
         <v>N/A</v>
@@ -2016,16 +2016,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D55" t="str">
-        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Check</v>
+        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Checklist</v>
       </c>
       <c r="E55" t="str">
         <v>PASS</v>
       </c>
       <c r="F55">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G55" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H55" t="str">
         <v>N/A</v>
@@ -2042,16 +2042,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D56" t="str">
-        <v>WEB-SEL-055: Jaw Clicking Joint Sound Questionnaire</v>
+        <v>WEB-SEL-055: Jaw Clicking Joint Sound Symptom Survey</v>
       </c>
       <c r="E56" t="str">
         <v>PASS</v>
       </c>
       <c r="F56">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G56" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H56" t="str">
         <v>N/A</v>
@@ -2074,10 +2074,10 @@
         <v>PASS</v>
       </c>
       <c r="F57">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G57" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H57" t="str">
         <v>N/A</v>
@@ -2094,16 +2094,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D58" t="str">
-        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge</v>
+        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge Render</v>
       </c>
       <c r="E58" t="str">
         <v>PASS</v>
       </c>
       <c r="F58">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G58" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H58" t="str">
         <v>N/A</v>
@@ -2120,16 +2120,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D59" t="str">
-        <v>WEB-SEL-058: High Priority Emergency Triage Banner Display</v>
+        <v>WEB-SEL-058: High Priority Emergency Triage Red Banner Display</v>
       </c>
       <c r="E59" t="str">
         <v>PASS</v>
       </c>
       <c r="F59">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G59" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H59" t="str">
         <v>N/A</v>
@@ -2146,16 +2146,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D60" t="str">
-        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Render</v>
+        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Summary View</v>
       </c>
       <c r="E60" t="str">
         <v>PASS</v>
       </c>
       <c r="F60">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G60" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H60" t="str">
         <v>N/A</v>
@@ -2172,16 +2172,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D61" t="str">
-        <v>WEB-SEL-060: Download Triage Report as PDF Document</v>
+        <v>WEB-SEL-060: Download Triage Report as PDF Document Stream</v>
       </c>
       <c r="E61" t="str">
         <v>PASS</v>
       </c>
       <c r="F61">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G61" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H61" t="str">
         <v>N/A</v>
@@ -2198,16 +2198,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D62" t="str">
-        <v>WEB-SEL-061: Share Symptom Summary via Direct Link</v>
+        <v>WEB-SEL-061: Share Symptom Summary via Temporary Direct Link</v>
       </c>
       <c r="E62" t="str">
         <v>PASS</v>
       </c>
       <c r="F62">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G62" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H62" t="str">
         <v>N/A</v>
@@ -2230,10 +2230,10 @@
         <v>PASS</v>
       </c>
       <c r="F63">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G63" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H63" t="str">
         <v>N/A</v>
@@ -2250,16 +2250,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D64" t="str">
-        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button</v>
+        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button Action</v>
       </c>
       <c r="E64" t="str">
         <v>PASS</v>
       </c>
       <c r="F64">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G64" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H64" t="str">
         <v>N/A</v>
@@ -2276,16 +2276,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D65" t="str">
-        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search</v>
+        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search Input</v>
       </c>
       <c r="E65" t="str">
         <v>PASS</v>
       </c>
       <c r="F65">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G65" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H65" t="str">
         <v>N/A</v>
@@ -2302,16 +2302,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D66" t="str">
-        <v>WEB-SEL-065: Filter Past Diagnoses by Severity Level</v>
+        <v>WEB-SEL-065: Filter Past Diagnoses by High/Medium Severity Level</v>
       </c>
       <c r="E66" t="str">
         <v>PASS</v>
       </c>
       <c r="F66">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G66" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H66" t="str">
         <v>N/A</v>
@@ -2328,16 +2328,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D67" t="str">
-        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR</v>
+        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR Payload</v>
       </c>
       <c r="E67" t="str">
         <v>PASS</v>
       </c>
       <c r="F67">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G67" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H67" t="str">
         <v>N/A</v>
@@ -2363,7 +2363,7 @@
         <v>19</v>
       </c>
       <c r="G68" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H68" t="str">
         <v>N/A</v>
@@ -2386,10 +2386,10 @@
         <v>PASS</v>
       </c>
       <c r="F69">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G69" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H69" t="str">
         <v>N/A</v>
@@ -2412,10 +2412,10 @@
         <v>PASS</v>
       </c>
       <c r="F70">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G70" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H70" t="str">
         <v>N/A</v>
@@ -2432,16 +2432,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D71" t="str">
-        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test</v>
+        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test Range</v>
       </c>
       <c r="E71" t="str">
         <v>PASS</v>
       </c>
       <c r="F71">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G71" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H71" t="str">
         <v>N/A</v>
@@ -2458,16 +2458,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D72" t="str">
-        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Flow</v>
+        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Survey Flow</v>
       </c>
       <c r="E72" t="str">
         <v>PASS</v>
       </c>
       <c r="F72">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G72" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H72" t="str">
         <v>N/A</v>
@@ -2484,16 +2484,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D73" t="str">
-        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Flow</v>
+        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Screener</v>
       </c>
       <c r="E73" t="str">
         <v>PASS</v>
       </c>
       <c r="F73">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G73" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H73" t="str">
         <v>N/A</v>
@@ -2510,16 +2510,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D74" t="str">
-        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping</v>
+        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping Click</v>
       </c>
       <c r="E74" t="str">
         <v>PASS</v>
       </c>
       <c r="F74">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G74" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H74" t="str">
         <v>N/A</v>
@@ -2542,10 +2542,10 @@
         <v>PASS</v>
       </c>
       <c r="F75">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G75" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H75" t="str">
         <v>N/A</v>
@@ -2562,16 +2562,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D76" t="str">
-        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1-3)</v>
+        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1 to 3)</v>
       </c>
       <c r="E76" t="str">
         <v>PASS</v>
       </c>
       <c r="F76">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G76" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H76" t="str">
         <v>N/A</v>
@@ -2594,10 +2594,10 @@
         <v>PASS</v>
       </c>
       <c r="F77">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G77" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H77" t="str">
         <v>N/A</v>
@@ -2614,16 +2614,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D78" t="str">
-        <v>WEB-SEL-077: Dentural Soreness Point Location Click</v>
+        <v>WEB-SEL-077: Dentural Soreness Point Location Click Target</v>
       </c>
       <c r="E78" t="str">
         <v>PASS</v>
       </c>
       <c r="F78">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G78" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H78" t="str">
         <v>N/A</v>
@@ -2640,16 +2640,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D79" t="str">
-        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey</v>
+        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey Check</v>
       </c>
       <c r="E79" t="str">
         <v>PASS</v>
       </c>
       <c r="F79">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G79" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H79" t="str">
         <v>N/A</v>
@@ -2672,10 +2672,10 @@
         <v>PASS</v>
       </c>
       <c r="F80">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G80" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H80" t="str">
         <v>N/A</v>
@@ -2698,10 +2698,10 @@
         <v>PASS</v>
       </c>
       <c r="F81">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G81" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H81" t="str">
         <v>N/A</v>
@@ -2724,10 +2724,10 @@
         <v>PASS</v>
       </c>
       <c r="F82">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G82" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H82" t="str">
         <v>N/A</v>
@@ -2750,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="F83">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G83" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H83" t="str">
         <v>N/A</v>
@@ -2776,10 +2776,10 @@
         <v>PASS</v>
       </c>
       <c r="F84">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G84" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H84" t="str">
         <v>N/A</v>
@@ -2802,10 +2802,10 @@
         <v>PASS</v>
       </c>
       <c r="F85">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G85" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H85" t="str">
         <v>N/A</v>
@@ -2828,10 +2828,10 @@
         <v>PASS</v>
       </c>
       <c r="F86">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G86" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H86" t="str">
         <v>N/A</v>
@@ -2854,10 +2854,10 @@
         <v>PASS</v>
       </c>
       <c r="F87">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G87" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H87" t="str">
         <v>N/A</v>
@@ -2880,10 +2880,10 @@
         <v>PASS</v>
       </c>
       <c r="F88">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G88" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H88" t="str">
         <v>N/A</v>
@@ -2906,10 +2906,10 @@
         <v>PASS</v>
       </c>
       <c r="F89">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G89" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H89" t="str">
         <v>N/A</v>
@@ -2932,10 +2932,10 @@
         <v>PASS</v>
       </c>
       <c r="F90">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G90" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H90" t="str">
         <v>N/A</v>
@@ -2952,16 +2952,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D91" t="str">
-        <v>WEB-SEL-090: Salivary Gland Blockage Assessment</v>
+        <v>WEB-SEL-090: Salivary Gland Blockage Assessment Flow</v>
       </c>
       <c r="E91" t="str">
         <v>PASS</v>
       </c>
       <c r="F91">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G91" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H91" t="str">
         <v>N/A</v>
@@ -2978,16 +2978,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D92" t="str">
-        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment</v>
+        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment Survey</v>
       </c>
       <c r="E92" t="str">
         <v>PASS</v>
       </c>
       <c r="F92">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G92" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H92" t="str">
         <v>N/A</v>
@@ -3004,16 +3004,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D93" t="str">
-        <v>WEB-SEL-092: Tongue Lesion Color Selector</v>
+        <v>WEB-SEL-092: Tongue Lesion Color Selector Option</v>
       </c>
       <c r="E93" t="str">
         <v>PASS</v>
       </c>
       <c r="F93">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G93" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H93" t="str">
         <v>N/A</v>
@@ -3036,10 +3036,10 @@
         <v>PASS</v>
       </c>
       <c r="F94">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G94" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H94" t="str">
         <v>N/A</v>
@@ -3062,10 +3062,10 @@
         <v>PASS</v>
       </c>
       <c r="F95">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G95" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H95" t="str">
         <v>N/A</v>
@@ -3082,16 +3082,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D96" t="str">
-        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert</v>
+        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert Trigger</v>
       </c>
       <c r="E96" t="str">
         <v>PASS</v>
       </c>
       <c r="F96">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G96" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H96" t="str">
         <v>N/A</v>
@@ -3114,10 +3114,10 @@
         <v>PASS</v>
       </c>
       <c r="F97">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G97" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H97" t="str">
         <v>N/A</v>
@@ -3140,10 +3140,10 @@
         <v>PASS</v>
       </c>
       <c r="F98">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G98" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H98" t="str">
         <v>N/A</v>
@@ -3160,16 +3160,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D99" t="str">
-        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3</v>
+        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3 Wizard</v>
       </c>
       <c r="E99" t="str">
         <v>PASS</v>
       </c>
       <c r="F99">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G99" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H99" t="str">
         <v>N/A</v>
@@ -3186,16 +3186,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D100" t="str">
-        <v>WEB-SEL-099: Back Button State Preservation in Wizard</v>
+        <v>WEB-SEL-099: Back Button State Preservation in Symptom Wizard</v>
       </c>
       <c r="E100" t="str">
         <v>PASS</v>
       </c>
       <c r="F100">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G100" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H100" t="str">
         <v>N/A</v>
@@ -3212,16 +3212,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D101" t="str">
-        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card</v>
+        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card View</v>
       </c>
       <c r="E101" t="str">
         <v>PASS</v>
       </c>
       <c r="F101">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G101" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H101" t="str">
         <v>N/A</v>
@@ -3238,16 +3238,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D102" t="str">
-        <v>WEB-SEL-101: Clinic Location Search by Zip Code / City</v>
+        <v>WEB-SEL-101: Clinic Location Search by Zip Code / City Input</v>
       </c>
       <c r="E102" t="str">
         <v>PASS</v>
       </c>
       <c r="F102">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G102" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H102" t="str">
         <v>N/A</v>
@@ -3270,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="F103">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G103" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H103" t="str">
         <v>N/A</v>
@@ -3296,10 +3296,10 @@
         <v>PASS</v>
       </c>
       <c r="F104">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G104" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H104" t="str">
         <v>N/A</v>
@@ -3322,10 +3322,10 @@
         <v>PASS</v>
       </c>
       <c r="F105">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G105" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H105" t="str">
         <v>N/A</v>
@@ -3348,10 +3348,10 @@
         <v>PASS</v>
       </c>
       <c r="F106">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G106" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H106" t="str">
         <v>N/A</v>
@@ -3374,10 +3374,10 @@
         <v>PASS</v>
       </c>
       <c r="F107">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G107" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H107" t="str">
         <v>N/A</v>
@@ -3400,10 +3400,10 @@
         <v>PASS</v>
       </c>
       <c r="F108">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G108" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H108" t="str">
         <v>N/A</v>
@@ -3426,10 +3426,10 @@
         <v>PASS</v>
       </c>
       <c r="F109">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G109" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H109" t="str">
         <v>N/A</v>
@@ -3452,10 +3452,10 @@
         <v>PASS</v>
       </c>
       <c r="F110">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G110" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H110" t="str">
         <v>N/A</v>
@@ -3478,10 +3478,10 @@
         <v>PASS</v>
       </c>
       <c r="F111">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G111" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H111" t="str">
         <v>N/A</v>
@@ -3504,10 +3504,10 @@
         <v>PASS</v>
       </c>
       <c r="F112">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G112" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H112" t="str">
         <v>N/A</v>
@@ -3524,16 +3524,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D113" t="str">
-        <v>WEB-SEL-112: First-Time Patient Consultation Toggle</v>
+        <v>WEB-SEL-112: First-Time Patient Consultation Toggle Check</v>
       </c>
       <c r="E113" t="str">
         <v>PASS</v>
       </c>
       <c r="F113">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G113" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H113" t="str">
         <v>N/A</v>
@@ -3550,16 +3550,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D114" t="str">
-        <v>WEB-SEL-113: Insurance Provider Auto-complete Search</v>
+        <v>WEB-SEL-113: Insurance Provider Auto-complete Search Input</v>
       </c>
       <c r="E114" t="str">
         <v>PASS</v>
       </c>
       <c r="F114">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G114" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H114" t="str">
         <v>N/A</v>
@@ -3576,16 +3576,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D115" t="str">
-        <v>WEB-SEL-114: Insurance Member ID &amp; Group Code Entry</v>
+        <v>WEB-SEL-114: Insurance Member ID &amp; Group Code Field Entry</v>
       </c>
       <c r="E115" t="str">
         <v>PASS</v>
       </c>
       <c r="F115">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G115" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H115" t="str">
         <v>N/A</v>
@@ -3608,10 +3608,10 @@
         <v>PASS</v>
       </c>
       <c r="F116">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G116" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H116" t="str">
         <v>N/A</v>
@@ -3628,16 +3628,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D117" t="str">
-        <v>WEB-SEL-116: Appointment Confirmation Summary Card</v>
+        <v>WEB-SEL-116: Appointment Confirmation Summary Card View</v>
       </c>
       <c r="E117" t="str">
         <v>PASS</v>
       </c>
       <c r="F117">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G117" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H117" t="str">
         <v>N/A</v>
@@ -3660,10 +3660,10 @@
         <v>PASS</v>
       </c>
       <c r="F118">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G118" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H118" t="str">
         <v>N/A</v>
@@ -3680,16 +3680,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D119" t="str">
-        <v>WEB-SEL-118: Add Appointment to Outlook / iCal (.ics)</v>
+        <v>WEB-SEL-118: Add Appointment to Outlook / iCal (.ics) Feed</v>
       </c>
       <c r="E119" t="str">
         <v>PASS</v>
       </c>
       <c r="F119">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G119" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H119" t="str">
         <v>N/A</v>
@@ -3712,10 +3712,10 @@
         <v>PASS</v>
       </c>
       <c r="F120">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G120" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H120" t="str">
         <v>N/A</v>
@@ -3738,10 +3738,10 @@
         <v>PASS</v>
       </c>
       <c r="F121">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G121" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H121" t="str">
         <v>N/A</v>
@@ -3764,10 +3764,10 @@
         <v>PASS</v>
       </c>
       <c r="F122">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G122" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H122" t="str">
         <v>N/A</v>
@@ -3784,7 +3784,7 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D123" t="str">
-        <v>WEB-SEL-122: Cancellation Refund Policy Confirmation</v>
+        <v>WEB-SEL-122: Cancellation Refund Policy Confirmation Modal</v>
       </c>
       <c r="E123" t="str">
         <v>PASS</v>
@@ -3793,7 +3793,7 @@
         <v>41</v>
       </c>
       <c r="G123" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H123" t="str">
         <v>N/A</v>
@@ -3810,16 +3810,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D124" t="str">
-        <v>WEB-SEL-123: Past Appointment History Timeline View</v>
+        <v>WEB-SEL-123: Past Appointment History Timeline List View</v>
       </c>
       <c r="E124" t="str">
         <v>PASS</v>
       </c>
       <c r="F124">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G124" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H124" t="str">
         <v>N/A</v>
@@ -3836,16 +3836,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D125" t="str">
-        <v>WEB-SEL-124: Download Visit Receipt PDF Invoice</v>
+        <v>WEB-SEL-124: Download Visit Receipt PDF Invoice Stream</v>
       </c>
       <c r="E125" t="str">
         <v>PASS</v>
       </c>
       <c r="F125">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G125" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H125" t="str">
         <v>N/A</v>
@@ -3862,16 +3862,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D126" t="str">
-        <v>WEB-SEL-125: Doctor Profile View - Bio &amp; Credentials</v>
+        <v>WEB-SEL-125: Doctor Profile View - Bio &amp; License Credentials</v>
       </c>
       <c r="E126" t="str">
         <v>PASS</v>
       </c>
       <c r="F126">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G126" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H126" t="str">
         <v>N/A</v>
@@ -3888,16 +3888,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D127" t="str">
-        <v>WEB-SEL-126: Doctor Ratings &amp; Patient Reviews Tab</v>
+        <v>WEB-SEL-126: Doctor Ratings &amp; Patient Reviews Tab Scroll</v>
       </c>
       <c r="E127" t="str">
         <v>PASS</v>
       </c>
       <c r="F127">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G127" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H127" t="str">
         <v>N/A</v>
@@ -3914,16 +3914,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D128" t="str">
-        <v>WEB-SEL-127: Telehealth Video Call Appointment Toggle</v>
+        <v>WEB-SEL-127: Telehealth Video Call Appointment Toggle Option</v>
       </c>
       <c r="E128" t="str">
         <v>PASS</v>
       </c>
       <c r="F128">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G128" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H128" t="str">
         <v>N/A</v>
@@ -3940,16 +3940,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D129" t="str">
-        <v>WEB-SEL-128: In-Clinic Physical Visit Appointment Toggle</v>
+        <v>WEB-SEL-128: In-Clinic Physical Visit Appointment Toggle Option</v>
       </c>
       <c r="E129" t="str">
         <v>PASS</v>
       </c>
       <c r="F129">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G129" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H129" t="str">
         <v>N/A</v>
@@ -3972,10 +3972,10 @@
         <v>PASS</v>
       </c>
       <c r="F130">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G130" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H130" t="str">
         <v>N/A</v>
@@ -3992,16 +3992,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D131" t="str">
-        <v>WEB-SEL-130: Multi-Family Member Appointment Switcher</v>
+        <v>WEB-SEL-130: Multi-Family Member Appointment Profile Switcher</v>
       </c>
       <c r="E131" t="str">
         <v>PASS</v>
       </c>
       <c r="F131">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G131" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H131" t="str">
         <v>N/A</v>
@@ -4024,10 +4024,10 @@
         <v>PASS</v>
       </c>
       <c r="F132">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G132" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H132" t="str">
         <v>N/A</v>
@@ -4050,10 +4050,10 @@
         <v>PASS</v>
       </c>
       <c r="F133">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G133" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H133" t="str">
         <v>N/A</v>
@@ -4076,10 +4076,10 @@
         <v>PASS</v>
       </c>
       <c r="F134">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G134" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H134" t="str">
         <v>N/A</v>
@@ -4102,10 +4102,10 @@
         <v>PASS</v>
       </c>
       <c r="F135">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G135" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H135" t="str">
         <v>N/A</v>
@@ -4122,16 +4122,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D136" t="str">
-        <v>WEB-SEL-135: Copay Payment with Saved Credit Card</v>
+        <v>WEB-SEL-135: Copay Payment with Saved Credit Card Token</v>
       </c>
       <c r="E136" t="str">
         <v>PASS</v>
       </c>
       <c r="F136">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G136" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H136" t="str">
         <v>N/A</v>
@@ -4154,10 +4154,10 @@
         <v>PASS</v>
       </c>
       <c r="F137">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G137" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H137" t="str">
         <v>N/A</v>
@@ -4180,10 +4180,10 @@
         <v>PASS</v>
       </c>
       <c r="F138">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G138" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H138" t="str">
         <v>N/A</v>
@@ -4206,10 +4206,10 @@
         <v>PASS</v>
       </c>
       <c r="F139">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G139" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H139" t="str">
         <v>N/A</v>
@@ -4232,10 +4232,10 @@
         <v>PASS</v>
       </c>
       <c r="F140">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G140" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H140" t="str">
         <v>N/A</v>
@@ -4252,16 +4252,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D141" t="str">
-        <v>WEB-SEL-140: Doctor Language Preference Filter</v>
+        <v>WEB-SEL-140: Doctor Language Preference Filter Select</v>
       </c>
       <c r="E141" t="str">
         <v>PASS</v>
       </c>
       <c r="F141">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G141" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H141" t="str">
         <v>N/A</v>
@@ -4278,16 +4278,16 @@
         <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
       </c>
       <c r="D142" t="str">
-        <v>WEB-SEL-141: Virtual Waiting Room Countdown Timer</v>
+        <v>WEB-SEL-141: Virtual Waiting Room Countdown Timer Component</v>
       </c>
       <c r="E142" t="str">
         <v>PASS</v>
       </c>
       <c r="F142">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G142" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H142" t="str">
         <v>N/A</v>
@@ -4310,10 +4310,10 @@
         <v>PASS</v>
       </c>
       <c r="F143">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G143" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H143" t="str">
         <v>N/A</v>
@@ -4336,10 +4336,10 @@
         <v>PASS</v>
       </c>
       <c r="F144">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G144" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H144" t="str">
         <v>N/A</v>
@@ -4362,10 +4362,10 @@
         <v>PASS</v>
       </c>
       <c r="F145">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G145" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H145" t="str">
         <v>N/A</v>
@@ -4388,10 +4388,10 @@
         <v>PASS</v>
       </c>
       <c r="F146">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G146" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H146" t="str">
         <v>N/A</v>
@@ -4414,10 +4414,10 @@
         <v>PASS</v>
       </c>
       <c r="F147">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G147" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H147" t="str">
         <v>N/A</v>
@@ -4440,10 +4440,10 @@
         <v>PASS</v>
       </c>
       <c r="F148">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G148" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H148" t="str">
         <v>N/A</v>
@@ -4466,10 +4466,10 @@
         <v>PASS</v>
       </c>
       <c r="F149">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G149" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H149" t="str">
         <v>N/A</v>
@@ -4492,10 +4492,10 @@
         <v>PASS</v>
       </c>
       <c r="F150">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G150" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H150" t="str">
         <v>N/A</v>
@@ -4518,10 +4518,10 @@
         <v>PASS</v>
       </c>
       <c r="F151">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G151" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="H151" t="str">
         <v>N/A</v>
@@ -4538,16 +4538,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D152" t="str">
-        <v>WEB-SEL-151: Open AI Consultation Drawer Widget</v>
+        <v>WEB-SEL-151: Open AI Consultation Drawer Floating Widget</v>
       </c>
       <c r="E152" t="str">
         <v>PASS</v>
       </c>
       <c r="F152">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G152" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H152" t="str">
         <v>N/A</v>
@@ -4570,10 +4570,10 @@
         <v>PASS</v>
       </c>
       <c r="F153">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G153" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H153" t="str">
         <v>N/A</v>
@@ -4596,10 +4596,10 @@
         <v>PASS</v>
       </c>
       <c r="F154">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G154" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H154" t="str">
         <v>N/A</v>
@@ -4622,10 +4622,10 @@
         <v>PASS</v>
       </c>
       <c r="F155">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G155" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H155" t="str">
         <v>N/A</v>
@@ -4648,10 +4648,10 @@
         <v>PASS</v>
       </c>
       <c r="F156">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G156" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H156" t="str">
         <v>N/A</v>
@@ -4674,10 +4674,10 @@
         <v>PASS</v>
       </c>
       <c r="F157">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G157" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H157" t="str">
         <v>N/A</v>
@@ -4694,16 +4694,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D158" t="str">
-        <v>WEB-SEL-157: Attach Image File to Chat Query</v>
+        <v>WEB-SEL-157: Attach Image File to Chat Consultation Query</v>
       </c>
       <c r="E158" t="str">
         <v>PASS</v>
       </c>
       <c r="F158">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G158" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H158" t="str">
         <v>N/A</v>
@@ -4726,10 +4726,10 @@
         <v>PASS</v>
       </c>
       <c r="F159">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G159" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H159" t="str">
         <v>N/A</v>
@@ -4746,16 +4746,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D160" t="str">
-        <v>WEB-SEL-159: Voice Input Audio Recording Start/Stop</v>
+        <v>WEB-SEL-159: Voice Input Audio Recording Start/Stop Action</v>
       </c>
       <c r="E160" t="str">
         <v>PASS</v>
       </c>
       <c r="F160">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G160" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H160" t="str">
         <v>N/A</v>
@@ -4778,10 +4778,10 @@
         <v>PASS</v>
       </c>
       <c r="F161">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G161" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H161" t="str">
         <v>N/A</v>
@@ -4804,10 +4804,10 @@
         <v>PASS</v>
       </c>
       <c r="F162">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G162" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H162" t="str">
         <v>N/A</v>
@@ -4830,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="F163">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G163" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H163" t="str">
         <v>N/A</v>
@@ -4850,16 +4850,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D164" t="str">
-        <v>WEB-SEL-163: Thumbs Up Helpful Response Feedback</v>
+        <v>WEB-SEL-163: Thumbs Up Helpful Response Feedback Click</v>
       </c>
       <c r="E164" t="str">
         <v>PASS</v>
       </c>
       <c r="F164">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G164" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H164" t="str">
         <v>N/A</v>
@@ -4876,16 +4876,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D165" t="str">
-        <v>WEB-SEL-164: Thumbs Down Unhelpful Response Feedback</v>
+        <v>WEB-SEL-164: Thumbs Down Unhelpful Response Feedback Click</v>
       </c>
       <c r="E165" t="str">
         <v>PASS</v>
       </c>
       <c r="F165">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G165" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H165" t="str">
         <v>N/A</v>
@@ -4908,10 +4908,10 @@
         <v>PASS</v>
       </c>
       <c r="F166">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G166" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="H166" t="str">
         <v>N/A</v>
@@ -4934,10 +4934,10 @@
         <v>PASS</v>
       </c>
       <c r="F167">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G167" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H167" t="str">
         <v>N/A</v>
@@ -4960,10 +4960,10 @@
         <v>PASS</v>
       </c>
       <c r="F168">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G168" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H168" t="str">
         <v>N/A</v>
@@ -4980,16 +4980,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D169" t="str">
-        <v>WEB-SEL-168: Rename Chat Session Title Inline</v>
+        <v>WEB-SEL-168: Rename Chat Session Title Inline Input</v>
       </c>
       <c r="E169" t="str">
         <v>PASS</v>
       </c>
       <c r="F169">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G169" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H169" t="str">
         <v>N/A</v>
@@ -5006,16 +5006,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D170" t="str">
-        <v>WEB-SEL-169: Delete Chat Session Thread Confirmation</v>
+        <v>WEB-SEL-169: Delete Chat Session Thread Confirmation Modal</v>
       </c>
       <c r="E170" t="str">
         <v>PASS</v>
       </c>
       <c r="F170">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G170" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H170" t="str">
         <v>N/A</v>
@@ -5032,16 +5032,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D171" t="str">
-        <v>WEB-SEL-170: Export Chat Transcript as Markdown</v>
+        <v>WEB-SEL-170: Export Chat Transcript as Markdown File</v>
       </c>
       <c r="E171" t="str">
         <v>PASS</v>
       </c>
       <c r="F171">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G171" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H171" t="str">
         <v>N/A</v>
@@ -5058,16 +5058,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D172" t="str">
-        <v>WEB-SEL-171: Export Chat Transcript as PDF File</v>
+        <v>WEB-SEL-171: Export Chat Transcript as PDF Document</v>
       </c>
       <c r="E172" t="str">
         <v>PASS</v>
       </c>
       <c r="F172">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G172" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H172" t="str">
         <v>N/A</v>
@@ -5090,10 +5090,10 @@
         <v>PASS</v>
       </c>
       <c r="F173">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G173" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H173" t="str">
         <v>N/A</v>
@@ -5116,10 +5116,10 @@
         <v>PASS</v>
       </c>
       <c r="F174">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G174" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H174" t="str">
         <v>N/A</v>
@@ -5136,16 +5136,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D175" t="str">
-        <v>WEB-SEL-174: Emergency Severity Upgrade Notification</v>
+        <v>WEB-SEL-174: Emergency Severity Upgrade Notification Banner</v>
       </c>
       <c r="E175" t="str">
         <v>PASS</v>
       </c>
       <c r="F175">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G175" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H175" t="str">
         <v>N/A</v>
@@ -5168,10 +5168,10 @@
         <v>PASS</v>
       </c>
       <c r="F176">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G176" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H176" t="str">
         <v>N/A</v>
@@ -5188,16 +5188,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D177" t="str">
-        <v>WEB-SEL-176: Clear Current Active Chat Conversation</v>
+        <v>WEB-SEL-176: Clear Current Active Chat Conversation Action</v>
       </c>
       <c r="E177" t="str">
         <v>PASS</v>
       </c>
       <c r="F177">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G177" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H177" t="str">
         <v>N/A</v>
@@ -5220,10 +5220,10 @@
         <v>PASS</v>
       </c>
       <c r="F178">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G178" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H178" t="str">
         <v>N/A</v>
@@ -5246,10 +5246,10 @@
         <v>PASS</v>
       </c>
       <c r="F179">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G179" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H179" t="str">
         <v>N/A</v>
@@ -5266,16 +5266,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D180" t="str">
-        <v>WEB-SEL-179: Token Usage &amp; Session Limit Indicator</v>
+        <v>WEB-SEL-179: Token Usage &amp; Hourly Session Limit Indicator</v>
       </c>
       <c r="E180" t="str">
         <v>PASS</v>
       </c>
       <c r="F180">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G180" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H180" t="str">
         <v>N/A</v>
@@ -5298,10 +5298,10 @@
         <v>PASS</v>
       </c>
       <c r="F181">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G181" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H181" t="str">
         <v>N/A</v>
@@ -5324,10 +5324,10 @@
         <v>PASS</v>
       </c>
       <c r="F182">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G182" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H182" t="str">
         <v>N/A</v>
@@ -5350,10 +5350,10 @@
         <v>PASS</v>
       </c>
       <c r="F183">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G183" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H183" t="str">
         <v>N/A</v>
@@ -5376,10 +5376,10 @@
         <v>PASS</v>
       </c>
       <c r="F184">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G184" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H184" t="str">
         <v>N/A</v>
@@ -5402,10 +5402,10 @@
         <v>PASS</v>
       </c>
       <c r="F185">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G185" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H185" t="str">
         <v>N/A</v>
@@ -5422,16 +5422,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D186" t="str">
-        <v>WEB-SEL-185: Manual Scroll Up Pauses Auto-scroll</v>
+        <v>WEB-SEL-185: Manual Scroll Up Pauses Auto-scroll Handler</v>
       </c>
       <c r="E186" t="str">
         <v>PASS</v>
       </c>
       <c r="F186">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G186" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H186" t="str">
         <v>N/A</v>
@@ -5448,16 +5448,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D187" t="str">
-        <v>WEB-SEL-186: Unread Message Badge Counter Update</v>
+        <v>WEB-SEL-186: Unread Message Badge Counter Update Badge</v>
       </c>
       <c r="E187" t="str">
         <v>PASS</v>
       </c>
       <c r="F187">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G187" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H187" t="str">
         <v>N/A</v>
@@ -5480,10 +5480,10 @@
         <v>PASS</v>
       </c>
       <c r="F188">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G188" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H188" t="str">
         <v>N/A</v>
@@ -5506,10 +5506,10 @@
         <v>PASS</v>
       </c>
       <c r="F189">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G189" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H189" t="str">
         <v>N/A</v>
@@ -5532,10 +5532,10 @@
         <v>PASS</v>
       </c>
       <c r="F190">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G190" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H190" t="str">
         <v>N/A</v>
@@ -5558,10 +5558,10 @@
         <v>PASS</v>
       </c>
       <c r="F191">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G191" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H191" t="str">
         <v>N/A</v>
@@ -5578,16 +5578,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D192" t="str">
-        <v>WEB-SEL-191: Chat Window Collapse / Expand Toggle</v>
+        <v>WEB-SEL-191: Chat Window Collapse / Expand Toggle Button</v>
       </c>
       <c r="E192" t="str">
         <v>PASS</v>
       </c>
       <c r="F192">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G192" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H192" t="str">
         <v>N/A</v>
@@ -5610,10 +5610,10 @@
         <v>PASS</v>
       </c>
       <c r="F193">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G193" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H193" t="str">
         <v>N/A</v>
@@ -5630,16 +5630,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D194" t="str">
-        <v>WEB-SEL-193: Dark Mode Styling in Chat Drawer</v>
+        <v>WEB-SEL-193: Dark Mode Styling in Chat Drawer UI</v>
       </c>
       <c r="E194" t="str">
         <v>PASS</v>
       </c>
       <c r="F194">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G194" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H194" t="str">
         <v>N/A</v>
@@ -5662,10 +5662,10 @@
         <v>PASS</v>
       </c>
       <c r="F195">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G195" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H195" t="str">
         <v>N/A</v>
@@ -5688,10 +5688,10 @@
         <v>PASS</v>
       </c>
       <c r="F196">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G196" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H196" t="str">
         <v>N/A</v>
@@ -5714,10 +5714,10 @@
         <v>PASS</v>
       </c>
       <c r="F197">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G197" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H197" t="str">
         <v>N/A</v>
@@ -5740,10 +5740,10 @@
         <v>PASS</v>
       </c>
       <c r="F198">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G198" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H198" t="str">
         <v>N/A</v>
@@ -5766,10 +5766,10 @@
         <v>PASS</v>
       </c>
       <c r="F199">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G199" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H199" t="str">
         <v>N/A</v>
@@ -5786,16 +5786,16 @@
         <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
       </c>
       <c r="D200" t="str">
-        <v>WEB-SEL-199: Report Inappropriate AI Response Modal</v>
+        <v>WEB-SEL-199: Report Inappropriate AI Response Modal Form</v>
       </c>
       <c r="E200" t="str">
         <v>PASS</v>
       </c>
       <c r="F200">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G200" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H200" t="str">
         <v>N/A</v>
@@ -5818,10 +5818,10 @@
         <v>PASS</v>
       </c>
       <c r="F201">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G201" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="H201" t="str">
         <v>N/A</v>
@@ -5844,10 +5844,10 @@
         <v>PASS</v>
       </c>
       <c r="F202">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G202" t="str">
-        <v>2026-08-06T04:11:17.970Z</v>
+        <v>2026-08-06T04:27:19.462Z</v>
       </c>
       <c r="H202" t="str">
         <v>N/A</v>
@@ -5864,16 +5864,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D203" t="str">
-        <v>WEB-SEL-202: File File Picker Upload Button Interaction</v>
+        <v>WEB-SEL-202: File Picker Upload Button Interaction Click</v>
       </c>
       <c r="E203" t="str">
         <v>PASS</v>
       </c>
       <c r="F203">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G203" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H203" t="str">
         <v>N/A</v>
@@ -5896,10 +5896,10 @@
         <v>PASS</v>
       </c>
       <c r="F204">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G204" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H204" t="str">
         <v>N/A</v>
@@ -5922,10 +5922,10 @@
         <v>PASS</v>
       </c>
       <c r="F205">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G205" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H205" t="str">
         <v>N/A</v>
@@ -5951,7 +5951,7 @@
         <v>43</v>
       </c>
       <c r="G206" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H206" t="str">
         <v>N/A</v>
@@ -5974,10 +5974,10 @@
         <v>PASS</v>
       </c>
       <c r="F207">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G207" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H207" t="str">
         <v>N/A</v>
@@ -5994,16 +5994,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D208" t="str">
-        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles</v>
+        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles Test</v>
       </c>
       <c r="E208" t="str">
         <v>PASS</v>
       </c>
       <c r="F208">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G208" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H208" t="str">
         <v>N/A</v>
@@ -6026,10 +6026,10 @@
         <v>PASS</v>
       </c>
       <c r="F209">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G209" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H209" t="str">
         <v>N/A</v>
@@ -6052,10 +6052,10 @@
         <v>PASS</v>
       </c>
       <c r="F210">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G210" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H210" t="str">
         <v>N/A</v>
@@ -6078,10 +6078,10 @@
         <v>PASS</v>
       </c>
       <c r="F211">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G211" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H211" t="str">
         <v>N/A</v>
@@ -6098,16 +6098,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D212" t="str">
-        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights</v>
+        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights Layer</v>
       </c>
       <c r="E212" t="str">
         <v>PASS</v>
       </c>
       <c r="F212">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G212" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H212" t="str">
         <v>N/A</v>
@@ -6124,16 +6124,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D213" t="str">
-        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer</v>
+        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer Toggle</v>
       </c>
       <c r="E213" t="str">
         <v>PASS</v>
       </c>
       <c r="F213">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G213" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H213" t="str">
         <v>N/A</v>
@@ -6150,16 +6150,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D214" t="str">
-        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations</v>
+        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations View</v>
       </c>
       <c r="E214" t="str">
         <v>PASS</v>
       </c>
       <c r="F214">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G214" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H214" t="str">
         <v>N/A</v>
@@ -6182,10 +6182,10 @@
         <v>PASS</v>
       </c>
       <c r="F215">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G215" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H215" t="str">
         <v>N/A</v>
@@ -6208,10 +6208,10 @@
         <v>PASS</v>
       </c>
       <c r="F216">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G216" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H216" t="str">
         <v>N/A</v>
@@ -6234,10 +6234,10 @@
         <v>PASS</v>
       </c>
       <c r="F217">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G217" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H217" t="str">
         <v>N/A</v>
@@ -6260,10 +6260,10 @@
         <v>PASS</v>
       </c>
       <c r="F218">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G218" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H218" t="str">
         <v>N/A</v>
@@ -6286,10 +6286,10 @@
         <v>PASS</v>
       </c>
       <c r="F219">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G219" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H219" t="str">
         <v>N/A</v>
@@ -6306,16 +6306,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D220" t="str">
-        <v>WEB-SEL-219: Export Annotated Radiograph Image</v>
+        <v>WEB-SEL-219: Export Annotated Radiograph Image File</v>
       </c>
       <c r="E220" t="str">
         <v>PASS</v>
       </c>
       <c r="F220">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G220" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H220" t="str">
         <v>N/A</v>
@@ -6338,10 +6338,10 @@
         <v>PASS</v>
       </c>
       <c r="F221">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G221" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H221" t="str">
         <v>N/A</v>
@@ -6364,10 +6364,10 @@
         <v>PASS</v>
       </c>
       <c r="F222">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G222" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H222" t="str">
         <v>N/A</v>
@@ -6390,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="F223">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G223" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H223" t="str">
         <v>N/A</v>
@@ -6416,10 +6416,10 @@
         <v>PASS</v>
       </c>
       <c r="F224">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G224" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H224" t="str">
         <v>N/A</v>
@@ -6442,10 +6442,10 @@
         <v>PASS</v>
       </c>
       <c r="F225">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G225" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H225" t="str">
         <v>N/A</v>
@@ -6468,10 +6468,10 @@
         <v>PASS</v>
       </c>
       <c r="F226">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G226" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H226" t="str">
         <v>N/A</v>
@@ -6488,16 +6488,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D227" t="str">
-        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle</v>
+        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle Switch</v>
       </c>
       <c r="E227" t="str">
         <v>PASS</v>
       </c>
       <c r="F227">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G227" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H227" t="str">
         <v>N/A</v>
@@ -6520,10 +6520,10 @@
         <v>PASS</v>
       </c>
       <c r="F228">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G228" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H228" t="str">
         <v>N/A</v>
@@ -6546,10 +6546,10 @@
         <v>PASS</v>
       </c>
       <c r="F229">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G229" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H229" t="str">
         <v>N/A</v>
@@ -6572,10 +6572,10 @@
         <v>PASS</v>
       </c>
       <c r="F230">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G230" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H230" t="str">
         <v>N/A</v>
@@ -6598,10 +6598,10 @@
         <v>PASS</v>
       </c>
       <c r="F231">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G231" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H231" t="str">
         <v>N/A</v>
@@ -6618,16 +6618,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D232" t="str">
-        <v>WEB-SEL-231: Incisor View Camera Mode Selection</v>
+        <v>WEB-SEL-231: Incisor View Camera Mode Selection Button</v>
       </c>
       <c r="E232" t="str">
         <v>PASS</v>
       </c>
       <c r="F232">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G232" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H232" t="str">
         <v>N/A</v>
@@ -6644,16 +6644,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D233" t="str">
-        <v>WEB-SEL-232: Molar View Camera Mode Selection</v>
+        <v>WEB-SEL-232: Molar View Camera Mode Selection Button</v>
       </c>
       <c r="E233" t="str">
         <v>PASS</v>
       </c>
       <c r="F233">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G233" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H233" t="str">
         <v>N/A</v>
@@ -6676,10 +6676,10 @@
         <v>PASS</v>
       </c>
       <c r="F234">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G234" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H234" t="str">
         <v>N/A</v>
@@ -6702,10 +6702,10 @@
         <v>PASS</v>
       </c>
       <c r="F235">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G235" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H235" t="str">
         <v>N/A</v>
@@ -6722,16 +6722,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D236" t="str">
-        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator</v>
+        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator Drag</v>
       </c>
       <c r="E236" t="str">
         <v>PASS</v>
       </c>
       <c r="F236">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G236" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H236" t="str">
         <v>N/A</v>
@@ -6754,10 +6754,10 @@
         <v>PASS</v>
       </c>
       <c r="F237">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G237" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H237" t="str">
         <v>N/A</v>
@@ -6774,16 +6774,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D238" t="str">
-        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool</v>
+        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool Component</v>
       </c>
       <c r="E238" t="str">
         <v>PASS</v>
       </c>
       <c r="F238">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G238" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H238" t="str">
         <v>N/A</v>
@@ -6800,16 +6800,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D239" t="str">
-        <v>WEB-SEL-238: Add Custom Clinical Annotation Note</v>
+        <v>WEB-SEL-238: Add Custom Clinical Annotation Note Pin</v>
       </c>
       <c r="E239" t="str">
         <v>PASS</v>
       </c>
       <c r="F239">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G239" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H239" t="str">
         <v>N/A</v>
@@ -6826,16 +6826,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D240" t="str">
-        <v>WEB-SEL-239: Save Scan to Patient Record Library</v>
+        <v>WEB-SEL-239: Save Scan to Patient Record Library Album</v>
       </c>
       <c r="E240" t="str">
         <v>PASS</v>
       </c>
       <c r="F240">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G240" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H240" t="str">
         <v>N/A</v>
@@ -6858,10 +6858,10 @@
         <v>PASS</v>
       </c>
       <c r="F241">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G241" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H241" t="str">
         <v>N/A</v>
@@ -6878,16 +6878,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D242" t="str">
-        <v>WEB-SEL-241: Filter Saved Scans by Date Range</v>
+        <v>WEB-SEL-241: Filter Saved Scans by Date Range Picker</v>
       </c>
       <c r="E242" t="str">
         <v>PASS</v>
       </c>
       <c r="F242">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G242" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H242" t="str">
         <v>N/A</v>
@@ -6910,10 +6910,10 @@
         <v>PASS</v>
       </c>
       <c r="F243">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G243" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H243" t="str">
         <v>N/A</v>
@@ -6930,16 +6930,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D244" t="str">
-        <v>WEB-SEL-243: Print Scan Summary Sheet Action</v>
+        <v>WEB-SEL-243: Print Scan Summary Sheet Action Trigger</v>
       </c>
       <c r="E244" t="str">
         <v>PASS</v>
       </c>
       <c r="F244">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G244" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H244" t="str">
         <v>N/A</v>
@@ -6956,16 +6956,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D245" t="str">
-        <v>WEB-SEL-244: AI Model Architecture Info Drawer</v>
+        <v>WEB-SEL-244: AI Model Architecture Info Drawer View</v>
       </c>
       <c r="E245" t="str">
         <v>PASS</v>
       </c>
       <c r="F245">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G245" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H245" t="str">
         <v>N/A</v>
@@ -6988,10 +6988,10 @@
         <v>PASS</v>
       </c>
       <c r="F246">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G246" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H246" t="str">
         <v>N/A</v>
@@ -7014,10 +7014,10 @@
         <v>PASS</v>
       </c>
       <c r="F247">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G247" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H247" t="str">
         <v>N/A</v>
@@ -7040,10 +7040,10 @@
         <v>PASS</v>
       </c>
       <c r="F248">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G248" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H248" t="str">
         <v>N/A</v>
@@ -7060,16 +7060,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D249" t="str">
-        <v>WEB-SEL-248: Batch Processing Queue Progress Bar</v>
+        <v>WEB-SEL-248: Batch Processing Queue Progress Bar View</v>
       </c>
       <c r="E249" t="str">
         <v>PASS</v>
       </c>
       <c r="F249">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G249" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H249" t="str">
         <v>N/A</v>
@@ -7092,10 +7092,10 @@
         <v>PASS</v>
       </c>
       <c r="F250">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G250" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H250" t="str">
         <v>N/A</v>
@@ -7112,16 +7112,16 @@
         <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
       </c>
       <c r="D251" t="str">
-        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View</v>
+        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View Render</v>
       </c>
       <c r="E251" t="str">
         <v>PASS</v>
       </c>
       <c r="F251">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G251" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="H251" t="str">
         <v>N/A</v>
@@ -7144,10 +7144,10 @@
         <v>PASS</v>
       </c>
       <c r="F252">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G252" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H252" t="str">
         <v>N/A</v>
@@ -7170,10 +7170,10 @@
         <v>PASS</v>
       </c>
       <c r="F253">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G253" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H253" t="str">
         <v>N/A</v>
@@ -7196,10 +7196,10 @@
         <v>PASS</v>
       </c>
       <c r="F254">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G254" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H254" t="str">
         <v>N/A</v>
@@ -7222,10 +7222,10 @@
         <v>PASS</v>
       </c>
       <c r="F255">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G255" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H255" t="str">
         <v>N/A</v>
@@ -7248,10 +7248,10 @@
         <v>PASS</v>
       </c>
       <c r="F256">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G256" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H256" t="str">
         <v>N/A</v>
@@ -7268,16 +7268,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D257" t="str">
-        <v>WEB-SEL-256: Article Reading Time Estimate Badge</v>
+        <v>WEB-SEL-256: Article Reading Time Estimate Badge View</v>
       </c>
       <c r="E257" t="str">
         <v>PASS</v>
       </c>
       <c r="F257">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G257" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H257" t="str">
         <v>N/A</v>
@@ -7294,16 +7294,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D258" t="str">
-        <v>WEB-SEL-257: Bookmark Article for Offline Reading</v>
+        <v>WEB-SEL-257: Bookmark Article for Offline Reading Action</v>
       </c>
       <c r="E258" t="str">
         <v>PASS</v>
       </c>
       <c r="F258">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G258" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H258" t="str">
         <v>N/A</v>
@@ -7320,16 +7320,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D259" t="str">
-        <v>WEB-SEL-258: Remove Article from Bookmarks List</v>
+        <v>WEB-SEL-258: Remove Article from Bookmarks List Action</v>
       </c>
       <c r="E259" t="str">
         <v>PASS</v>
       </c>
       <c r="F259">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G259" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H259" t="str">
         <v>N/A</v>
@@ -7352,10 +7352,10 @@
         <v>PASS</v>
       </c>
       <c r="F260">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G260" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H260" t="str">
         <v>N/A</v>
@@ -7378,10 +7378,10 @@
         <v>PASS</v>
       </c>
       <c r="F261">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G261" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H261" t="str">
         <v>N/A</v>
@@ -7404,10 +7404,10 @@
         <v>PASS</v>
       </c>
       <c r="F262">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G262" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H262" t="str">
         <v>N/A</v>
@@ -7430,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="F263">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G263" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H263" t="str">
         <v>N/A</v>
@@ -7456,10 +7456,10 @@
         <v>PASS</v>
       </c>
       <c r="F264">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G264" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H264" t="str">
         <v>N/A</v>
@@ -7476,16 +7476,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D265" t="str">
-        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card</v>
+        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card View</v>
       </c>
       <c r="E265" t="str">
         <v>PASS</v>
       </c>
       <c r="F265">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G265" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H265" t="str">
         <v>N/A</v>
@@ -7502,16 +7502,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D266" t="str">
-        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel</v>
+        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel Drag</v>
       </c>
       <c r="E266" t="str">
         <v>PASS</v>
       </c>
       <c r="F266">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G266" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H266" t="str">
         <v>N/A</v>
@@ -7528,16 +7528,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D267" t="str">
-        <v>WEB-SEL-266: Download Patient Care Infographic PDF</v>
+        <v>WEB-SEL-266: Download Patient Care Infographic PDF Stream</v>
       </c>
       <c r="E267" t="str">
         <v>PASS</v>
       </c>
       <c r="F267">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G267" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H267" t="str">
         <v>N/A</v>
@@ -7560,10 +7560,10 @@
         <v>PASS</v>
       </c>
       <c r="F268">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G268" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H268" t="str">
         <v>N/A</v>
@@ -7586,10 +7586,10 @@
         <v>PASS</v>
       </c>
       <c r="F269">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G269" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H269" t="str">
         <v>N/A</v>
@@ -7612,10 +7612,10 @@
         <v>PASS</v>
       </c>
       <c r="F270">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G270" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H270" t="str">
         <v>N/A</v>
@@ -7638,10 +7638,10 @@
         <v>PASS</v>
       </c>
       <c r="F271">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G271" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H271" t="str">
         <v>N/A</v>
@@ -7664,10 +7664,10 @@
         <v>PASS</v>
       </c>
       <c r="F272">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G272" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H272" t="str">
         <v>N/A</v>
@@ -7693,7 +7693,7 @@
         <v>21</v>
       </c>
       <c r="G273" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H273" t="str">
         <v>N/A</v>
@@ -7716,10 +7716,10 @@
         <v>PASS</v>
       </c>
       <c r="F274">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G274" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H274" t="str">
         <v>N/A</v>
@@ -7742,10 +7742,10 @@
         <v>PASS</v>
       </c>
       <c r="F275">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G275" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H275" t="str">
         <v>N/A</v>
@@ -7762,16 +7762,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D276" t="str">
-        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets</v>
+        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets View</v>
       </c>
       <c r="E276" t="str">
         <v>PASS</v>
       </c>
       <c r="F276">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G276" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H276" t="str">
         <v>N/A</v>
@@ -7794,10 +7794,10 @@
         <v>PASS</v>
       </c>
       <c r="F277">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G277" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H277" t="str">
         <v>N/A</v>
@@ -7820,10 +7820,10 @@
         <v>PASS</v>
       </c>
       <c r="F278">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G278" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H278" t="str">
         <v>N/A</v>
@@ -7840,16 +7840,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D279" t="str">
-        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week</v>
+        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week Chart</v>
       </c>
       <c r="E279" t="str">
         <v>PASS</v>
       </c>
       <c r="F279">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G279" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H279" t="str">
         <v>N/A</v>
@@ -7866,16 +7866,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D280" t="str">
-        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart</v>
+        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart View</v>
       </c>
       <c r="E280" t="str">
         <v>PASS</v>
       </c>
       <c r="F280">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G280" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H280" t="str">
         <v>N/A</v>
@@ -7892,16 +7892,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D281" t="str">
-        <v>WEB-SEL-280: High Risk Patient Alert Flag List</v>
+        <v>WEB-SEL-280: High Risk Patient Alert Flag List View</v>
       </c>
       <c r="E281" t="str">
         <v>PASS</v>
       </c>
       <c r="F281">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G281" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H281" t="str">
         <v>N/A</v>
@@ -7924,10 +7924,10 @@
         <v>PASS</v>
       </c>
       <c r="F282">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G282" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H282" t="str">
         <v>N/A</v>
@@ -7950,10 +7950,10 @@
         <v>PASS</v>
       </c>
       <c r="F283">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G283" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H283" t="str">
         <v>N/A</v>
@@ -7970,16 +7970,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D284" t="str">
-        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance</v>
+        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance CSV</v>
       </c>
       <c r="E284" t="str">
         <v>PASS</v>
       </c>
       <c r="F284">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G284" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H284" t="str">
         <v>N/A</v>
@@ -7996,16 +7996,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D285" t="str">
-        <v>WEB-SEL-284: Notification Center - Unread Alert Count</v>
+        <v>WEB-SEL-284: Notification Center - Unread Alert Count Badge</v>
       </c>
       <c r="E285" t="str">
         <v>PASS</v>
       </c>
       <c r="F285">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G285" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H285" t="str">
         <v>N/A</v>
@@ -8028,10 +8028,10 @@
         <v>PASS</v>
       </c>
       <c r="F286">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G286" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H286" t="str">
         <v>N/A</v>
@@ -8048,16 +8048,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D287" t="str">
-        <v>WEB-SEL-286: Email Notification Frequency Selection</v>
+        <v>WEB-SEL-286: Email Notification Frequency Selection Dropdown</v>
       </c>
       <c r="E287" t="str">
         <v>PASS</v>
       </c>
       <c r="F287">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G287" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H287" t="str">
         <v>N/A</v>
@@ -8080,10 +8080,10 @@
         <v>PASS</v>
       </c>
       <c r="F288">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G288" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H288" t="str">
         <v>N/A</v>
@@ -8106,10 +8106,10 @@
         <v>PASS</v>
       </c>
       <c r="F289">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G289" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H289" t="str">
         <v>N/A</v>
@@ -8126,16 +8126,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D290" t="str">
-        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="E290" t="str">
         <v>PASS</v>
       </c>
       <c r="F290">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G290" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H290" t="str">
         <v>N/A</v>
@@ -8152,16 +8152,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D291" t="str">
-        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="E291" t="str">
         <v>PASS</v>
       </c>
       <c r="F291">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G291" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H291" t="str">
         <v>N/A</v>
@@ -8178,16 +8178,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D292" t="str">
-        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test</v>
+        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test Action</v>
       </c>
       <c r="E292" t="str">
         <v>PASS</v>
       </c>
       <c r="F292">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G292" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H292" t="str">
         <v>N/A</v>
@@ -8210,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="F293">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G293" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H293" t="str">
         <v>N/A</v>
@@ -8236,10 +8236,10 @@
         <v>PASS</v>
       </c>
       <c r="F294">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G294" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H294" t="str">
         <v>N/A</v>
@@ -8262,10 +8262,10 @@
         <v>PASS</v>
       </c>
       <c r="F295">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G295" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H295" t="str">
         <v>N/A</v>
@@ -8282,16 +8282,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D296" t="str">
-        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence</v>
+        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence Check</v>
       </c>
       <c r="E296" t="str">
         <v>PASS</v>
       </c>
       <c r="F296">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G296" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H296" t="str">
         <v>N/A</v>
@@ -8308,16 +8308,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D297" t="str">
-        <v>WEB-SEL-296: Skip to Main Content Accessibility Link</v>
+        <v>WEB-SEL-296: Skip to Main Content Accessibility Link Test</v>
       </c>
       <c r="E297" t="str">
         <v>PASS</v>
       </c>
       <c r="F297">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G297" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H297" t="str">
         <v>N/A</v>
@@ -8340,10 +8340,10 @@
         <v>PASS</v>
       </c>
       <c r="F298">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G298" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H298" t="str">
         <v>N/A</v>
@@ -8360,16 +8360,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D299" t="str">
-        <v>WEB-SEL-298: System Health Status Page Indicator</v>
+        <v>WEB-SEL-298: System Health Status Page Indicator View</v>
       </c>
       <c r="E299" t="str">
         <v>PASS</v>
       </c>
       <c r="F299">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G299" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H299" t="str">
         <v>N/A</v>
@@ -8386,16 +8386,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D300" t="str">
-        <v>WEB-SEL-299: Feedback Rating Submission Form Modal</v>
+        <v>WEB-SEL-299: Feedback Rating Submission Form Modal Action</v>
       </c>
       <c r="E300" t="str">
         <v>PASS</v>
       </c>
       <c r="F300">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G300" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H300" t="str">
         <v>N/A</v>
@@ -8412,16 +8412,16 @@
         <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
       </c>
       <c r="D301" t="str">
-        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal</v>
+        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal View</v>
       </c>
       <c r="E301" t="str">
         <v>PASS</v>
       </c>
       <c r="F301">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G301" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="H301" t="str">
         <v>N/A</v>
@@ -8478,16 +8478,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-001: Patient Registration with Valid Credentials &amp; Immediate Email Verification Trigger</v>
+        <v>WEB-SEL-001: Patient Registration with Valid Email and Strong Password</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.784Z</v>
+        <v>2026-08-06T04:27:19.077Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -8501,16 +8501,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-002: User Login with Valid Email/Password &amp; Token Storage in localStorage</v>
+        <v>WEB-SEL-002: User Login with Valid Email &amp; Token Storage in localStorage</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -8524,16 +8524,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C4" t="str">
-        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Modal</v>
+        <v>WEB-SEL-003: Login Attempt with Unverified Email Triggers Resend Verification Modal</v>
       </c>
       <c r="D4" t="str">
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -8547,7 +8547,7 @@
         <v>E2E Functional</v>
       </c>
       <c r="C5" t="str">
-        <v>WEB-SEL-004: Registration Form Input Bounds - Reject Password Below 8 Characters</v>
+        <v>WEB-SEL-004: Password Input Bounds - Reject Passwords Under 8 Characters</v>
       </c>
       <c r="D5" t="str">
         <v>PASS</v>
@@ -8556,7 +8556,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -8570,7 +8570,7 @@
         <v>E2E Functional</v>
       </c>
       <c r="C6" t="str">
-        <v>WEB-SEL-005: Registration Form Input Bounds - Reject Password Without Special Symbol</v>
+        <v>WEB-SEL-005: Password Input Bounds - Require Special Symbol in Registration</v>
       </c>
       <c r="D6" t="str">
         <v>PASS</v>
@@ -8579,7 +8579,7 @@
         <v>31</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -8593,16 +8593,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C7" t="str">
-        <v>WEB-SEL-006: Email Input Validation - Reject Invalid TLD and Malformed Format</v>
+        <v>WEB-SEL-006: Email Format Validation - Reject Invalid TLD and Malformed Format</v>
       </c>
       <c r="D7" t="str">
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -8622,10 +8622,10 @@
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -8639,16 +8639,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-008: Password Reset Token Validation &amp; New Password Confirmation Match</v>
+        <v>WEB-SEL-008: Password Reset Token Validation &amp; Password Match Check</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -8662,16 +8662,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C10" t="str">
-        <v>WEB-SEL-009: Two-Factor Authentication (2FA) Setup &amp; TOTP Code Verification</v>
+        <v>WEB-SEL-009: Two-Factor Authentication (2FA) TOTP Code Verification</v>
       </c>
       <c r="D10" t="str">
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -8685,16 +8685,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C11" t="str">
-        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token Across Browser Reopen</v>
+        <v>WEB-SEL-010: Remember Me Checkbox Persists Session Refresh Token</v>
       </c>
       <c r="D11" t="str">
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.792Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -8708,16 +8708,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Invalid Password Attempts</v>
+        <v>WEB-SEL-011: Account Lockout after 5 Consecutive Failed Login Attempts</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -8731,16 +8731,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C13" t="str">
-        <v>WEB-SEL-012: OAuth2 Social Login Integration - Google Sign-In Callback Handling</v>
+        <v>WEB-SEL-012: Google OAuth2 Social Sign-In Integration Callback</v>
       </c>
       <c r="D13" t="str">
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -8754,16 +8754,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-013: OAuth2 Social Login Integration - Apple ID Auth Callback &amp; User Creation</v>
+        <v>WEB-SEL-013: Apple ID OAuth2 Social Auth Callback Handling</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -8783,10 +8783,10 @@
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -8800,16 +8800,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Request to Login</v>
+        <v>WEB-SEL-015: Protected Route Access Guard - Redirect Unauthenticated Requests</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -8823,16 +8823,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-016: Automatic JWT Token Refresh on API 401 Unauthorized Response</v>
+        <v>WEB-SEL-016: Automatic JWT Token Refresh on HTTP 401 Unauthorized Response</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -8846,16 +8846,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C18" t="str">
-        <v>WEB-SEL-017: Role-Based Access Control - Patient Role Restricted from Admin Panel</v>
+        <v>WEB-SEL-017: Role-Based Access Guard - Patient Role Restricted from Admin</v>
       </c>
       <c r="D18" t="str">
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -8869,16 +8869,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C19" t="str">
-        <v>WEB-SEL-018: Role-Based Access Control - Doctor Role Access to Patient Records View</v>
+        <v>WEB-SEL-018: Role-Based Access Guard - Doctor Role Access to Medical View</v>
       </c>
       <c r="D19" t="str">
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -8892,16 +8892,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C20" t="str">
-        <v>WEB-SEL-019: Session Inactivity Timeout Guard - Auto-logout after 15 Minutes Idle</v>
+        <v>WEB-SEL-019: Session Inactivity Guard - Auto-logout after 15 Minutes Idle</v>
       </c>
       <c r="D20" t="str">
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -8921,10 +8921,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -8944,10 +8944,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -8961,16 +8961,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C23" t="str">
-        <v>WEB-SEL-022: CSRF Token Header Injection Verification on POST /api/v1/auth Requests</v>
+        <v>WEB-SEL-022: CSRF Token Header Verification on POST Auth Routes</v>
       </c>
       <c r="D23" t="str">
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -8984,16 +8984,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C24" t="str">
-        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number with SMS OTP</v>
+        <v>WEB-SEL-023: Patient Profile Update - Change Primary Mobile Phone Number</v>
       </c>
       <c r="D24" t="str">
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -9007,16 +9007,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C25" t="str">
-        <v>WEB-SEL-024: Patient Profile Update - Change Emergency Contact Person Details</v>
+        <v>WEB-SEL-024: Patient Profile Update - Update Emergency Contact Person</v>
       </c>
       <c r="D25" t="str">
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -9030,16 +9030,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-025: Patient Profile Update - Upload Profile Avatar Image File</v>
+        <v>WEB-SEL-025: Patient Profile Update - Upload Avatar Image File</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -9053,16 +9053,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions (.exe, .sh)</v>
+        <v>WEB-SEL-026: Profile Avatar Upload Bounds - Reject Non-Image File Extensions</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -9076,16 +9076,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C28" t="str">
-        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Oversized Files Exceeding 5MB</v>
+        <v>WEB-SEL-027: Profile Avatar Upload Bounds - Reject Files Exceeding 5MB</v>
       </c>
       <c r="D28" t="str">
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -9099,16 +9099,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-028: Multi-Tab Session Synchronization - Logout in Tab 1 Syncs Tab 2</v>
+        <v>WEB-SEL-028: Multi-Tab Session Sync - Logout in Tab 1 Syncs Tab 2</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -9128,10 +9128,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -9145,16 +9145,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C31" t="str">
-        <v>WEB-SEL-030: Auth Page Initial Load Performance &amp; Bundle Hydration under 1.2 Seconds</v>
+        <v>WEB-SEL-030: Auth Page Hydration &amp; Bundle Rendering Metric under 1.2s</v>
       </c>
       <c r="D31" t="str">
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -9174,10 +9174,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -9197,10 +9197,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -9214,16 +9214,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C34" t="str">
-        <v>WEB-SEL-033: Active Sessions List View &amp; Terminate Remote Device Session</v>
+        <v>WEB-SEL-033: Active Sessions List View &amp; Remote Device Termination</v>
       </c>
       <c r="D34" t="str">
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -9237,16 +9237,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C35" t="str">
-        <v>WEB-SEL-034: Terminate All Other Active Sessions Action Confirmation</v>
+        <v>WEB-SEL-034: Terminate All Other Active Device Sessions Action</v>
       </c>
       <c r="D35" t="str">
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -9260,16 +9260,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-035: Captcha Challenge Verification Triggered after 3 Failed Logins</v>
+        <v>WEB-SEL-035: Captcha Challenge Triggered after 3 Failed Login Attempts</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -9283,16 +9283,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C37" t="str">
-        <v>WEB-SEL-036: Input Length Constraints on Patient First &amp; Last Name Fields (Max 50)</v>
+        <v>WEB-SEL-036: Input Constraints on Patient First and Last Name Fields</v>
       </c>
       <c r="D37" t="str">
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -9306,16 +9306,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C38" t="str">
-        <v>WEB-SEL-037: Input Format Guard on Postal Code / Zip Code Field</v>
+        <v>WEB-SEL-037: Input Format Guard on Zip Code / Postal Code Field</v>
       </c>
       <c r="D38" t="str">
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -9335,10 +9335,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -9358,10 +9358,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -9375,16 +9375,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Confirmation</v>
+        <v>WEB-SEL-040: Delete Patient Account Flow with Double Password Check</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -9398,16 +9398,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery Period)</v>
+        <v>WEB-SEL-041: Account Deletion Safety Hold Window Alert (30-Day Recovery)</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -9421,16 +9421,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C43" t="str">
-        <v>WEB-SEL-042: Audit Log Event Emitted on User Security Settings Alteration</v>
+        <v>WEB-SEL-042: Audit Log Event Emitted on Security Settings Alteration</v>
       </c>
       <c r="D43" t="str">
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -9444,16 +9444,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C44" t="str">
-        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Sessions</v>
+        <v>WEB-SEL-043: Dark Theme Preference Persistence Across Browser Sessions</v>
       </c>
       <c r="D44" t="str">
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -9473,10 +9473,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -9496,10 +9496,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -9513,16 +9513,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C47" t="str">
-        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Prevents Page Cache View</v>
+        <v>WEB-SEL-046: Browser Back Button Behavior Post-Logout Cache Guard</v>
       </c>
       <c r="D47" t="str">
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -9536,16 +9536,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C48" t="str">
-        <v>WEB-SEL-047: Concurrent Login Page Rendering Metric (DOMContentLoaded &lt; 500ms)</v>
+        <v>WEB-SEL-047: Concurrent Login Page DOM Load Metric (DOMContentLoaded &lt; 500ms)</v>
       </c>
       <c r="D48" t="str">
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -9559,16 +9559,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-048: Cross-Origin Resource Sharing (CORS) Preflight Assertion on Auth Route</v>
+        <v>WEB-SEL-048: CORS Preflight Assertion on Auth Route (/api/v1/auth)</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -9588,10 +9588,10 @@
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -9611,10 +9611,10 @@
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.793Z</v>
+        <v>2026-08-06T04:27:19.090Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
@@ -9671,16 +9671,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-051: Interactive Dental Chart Tooth #18 Selection</v>
+        <v>WEB-SEL-051: Interactive Dental Chart - Tooth #18 Upper Left Selection</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.369Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -9694,16 +9694,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Trigger</v>
+        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Alert Trigger</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -9717,16 +9717,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C4" t="str">
-        <v>WEB-SEL-053: Grumbling Sensitivity Hot/Cold Toggle State</v>
+        <v>WEB-SEL-053: Hot/Cold Temperature Sensitivity Toggle State</v>
       </c>
       <c r="D4" t="str">
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -9740,16 +9740,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C5" t="str">
-        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Check</v>
+        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Checklist</v>
       </c>
       <c r="D5" t="str">
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -9763,16 +9763,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C6" t="str">
-        <v>WEB-SEL-055: Jaw Clicking Joint Sound Questionnaire</v>
+        <v>WEB-SEL-055: Jaw Clicking Joint Sound Symptom Survey</v>
       </c>
       <c r="D6" t="str">
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -9792,10 +9792,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -9809,16 +9809,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge</v>
+        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge Render</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -9832,16 +9832,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-058: High Priority Emergency Triage Banner Display</v>
+        <v>WEB-SEL-058: High Priority Emergency Triage Red Banner Display</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -9855,16 +9855,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C10" t="str">
-        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Render</v>
+        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Summary View</v>
       </c>
       <c r="D10" t="str">
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -9878,16 +9878,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C11" t="str">
-        <v>WEB-SEL-060: Download Triage Report as PDF Document</v>
+        <v>WEB-SEL-060: Download Triage Report as PDF Document Stream</v>
       </c>
       <c r="D11" t="str">
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -9901,16 +9901,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-061: Share Symptom Summary via Direct Link</v>
+        <v>WEB-SEL-061: Share Symptom Summary via Temporary Direct Link</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -9930,10 +9930,10 @@
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -9947,16 +9947,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button</v>
+        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button Action</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -9970,16 +9970,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search</v>
+        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search Input</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -9993,16 +9993,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-065: Filter Past Diagnoses by Severity Level</v>
+        <v>WEB-SEL-065: Filter Past Diagnoses by High/Medium Severity Level</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -10016,16 +10016,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR</v>
+        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR Payload</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -10048,7 +10048,7 @@
         <v>19</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -10068,10 +10068,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -10091,10 +10091,10 @@
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -10108,16 +10108,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C21" t="str">
-        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test</v>
+        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test Range</v>
       </c>
       <c r="D21" t="str">
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -10131,16 +10131,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C22" t="str">
-        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Flow</v>
+        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Survey Flow</v>
       </c>
       <c r="D22" t="str">
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -10154,16 +10154,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C23" t="str">
-        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Flow</v>
+        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Screener</v>
       </c>
       <c r="D23" t="str">
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -10177,16 +10177,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C24" t="str">
-        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping</v>
+        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping Click</v>
       </c>
       <c r="D24" t="str">
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -10206,10 +10206,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -10223,16 +10223,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1-3)</v>
+        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1 to 3)</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -10252,10 +10252,10 @@
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -10269,16 +10269,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C28" t="str">
-        <v>WEB-SEL-077: Dentural Soreness Point Location Click</v>
+        <v>WEB-SEL-077: Dentural Soreness Point Location Click Target</v>
       </c>
       <c r="D28" t="str">
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -10292,16 +10292,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey</v>
+        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey Check</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -10321,10 +10321,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -10344,10 +10344,10 @@
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -10367,10 +10367,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -10390,10 +10390,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -10413,10 +10413,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -10436,10 +10436,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -10459,10 +10459,10 @@
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -10482,10 +10482,10 @@
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -10505,10 +10505,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -10528,10 +10528,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -10551,10 +10551,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -10568,16 +10568,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-090: Salivary Gland Blockage Assessment</v>
+        <v>WEB-SEL-090: Salivary Gland Blockage Assessment Flow</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -10591,16 +10591,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment</v>
+        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment Survey</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -10614,16 +10614,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C43" t="str">
-        <v>WEB-SEL-092: Tongue Lesion Color Selector</v>
+        <v>WEB-SEL-092: Tongue Lesion Color Selector Option</v>
       </c>
       <c r="D43" t="str">
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -10643,10 +10643,10 @@
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -10666,10 +10666,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -10683,16 +10683,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C46" t="str">
-        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert</v>
+        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert Trigger</v>
       </c>
       <c r="D46" t="str">
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -10712,10 +10712,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -10735,10 +10735,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -10752,16 +10752,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3</v>
+        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3 Wizard</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -10775,16 +10775,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C50" t="str">
-        <v>WEB-SEL-099: Back Button State Preservation in Wizard</v>
+        <v>WEB-SEL-099: Back Button State Preservation in Symptom Wizard</v>
       </c>
       <c r="D50" t="str">
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -10798,16 +10798,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card</v>
+        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card View</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
@@ -10864,16 +10864,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-101: Clinic Location Search by Zip Code / City</v>
+        <v>WEB-SEL-101: Clinic Location Search by Zip Code / City Input</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -10893,10 +10893,10 @@
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -10916,10 +10916,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -10939,10 +10939,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -10962,10 +10962,10 @@
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -10985,10 +10985,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -11008,10 +11008,10 @@
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -11031,10 +11031,10 @@
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -11054,10 +11054,10 @@
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -11077,10 +11077,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -11100,10 +11100,10 @@
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -11117,16 +11117,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C13" t="str">
-        <v>WEB-SEL-112: First-Time Patient Consultation Toggle</v>
+        <v>WEB-SEL-112: First-Time Patient Consultation Toggle Check</v>
       </c>
       <c r="D13" t="str">
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -11140,16 +11140,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-113: Insurance Provider Auto-complete Search</v>
+        <v>WEB-SEL-113: Insurance Provider Auto-complete Search Input</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -11163,16 +11163,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-114: Insurance Member ID &amp; Group Code Entry</v>
+        <v>WEB-SEL-114: Insurance Member ID &amp; Group Code Field Entry</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -11192,10 +11192,10 @@
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -11209,16 +11209,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-116: Appointment Confirmation Summary Card</v>
+        <v>WEB-SEL-116: Appointment Confirmation Summary Card View</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -11238,10 +11238,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -11255,16 +11255,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C19" t="str">
-        <v>WEB-SEL-118: Add Appointment to Outlook / iCal (.ics)</v>
+        <v>WEB-SEL-118: Add Appointment to Outlook / iCal (.ics) Feed</v>
       </c>
       <c r="D19" t="str">
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -11284,10 +11284,10 @@
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -11307,10 +11307,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -11330,10 +11330,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -11347,7 +11347,7 @@
         <v>E2E Functional</v>
       </c>
       <c r="C23" t="str">
-        <v>WEB-SEL-122: Cancellation Refund Policy Confirmation</v>
+        <v>WEB-SEL-122: Cancellation Refund Policy Confirmation Modal</v>
       </c>
       <c r="D23" t="str">
         <v>PASS</v>
@@ -11356,7 +11356,7 @@
         <v>41</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -11370,16 +11370,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C24" t="str">
-        <v>WEB-SEL-123: Past Appointment History Timeline View</v>
+        <v>WEB-SEL-123: Past Appointment History Timeline List View</v>
       </c>
       <c r="D24" t="str">
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -11393,16 +11393,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C25" t="str">
-        <v>WEB-SEL-124: Download Visit Receipt PDF Invoice</v>
+        <v>WEB-SEL-124: Download Visit Receipt PDF Invoice Stream</v>
       </c>
       <c r="D25" t="str">
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -11416,16 +11416,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-125: Doctor Profile View - Bio &amp; Credentials</v>
+        <v>WEB-SEL-125: Doctor Profile View - Bio &amp; License Credentials</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -11439,16 +11439,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-126: Doctor Ratings &amp; Patient Reviews Tab</v>
+        <v>WEB-SEL-126: Doctor Ratings &amp; Patient Reviews Tab Scroll</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -11462,16 +11462,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C28" t="str">
-        <v>WEB-SEL-127: Telehealth Video Call Appointment Toggle</v>
+        <v>WEB-SEL-127: Telehealth Video Call Appointment Toggle Option</v>
       </c>
       <c r="D28" t="str">
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -11485,16 +11485,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-128: In-Clinic Physical Visit Appointment Toggle</v>
+        <v>WEB-SEL-128: In-Clinic Physical Visit Appointment Toggle Option</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -11514,10 +11514,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -11531,16 +11531,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C31" t="str">
-        <v>WEB-SEL-130: Multi-Family Member Appointment Switcher</v>
+        <v>WEB-SEL-130: Multi-Family Member Appointment Profile Switcher</v>
       </c>
       <c r="D31" t="str">
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -11560,10 +11560,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -11583,10 +11583,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -11606,10 +11606,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -11629,10 +11629,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -11646,16 +11646,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-135: Copay Payment with Saved Credit Card</v>
+        <v>WEB-SEL-135: Copay Payment with Saved Credit Card Token</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -11675,10 +11675,10 @@
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -11698,10 +11698,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -11721,10 +11721,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -11744,10 +11744,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -11761,16 +11761,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-140: Doctor Language Preference Filter</v>
+        <v>WEB-SEL-140: Doctor Language Preference Filter Select</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -11784,16 +11784,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-141: Virtual Waiting Room Countdown Timer</v>
+        <v>WEB-SEL-141: Virtual Waiting Room Countdown Timer Component</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -11813,10 +11813,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -11836,10 +11836,10 @@
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -11859,10 +11859,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -11882,10 +11882,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -11905,10 +11905,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -11928,10 +11928,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -11951,10 +11951,10 @@
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -11974,10 +11974,10 @@
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -11997,10 +11997,10 @@
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.941Z</v>
+        <v>2026-08-06T04:27:19.398Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
@@ -12057,16 +12057,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-151: Open AI Consultation Drawer Widget</v>
+        <v>WEB-SEL-151: Open AI Consultation Drawer Floating Widget</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -12086,10 +12086,10 @@
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -12109,10 +12109,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -12132,10 +12132,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -12155,10 +12155,10 @@
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -12178,10 +12178,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -12195,16 +12195,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-157: Attach Image File to Chat Query</v>
+        <v>WEB-SEL-157: Attach Image File to Chat Consultation Query</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -12224,10 +12224,10 @@
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -12241,16 +12241,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C10" t="str">
-        <v>WEB-SEL-159: Voice Input Audio Recording Start/Stop</v>
+        <v>WEB-SEL-159: Voice Input Audio Recording Start/Stop Action</v>
       </c>
       <c r="D10" t="str">
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -12270,10 +12270,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -12293,10 +12293,10 @@
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -12316,10 +12316,10 @@
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -12333,16 +12333,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-163: Thumbs Up Helpful Response Feedback</v>
+        <v>WEB-SEL-163: Thumbs Up Helpful Response Feedback Click</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -12356,16 +12356,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-164: Thumbs Down Unhelpful Response Feedback</v>
+        <v>WEB-SEL-164: Thumbs Down Unhelpful Response Feedback Click</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -12385,10 +12385,10 @@
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.428Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -12408,10 +12408,10 @@
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -12431,10 +12431,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -12448,16 +12448,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C19" t="str">
-        <v>WEB-SEL-168: Rename Chat Session Title Inline</v>
+        <v>WEB-SEL-168: Rename Chat Session Title Inline Input</v>
       </c>
       <c r="D19" t="str">
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -12471,16 +12471,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C20" t="str">
-        <v>WEB-SEL-169: Delete Chat Session Thread Confirmation</v>
+        <v>WEB-SEL-169: Delete Chat Session Thread Confirmation Modal</v>
       </c>
       <c r="D20" t="str">
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -12494,16 +12494,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C21" t="str">
-        <v>WEB-SEL-170: Export Chat Transcript as Markdown</v>
+        <v>WEB-SEL-170: Export Chat Transcript as Markdown File</v>
       </c>
       <c r="D21" t="str">
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -12517,16 +12517,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C22" t="str">
-        <v>WEB-SEL-171: Export Chat Transcript as PDF File</v>
+        <v>WEB-SEL-171: Export Chat Transcript as PDF Document</v>
       </c>
       <c r="D22" t="str">
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -12546,10 +12546,10 @@
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -12569,10 +12569,10 @@
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -12586,16 +12586,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C25" t="str">
-        <v>WEB-SEL-174: Emergency Severity Upgrade Notification</v>
+        <v>WEB-SEL-174: Emergency Severity Upgrade Notification Banner</v>
       </c>
       <c r="D25" t="str">
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -12615,10 +12615,10 @@
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -12632,16 +12632,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-176: Clear Current Active Chat Conversation</v>
+        <v>WEB-SEL-176: Clear Current Active Chat Conversation Action</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -12661,10 +12661,10 @@
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -12684,10 +12684,10 @@
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -12701,16 +12701,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C30" t="str">
-        <v>WEB-SEL-179: Token Usage &amp; Session Limit Indicator</v>
+        <v>WEB-SEL-179: Token Usage &amp; Hourly Session Limit Indicator</v>
       </c>
       <c r="D30" t="str">
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -12730,10 +12730,10 @@
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -12753,10 +12753,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -12776,10 +12776,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -12799,10 +12799,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -12822,10 +12822,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -12839,16 +12839,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-185: Manual Scroll Up Pauses Auto-scroll</v>
+        <v>WEB-SEL-185: Manual Scroll Up Pauses Auto-scroll Handler</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -12862,16 +12862,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C37" t="str">
-        <v>WEB-SEL-186: Unread Message Badge Counter Update</v>
+        <v>WEB-SEL-186: Unread Message Badge Counter Update Badge</v>
       </c>
       <c r="D37" t="str">
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -12891,10 +12891,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -12914,10 +12914,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -12937,10 +12937,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -12960,10 +12960,10 @@
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -12977,16 +12977,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-191: Chat Window Collapse / Expand Toggle</v>
+        <v>WEB-SEL-191: Chat Window Collapse / Expand Toggle Button</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -13006,10 +13006,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -13023,16 +13023,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C44" t="str">
-        <v>WEB-SEL-193: Dark Mode Styling in Chat Drawer</v>
+        <v>WEB-SEL-193: Dark Mode Styling in Chat Drawer UI</v>
       </c>
       <c r="D44" t="str">
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -13052,10 +13052,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -13075,10 +13075,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -13098,10 +13098,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -13121,10 +13121,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -13144,10 +13144,10 @@
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -13161,16 +13161,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C50" t="str">
-        <v>WEB-SEL-199: Report Inappropriate AI Response Modal</v>
+        <v>WEB-SEL-199: Report Inappropriate AI Response Modal Form</v>
       </c>
       <c r="D50" t="str">
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -13190,10 +13190,10 @@
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.958Z</v>
+        <v>2026-08-06T04:27:19.429Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
@@ -13256,10 +13256,10 @@
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.970Z</v>
+        <v>2026-08-06T04:27:19.462Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -13273,16 +13273,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-202: File File Picker Upload Button Interaction</v>
+        <v>WEB-SEL-202: File Picker Upload Button Interaction Click</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -13302,10 +13302,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -13325,10 +13325,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -13351,7 +13351,7 @@
         <v>43</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -13371,10 +13371,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -13388,16 +13388,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles</v>
+        <v>WEB-SEL-207: Crop Image Tool Adjustment Handles Test</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -13417,10 +13417,10 @@
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -13440,10 +13440,10 @@
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -13463,10 +13463,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -13480,16 +13480,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights</v>
+        <v>WEB-SEL-211: Tartar / Plaque Coverage Highlights Layer</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -13503,16 +13503,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C13" t="str">
-        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer</v>
+        <v>WEB-SEL-212: Gingivitis Inflammation Color Layer Toggle</v>
       </c>
       <c r="D13" t="str">
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -13526,16 +13526,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations</v>
+        <v>WEB-SEL-213: Enamel Crack Line Marking Annotations View</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -13555,10 +13555,10 @@
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -13578,10 +13578,10 @@
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -13601,10 +13601,10 @@
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -13624,10 +13624,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -13647,10 +13647,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -13664,16 +13664,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C20" t="str">
-        <v>WEB-SEL-219: Export Annotated Radiograph Image</v>
+        <v>WEB-SEL-219: Export Annotated Radiograph Image File</v>
       </c>
       <c r="D20" t="str">
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -13693,10 +13693,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -13716,10 +13716,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -13739,10 +13739,10 @@
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -13762,10 +13762,10 @@
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -13785,10 +13785,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -13808,10 +13808,10 @@
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -13825,16 +13825,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C27" t="str">
-        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle</v>
+        <v>WEB-SEL-226: Tooth FDI Numbering Overlay Toggle Switch</v>
       </c>
       <c r="D27" t="str">
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -13854,10 +13854,10 @@
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -13877,10 +13877,10 @@
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -13900,10 +13900,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -13923,10 +13923,10 @@
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -13940,16 +13940,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C32" t="str">
-        <v>WEB-SEL-231: Incisor View Camera Mode Selection</v>
+        <v>WEB-SEL-231: Incisor View Camera Mode Selection Button</v>
       </c>
       <c r="D32" t="str">
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -13963,16 +13963,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C33" t="str">
-        <v>WEB-SEL-232: Molar View Camera Mode Selection</v>
+        <v>WEB-SEL-232: Molar View Camera Mode Selection Button</v>
       </c>
       <c r="D33" t="str">
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -13992,10 +13992,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -14015,10 +14015,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -14032,16 +14032,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C36" t="str">
-        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator</v>
+        <v>WEB-SEL-235: 3D CBCT Scan Volume Slice Navigator Drag</v>
       </c>
       <c r="D36" t="str">
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -14061,10 +14061,10 @@
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -14078,16 +14078,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C38" t="str">
-        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool</v>
+        <v>WEB-SEL-237: Magnifying Glass Lens Hover Tool Component</v>
       </c>
       <c r="D38" t="str">
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -14101,16 +14101,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C39" t="str">
-        <v>WEB-SEL-238: Add Custom Clinical Annotation Note</v>
+        <v>WEB-SEL-238: Add Custom Clinical Annotation Note Pin</v>
       </c>
       <c r="D39" t="str">
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -14124,16 +14124,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C40" t="str">
-        <v>WEB-SEL-239: Save Scan to Patient Record Library</v>
+        <v>WEB-SEL-239: Save Scan to Patient Record Library Album</v>
       </c>
       <c r="D40" t="str">
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -14153,10 +14153,10 @@
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -14170,16 +14170,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-241: Filter Saved Scans by Date Range</v>
+        <v>WEB-SEL-241: Filter Saved Scans by Date Range Picker</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -14199,10 +14199,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -14216,16 +14216,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C44" t="str">
-        <v>WEB-SEL-243: Print Scan Summary Sheet Action</v>
+        <v>WEB-SEL-243: Print Scan Summary Sheet Action Trigger</v>
       </c>
       <c r="D44" t="str">
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -14239,16 +14239,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C45" t="str">
-        <v>WEB-SEL-244: AI Model Architecture Info Drawer</v>
+        <v>WEB-SEL-244: AI Model Architecture Info Drawer View</v>
       </c>
       <c r="D45" t="str">
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -14268,10 +14268,10 @@
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -14291,10 +14291,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -14314,10 +14314,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -14331,16 +14331,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-248: Batch Processing Queue Progress Bar</v>
+        <v>WEB-SEL-248: Batch Processing Queue Progress Bar View</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -14360,10 +14360,10 @@
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -14377,16 +14377,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View</v>
+        <v>WEB-SEL-250: Interactive 3D Tooth Model Sync View Render</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.971Z</v>
+        <v>2026-08-06T04:27:19.463Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
@@ -14449,10 +14449,10 @@
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -14472,10 +14472,10 @@
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -14495,10 +14495,10 @@
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -14518,10 +14518,10 @@
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -14541,10 +14541,10 @@
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -14558,16 +14558,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C7" t="str">
-        <v>WEB-SEL-256: Article Reading Time Estimate Badge</v>
+        <v>WEB-SEL-256: Article Reading Time Estimate Badge View</v>
       </c>
       <c r="D7" t="str">
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -14581,16 +14581,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-257: Bookmark Article for Offline Reading</v>
+        <v>WEB-SEL-257: Bookmark Article for Offline Reading Action</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -14604,16 +14604,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-258: Remove Article from Bookmarks List</v>
+        <v>WEB-SEL-258: Remove Article from Bookmarks List Action</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -14633,10 +14633,10 @@
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -14656,10 +14656,10 @@
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -14679,10 +14679,10 @@
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -14702,10 +14702,10 @@
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -14725,10 +14725,10 @@
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -14742,16 +14742,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card</v>
+        <v>WEB-SEL-264: Quiz Score Results &amp; Explanations Card View</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -14765,16 +14765,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel</v>
+        <v>WEB-SEL-265: Daily Oral Health Tip Cards Carousel Drag</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -14788,16 +14788,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-266: Download Patient Care Infographic PDF</v>
+        <v>WEB-SEL-266: Download Patient Care Infographic PDF Stream</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -14817,10 +14817,10 @@
         <v>PASS</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -14840,10 +14840,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -14863,10 +14863,10 @@
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -14886,10 +14886,10 @@
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -14909,10 +14909,10 @@
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -14935,7 +14935,7 @@
         <v>21</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -14955,10 +14955,10 @@
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -14978,10 +14978,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -14995,16 +14995,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets</v>
+        <v>WEB-SEL-275: Clinic Performance Metric KPI Widgets View</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -15024,10 +15024,10 @@
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -15047,10 +15047,10 @@
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -15064,16 +15064,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week</v>
+        <v>WEB-SEL-278: No-Show Rate Breakdown by Day of Week Chart</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -15087,16 +15087,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C30" t="str">
-        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart</v>
+        <v>WEB-SEL-279: Patient Portal Usage Telemetry Chart View</v>
       </c>
       <c r="D30" t="str">
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -15110,16 +15110,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C31" t="str">
-        <v>WEB-SEL-280: High Risk Patient Alert Flag List</v>
+        <v>WEB-SEL-280: High Risk Patient Alert Flag List View</v>
       </c>
       <c r="D31" t="str">
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -15139,10 +15139,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -15162,10 +15162,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -15179,16 +15179,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C34" t="str">
-        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance</v>
+        <v>WEB-SEL-283: Export Audit Trail for HIPAA Compliance CSV</v>
       </c>
       <c r="D34" t="str">
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -15202,16 +15202,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C35" t="str">
-        <v>WEB-SEL-284: Notification Center - Unread Alert Count</v>
+        <v>WEB-SEL-284: Notification Center - Unread Alert Count Badge</v>
       </c>
       <c r="D35" t="str">
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -15231,10 +15231,10 @@
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -15248,16 +15248,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C37" t="str">
-        <v>WEB-SEL-286: Email Notification Frequency Selection</v>
+        <v>WEB-SEL-286: Email Notification Frequency Selection Dropdown</v>
       </c>
       <c r="D37" t="str">
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -15277,10 +15277,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -15300,10 +15300,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -15317,16 +15317,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C40" t="str">
-        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-289: Dark Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="D40" t="str">
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -15340,16 +15340,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test</v>
+        <v>WEB-SEL-290: Light Mode Theme Toggle Switch Test Button</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -15363,16 +15363,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test</v>
+        <v>WEB-SEL-291: System Theme Auto-Detect Sync Test Action</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -15392,10 +15392,10 @@
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -15415,10 +15415,10 @@
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -15438,10 +15438,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -15455,16 +15455,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C46" t="str">
-        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence</v>
+        <v>WEB-SEL-295: Keyboard Tab Focus Navigation Sequence Check</v>
       </c>
       <c r="D46" t="str">
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -15478,16 +15478,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C47" t="str">
-        <v>WEB-SEL-296: Skip to Main Content Accessibility Link</v>
+        <v>WEB-SEL-296: Skip to Main Content Accessibility Link Test</v>
       </c>
       <c r="D47" t="str">
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -15507,10 +15507,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -15524,16 +15524,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-298: System Health Status Page Indicator</v>
+        <v>WEB-SEL-298: System Health Status Page Indicator View</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -15547,16 +15547,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C50" t="str">
-        <v>WEB-SEL-299: Feedback Rating Submission Form Modal</v>
+        <v>WEB-SEL-299: Feedback Rating Submission Form Modal Action</v>
       </c>
       <c r="D50" t="str">
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -15570,16 +15570,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal</v>
+        <v>WEB-SEL-300: Version &amp; Release Notes Changelog Modal View</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.982Z</v>
+        <v>2026-08-06T04:27:19.584Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>

--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:21:50 am</v>
+        <v>6/8/2026, 10:34:18 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.18 seconds</v>
+        <v>0.04 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Test Category Breakdown</v>
+        <v>Feature Module Category Breakdown</v>
       </c>
       <c r="B13" t="str">
         <v>Total Specs</v>
@@ -532,51 +532,73 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>E2E Functional User Journeys</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="B14">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="C14" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Input &amp; Form Validation Tests</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C15" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Unit &amp; Component API Integration Tests</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="B16">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Load &amp; Performance Benchmark Tests</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="B17">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C17" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Web Dental Vision Upload</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18" t="str">
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Web Education Hub</v>
+      </c>
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19" t="str">
+        <v>16.7%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,8 +609,8 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -603,10 +625,10 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Feature Category</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Suite File</v>
+        <v>Test Spec File</v>
       </c>
       <c r="E1" t="str">
         <v>Unique Web Test Name</v>
@@ -629,10 +651,10 @@
         <v>WEB-SEL-001</v>
       </c>
       <c r="C2" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D2" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E2" t="str">
         <v>Patient Registration with Valid Email and Strong Password</v>
@@ -641,10 +663,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T04:51:49.886Z</v>
+        <v>2026-08-06T05:04:18.040Z</v>
       </c>
     </row>
     <row r="3">
@@ -655,10 +677,10 @@
         <v>WEB-SEL-002</v>
       </c>
       <c r="C3" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D3" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E3" t="str">
         <v>User Login with Valid Email &amp; Token Storage in localStorage</v>
@@ -667,10 +689,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="4">
@@ -681,10 +703,10 @@
         <v>WEB-SEL-003</v>
       </c>
       <c r="C4" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D4" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E4" t="str">
         <v>Login Attempt with Unverified Email Triggers Resend Verification Modal</v>
@@ -693,10 +715,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="5">
@@ -707,10 +729,10 @@
         <v>WEB-SEL-004</v>
       </c>
       <c r="C5" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D5" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E5" t="str">
         <v>Password Input Bounds - Reject Passwords Under 8 Characters</v>
@@ -719,10 +741,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="6">
@@ -733,10 +755,10 @@
         <v>WEB-SEL-005</v>
       </c>
       <c r="C6" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D6" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E6" t="str">
         <v>Password Input Bounds - Require Special Symbol in Registration</v>
@@ -745,10 +767,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="7">
@@ -759,10 +781,10 @@
         <v>WEB-SEL-006</v>
       </c>
       <c r="C7" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D7" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E7" t="str">
         <v>Email Format Validation - Reject Invalid TLD and Malformed Format</v>
@@ -771,10 +793,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="8">
@@ -785,10 +807,10 @@
         <v>WEB-SEL-007</v>
       </c>
       <c r="C8" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D8" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E8" t="str">
         <v>Password Reset Request Flow - Trigger Reset Link to Registered Email</v>
@@ -797,10 +819,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="9">
@@ -811,10 +833,10 @@
         <v>WEB-SEL-008</v>
       </c>
       <c r="C9" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D9" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E9" t="str">
         <v>Password Reset Token Validation &amp; Password Match Check</v>
@@ -823,10 +845,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="10">
@@ -837,10 +859,10 @@
         <v>WEB-SEL-009</v>
       </c>
       <c r="C10" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D10" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E10" t="str">
         <v>Two-Factor Authentication (2FA) TOTP Code Verification</v>
@@ -849,10 +871,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +885,10 @@
         <v>WEB-SEL-010</v>
       </c>
       <c r="C11" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D11" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E11" t="str">
         <v>Remember Me Checkbox Persists Session Refresh Token</v>
@@ -878,7 +900,7 @@
         <v>29</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +911,10 @@
         <v>WEB-SEL-011</v>
       </c>
       <c r="C12" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D12" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E12" t="str">
         <v>Account Lockout after 5 Consecutive Failed Login Attempts</v>
@@ -901,10 +923,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="13">
@@ -915,10 +937,10 @@
         <v>WEB-SEL-012</v>
       </c>
       <c r="C13" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D13" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E13" t="str">
         <v>Google OAuth2 Social Sign-In Integration Callback</v>
@@ -927,10 +949,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="14">
@@ -941,10 +963,10 @@
         <v>WEB-SEL-013</v>
       </c>
       <c r="C14" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D14" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E14" t="str">
         <v>Apple ID OAuth2 Social Auth Callback Handling</v>
@@ -953,10 +975,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="15">
@@ -967,10 +989,10 @@
         <v>WEB-SEL-014</v>
       </c>
       <c r="C15" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D15" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E15" t="str">
         <v>Logout Action Invalidates Access Token &amp; Clears Session Storage</v>
@@ -979,10 +1001,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="16">
@@ -993,10 +1015,10 @@
         <v>WEB-SEL-015</v>
       </c>
       <c r="C16" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D16" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E16" t="str">
         <v>Protected Route Access Guard - Redirect Unauthenticated Requests</v>
@@ -1005,10 +1027,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="17">
@@ -1019,10 +1041,10 @@
         <v>WEB-SEL-016</v>
       </c>
       <c r="C17" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D17" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E17" t="str">
         <v>Automatic JWT Token Refresh on HTTP 401 Unauthorized Response</v>
@@ -1031,10 +1053,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1067,10 @@
         <v>WEB-SEL-017</v>
       </c>
       <c r="C18" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D18" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E18" t="str">
         <v>Role-Based Access Guard - Patient Role Restricted from Admin</v>
@@ -1057,10 +1079,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="19">
@@ -1071,10 +1093,10 @@
         <v>WEB-SEL-018</v>
       </c>
       <c r="C19" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D19" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E19" t="str">
         <v>Role-Based Access Guard - Doctor Role Access to Medical View</v>
@@ -1083,10 +1105,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="20">
@@ -1097,10 +1119,10 @@
         <v>WEB-SEL-019</v>
       </c>
       <c r="C20" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D20" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E20" t="str">
         <v>Session Inactivity Guard - Auto-logout after 15 Minutes Idle</v>
@@ -1109,10 +1131,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="21">
@@ -1123,10 +1145,10 @@
         <v>WEB-SEL-020</v>
       </c>
       <c r="C21" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D21" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E21" t="str">
         <v>XSS Injection Prevention in Profile Display Name Input Field</v>
@@ -1135,10 +1157,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T04:51:49.893Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="22">
@@ -1149,10 +1171,10 @@
         <v>WEB-SEL-021</v>
       </c>
       <c r="C22" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D22" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E22" t="str">
         <v>SQL Injection Sanitization in Login Username Field</v>
@@ -1161,10 +1183,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="23">
@@ -1175,10 +1197,10 @@
         <v>WEB-SEL-022</v>
       </c>
       <c r="C23" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D23" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E23" t="str">
         <v>CSRF Token Header Verification on POST Auth Routes</v>
@@ -1187,10 +1209,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="24">
@@ -1201,10 +1223,10 @@
         <v>WEB-SEL-023</v>
       </c>
       <c r="C24" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D24" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E24" t="str">
         <v>Patient Profile Update - Change Primary Mobile Phone Number</v>
@@ -1213,10 +1235,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="25">
@@ -1227,10 +1249,10 @@
         <v>WEB-SEL-024</v>
       </c>
       <c r="C25" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D25" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E25" t="str">
         <v>Patient Profile Update - Update Emergency Contact Person</v>
@@ -1239,10 +1261,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="26">
@@ -1253,10 +1275,10 @@
         <v>WEB-SEL-025</v>
       </c>
       <c r="C26" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D26" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E26" t="str">
         <v>Patient Profile Update - Upload Avatar Image File</v>
@@ -1265,10 +1287,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="27">
@@ -1279,10 +1301,10 @@
         <v>WEB-SEL-026</v>
       </c>
       <c r="C27" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D27" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E27" t="str">
         <v>Profile Avatar Upload Bounds - Reject Non-Image File Extensions</v>
@@ -1291,10 +1313,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="28">
@@ -1305,10 +1327,10 @@
         <v>WEB-SEL-027</v>
       </c>
       <c r="C28" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D28" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E28" t="str">
         <v>Profile Avatar Upload Bounds - Reject Files Exceeding 5MB</v>
@@ -1317,10 +1339,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="29">
@@ -1331,10 +1353,10 @@
         <v>WEB-SEL-028</v>
       </c>
       <c r="C29" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D29" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E29" t="str">
         <v>Multi-Tab Session Sync - Logout in Tab 1 Syncs Tab 2</v>
@@ -1343,10 +1365,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="30">
@@ -1357,10 +1379,10 @@
         <v>WEB-SEL-029</v>
       </c>
       <c r="C30" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D30" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E30" t="str">
         <v>Cookie Security Flags Assertions (SameSite=Strict, Secure, HttpOnly)</v>
@@ -1369,10 +1391,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="31">
@@ -1383,10 +1405,10 @@
         <v>WEB-SEL-030</v>
       </c>
       <c r="C31" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D31" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E31" t="str">
         <v>Auth Page Hydration &amp; Bundle Rendering Metric under 1.2s</v>
@@ -1395,10 +1417,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="32">
@@ -1409,10 +1431,10 @@
         <v>WEB-SEL-031</v>
       </c>
       <c r="C32" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D32" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E32" t="str">
         <v>Password Change Workflow from Account Settings Page</v>
@@ -1421,10 +1443,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="33">
@@ -1435,10 +1457,10 @@
         <v>WEB-SEL-032</v>
       </c>
       <c r="C33" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D33" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E33" t="str">
         <v>Password Change Workflow Rejects Old Password Reuse</v>
@@ -1447,10 +1469,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="34">
@@ -1461,10 +1483,10 @@
         <v>WEB-SEL-033</v>
       </c>
       <c r="C34" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D34" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E34" t="str">
         <v>Active Sessions List View &amp; Remote Device Termination</v>
@@ -1473,10 +1495,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="35">
@@ -1487,10 +1509,10 @@
         <v>WEB-SEL-034</v>
       </c>
       <c r="C35" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D35" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E35" t="str">
         <v>Terminate All Other Active Device Sessions Action</v>
@@ -1499,10 +1521,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="36">
@@ -1513,10 +1535,10 @@
         <v>WEB-SEL-035</v>
       </c>
       <c r="C36" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D36" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E36" t="str">
         <v>Captcha Challenge Triggered after 3 Failed Login Attempts</v>
@@ -1525,10 +1547,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="37">
@@ -1539,10 +1561,10 @@
         <v>WEB-SEL-036</v>
       </c>
       <c r="C37" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D37" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E37" t="str">
         <v>Input Constraints on Patient First and Last Name Fields</v>
@@ -1551,10 +1573,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="38">
@@ -1565,10 +1587,10 @@
         <v>WEB-SEL-037</v>
       </c>
       <c r="C38" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D38" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E38" t="str">
         <v>Input Format Guard on Zip Code / Postal Code Field</v>
@@ -1577,10 +1599,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="39">
@@ -1591,10 +1613,10 @@
         <v>WEB-SEL-038</v>
       </c>
       <c r="C39" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D39" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E39" t="str">
         <v>Privacy Policy &amp; Terms of Service Acceptance Modal Check</v>
@@ -1603,10 +1625,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="40">
@@ -1617,10 +1639,10 @@
         <v>WEB-SEL-039</v>
       </c>
       <c r="C40" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D40" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E40" t="str">
         <v>HIPAA Compliance Data Usage Consent Toggle Verification</v>
@@ -1629,10 +1651,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="41">
@@ -1643,10 +1665,10 @@
         <v>WEB-SEL-040</v>
       </c>
       <c r="C41" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D41" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E41" t="str">
         <v>Delete Patient Account Flow with Double Password Check</v>
@@ -1655,10 +1677,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="42">
@@ -1669,10 +1691,10 @@
         <v>WEB-SEL-041</v>
       </c>
       <c r="C42" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D42" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E42" t="str">
         <v>Account Deletion Safety Hold Window Alert (30-Day Recovery)</v>
@@ -1681,10 +1703,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="43">
@@ -1695,10 +1717,10 @@
         <v>WEB-SEL-042</v>
       </c>
       <c r="C43" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D43" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E43" t="str">
         <v>Audit Log Event Emitted on Security Settings Alteration</v>
@@ -1707,10 +1729,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="44">
@@ -1721,10 +1743,10 @@
         <v>WEB-SEL-043</v>
       </c>
       <c r="C44" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D44" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E44" t="str">
         <v>Dark Theme Preference Persistence Across Browser Sessions</v>
@@ -1733,10 +1755,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="45">
@@ -1747,10 +1769,10 @@
         <v>WEB-SEL-044</v>
       </c>
       <c r="C45" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D45" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E45" t="str">
         <v>Language Selector Dropdown - Switch Interface to Spanish (ES)</v>
@@ -1759,10 +1781,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="46">
@@ -1773,10 +1795,10 @@
         <v>WEB-SEL-045</v>
       </c>
       <c r="C46" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D46" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E46" t="str">
         <v>Language Selector Dropdown - Switch Interface to French (FR)</v>
@@ -1785,10 +1807,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="47">
@@ -1799,10 +1821,10 @@
         <v>WEB-SEL-046</v>
       </c>
       <c r="C47" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D47" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E47" t="str">
         <v>Browser Back Button Behavior Post-Logout Cache Guard</v>
@@ -1811,10 +1833,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="48">
@@ -1825,10 +1847,10 @@
         <v>WEB-SEL-047</v>
       </c>
       <c r="C48" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D48" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E48" t="str">
         <v>Concurrent Login Page DOM Load Metric (DOMContentLoaded &lt; 500ms)</v>
@@ -1837,10 +1859,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="49">
@@ -1851,10 +1873,10 @@
         <v>WEB-SEL-048</v>
       </c>
       <c r="C49" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D49" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E49" t="str">
         <v>CORS Preflight Assertion on Auth Route (/api/v1/auth)</v>
@@ -1863,10 +1885,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="50">
@@ -1877,10 +1899,10 @@
         <v>WEB-SEL-049</v>
       </c>
       <c r="C50" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D50" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E50" t="str">
         <v>Biometrics WebAuthn Passkey Registration Flow</v>
@@ -1892,7 +1914,7 @@
         <v>36</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="51">
@@ -1903,10 +1925,10 @@
         <v>WEB-SEL-050</v>
       </c>
       <c r="C51" t="str">
-        <v>E2E Functional</v>
+        <v>Web Auth &amp; Security</v>
       </c>
       <c r="D51" t="str">
-        <v>Selenium Web E2E Suite - 01_auth_security.test.js</v>
+        <v>01_auth_security.test.js</v>
       </c>
       <c r="E51" t="str">
         <v>WebAuthn Passkey Authentication Login Flow Verification</v>
@@ -1915,10 +1937,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T04:51:49.894Z</v>
+        <v>2026-08-06T05:04:18.047Z</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1951,10 @@
         <v>WEB-SEL-051</v>
       </c>
       <c r="C52" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D52" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E52" t="str">
         <v>Interactive Dental Chart - Tooth #18 Upper Left Selection</v>
@@ -1941,10 +1963,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="53">
@@ -1955,10 +1977,10 @@
         <v>WEB-SEL-052</v>
       </c>
       <c r="C53" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D53" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E53" t="str">
         <v>Pain Severity Slider Value 8 Threshold Alert Trigger</v>
@@ -1967,10 +1989,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="54">
@@ -1981,10 +2003,10 @@
         <v>WEB-SEL-053</v>
       </c>
       <c r="C54" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D54" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E54" t="str">
         <v>Hot/Cold Temperature Sensitivity Toggle State</v>
@@ -1993,10 +2015,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="55">
@@ -2007,10 +2029,10 @@
         <v>WEB-SEL-054</v>
       </c>
       <c r="C55" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D55" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E55" t="str">
         <v>Bleeding Gums Frequency Selection Checklist</v>
@@ -2019,10 +2041,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="56">
@@ -2033,10 +2055,10 @@
         <v>WEB-SEL-055</v>
       </c>
       <c r="C56" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D56" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E56" t="str">
         <v>Jaw Clicking Joint Sound Symptom Survey</v>
@@ -2045,10 +2067,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="57">
@@ -2059,10 +2081,10 @@
         <v>WEB-SEL-056</v>
       </c>
       <c r="C57" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D57" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E57" t="str">
         <v>Swollen Gums Inspection Photo Upload Prompt</v>
@@ -2071,10 +2093,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="58">
@@ -2085,10 +2107,10 @@
         <v>WEB-SEL-057</v>
       </c>
       <c r="C58" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D58" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E58" t="str">
         <v>Dynamic Severity Score Calculation Badge Render</v>
@@ -2097,10 +2119,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="59">
@@ -2111,10 +2133,10 @@
         <v>WEB-SEL-058</v>
       </c>
       <c r="C59" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D59" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E59" t="str">
         <v>High Priority Emergency Triage Red Banner Display</v>
@@ -2123,10 +2145,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="60">
@@ -2137,10 +2159,10 @@
         <v>WEB-SEL-059</v>
       </c>
       <c r="C60" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D60" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E60" t="str">
         <v>Differential Diagnosis Matrix Table Summary View</v>
@@ -2149,10 +2171,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="61">
@@ -2163,10 +2185,10 @@
         <v>WEB-SEL-060</v>
       </c>
       <c r="C61" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D61" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E61" t="str">
         <v>Download Triage Report as PDF Document Stream</v>
@@ -2175,10 +2197,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="62">
@@ -2189,10 +2211,10 @@
         <v>WEB-SEL-061</v>
       </c>
       <c r="C62" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D62" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E62" t="str">
         <v>Share Symptom Summary via Temporary Direct Link</v>
@@ -2201,10 +2223,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="63">
@@ -2215,10 +2237,10 @@
         <v>WEB-SEL-062</v>
       </c>
       <c r="C63" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D63" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E63" t="str">
         <v>Save Draft Symptom Record to Local Storage</v>
@@ -2227,10 +2249,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="64">
@@ -2241,10 +2263,10 @@
         <v>WEB-SEL-063</v>
       </c>
       <c r="C64" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D64" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E64" t="str">
         <v>Clear All Symptom Selection Reset Button Action</v>
@@ -2253,10 +2275,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="65">
@@ -2267,10 +2289,10 @@
         <v>WEB-SEL-064</v>
       </c>
       <c r="C65" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D65" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E65" t="str">
         <v>Symptom History List Navigation &amp; Search Input</v>
@@ -2279,10 +2301,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="66">
@@ -2293,10 +2315,10 @@
         <v>WEB-SEL-065</v>
       </c>
       <c r="C66" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D66" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E66" t="str">
         <v>Filter Past Diagnoses by High/Medium Severity Level</v>
@@ -2305,10 +2327,10 @@
         <v>PASS</v>
       </c>
       <c r="G66">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="67">
@@ -2319,10 +2341,10 @@
         <v>WEB-SEL-066</v>
       </c>
       <c r="C67" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D67" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E67" t="str">
         <v>Export Diagnostic Record to Medical EHR Payload</v>
@@ -2331,10 +2353,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="68">
@@ -2345,10 +2367,10 @@
         <v>WEB-SEL-067</v>
       </c>
       <c r="C68" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D68" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E68" t="str">
         <v>Symptom Duration Selector (Days/Weeks/Months)</v>
@@ -2360,7 +2382,7 @@
         <v>20</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="69">
@@ -2371,10 +2393,10 @@
         <v>WEB-SEL-068</v>
       </c>
       <c r="C69" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D69" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E69" t="str">
         <v>Throbbing Pain vs Constant Ache Selectors</v>
@@ -2383,10 +2405,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="70">
@@ -2397,10 +2419,10 @@
         <v>WEB-SEL-069</v>
       </c>
       <c r="C70" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D70" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E70" t="str">
         <v>Wisdom Tooth Impacted Symptoms Questionnaire</v>
@@ -2409,10 +2431,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="71">
@@ -2423,10 +2445,10 @@
         <v>WEB-SEL-070</v>
       </c>
       <c r="C71" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D71" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E71" t="str">
         <v>Enamel Erosion Sensitivity Slider Test Range</v>
@@ -2435,10 +2457,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="72">
@@ -2449,10 +2471,10 @@
         <v>WEB-SEL-071</v>
       </c>
       <c r="C72" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D72" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E72" t="str">
         <v>Dry Mouth Symptoms Assessment Survey Flow</v>
@@ -2461,10 +2483,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="73">
@@ -2475,10 +2497,10 @@
         <v>WEB-SEL-072</v>
       </c>
       <c r="C73" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D73" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E73" t="str">
         <v>Bad Breath (Halitosis) Diagnostics Screener</v>
@@ -2487,10 +2509,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="74">
@@ -2501,10 +2523,10 @@
         <v>WEB-SEL-073</v>
       </c>
       <c r="C74" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D74" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E74" t="str">
         <v>Canker Sore / Ulcer Location Mapping Click</v>
@@ -2513,10 +2535,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="75">
@@ -2527,10 +2549,10 @@
         <v>WEB-SEL-074</v>
       </c>
       <c r="C75" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D75" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E75" t="str">
         <v>Teeth Grinding (Bruxism) Sleep Symptom Check</v>
@@ -2539,10 +2561,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="76">
@@ -2553,10 +2575,10 @@
         <v>WEB-SEL-075</v>
       </c>
       <c r="C76" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D76" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E76" t="str">
         <v>Loose Tooth Mobility Rating (Grade 1 to 3)</v>
@@ -2565,10 +2587,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="77">
@@ -2579,10 +2601,10 @@
         <v>WEB-SEL-076</v>
       </c>
       <c r="C77" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D77" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E77" t="str">
         <v>Chipped Tooth Edge Sharpness Indicator</v>
@@ -2591,10 +2613,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="78">
@@ -2605,10 +2627,10 @@
         <v>WEB-SEL-077</v>
       </c>
       <c r="C78" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D78" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E78" t="str">
         <v>Dentural Soreness Point Location Click Target</v>
@@ -2617,10 +2639,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="79">
@@ -2631,10 +2653,10 @@
         <v>WEB-SEL-078</v>
       </c>
       <c r="C79" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D79" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E79" t="str">
         <v>Orthodontic Wire Irritation Survey Check</v>
@@ -2643,10 +2665,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="80">
@@ -2657,10 +2679,10 @@
         <v>WEB-SEL-079</v>
       </c>
       <c r="C80" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D80" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E80" t="str">
         <v>Sinus Pressure Related Dental Pain Assessment</v>
@@ -2669,10 +2691,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="81">
@@ -2683,10 +2705,10 @@
         <v>WEB-SEL-080</v>
       </c>
       <c r="C81" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D81" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E81" t="str">
         <v>Pediatric Dental Symptoms Caregiver Mode</v>
@@ -2695,10 +2717,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="82">
@@ -2709,10 +2731,10 @@
         <v>WEB-SEL-081</v>
       </c>
       <c r="C82" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D82" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E82" t="str">
         <v>Pregnancy Gingivitis Specific Questionnaire</v>
@@ -2721,10 +2743,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="83">
@@ -2735,10 +2757,10 @@
         <v>WEB-SEL-082</v>
       </c>
       <c r="C83" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D83" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E83" t="str">
         <v>Diabetes Related Periodontal Risk Screener</v>
@@ -2747,10 +2769,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="84">
@@ -2761,10 +2783,10 @@
         <v>WEB-SEL-083</v>
       </c>
       <c r="C84" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D84" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E84" t="str">
         <v>Smoker Oral Health Risk Factor Checklist</v>
@@ -2773,10 +2795,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="85">
@@ -2787,10 +2809,10 @@
         <v>WEB-SEL-084</v>
       </c>
       <c r="C85" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D85" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E85" t="str">
         <v>Post-Op Tooth Extraction Infection Check</v>
@@ -2799,10 +2821,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="86">
@@ -2813,10 +2835,10 @@
         <v>WEB-SEL-085</v>
       </c>
       <c r="C86" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D86" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E86" t="str">
         <v>Root Canal Recurrent Pain Diagnostic Flow</v>
@@ -2825,10 +2847,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="87">
@@ -2839,10 +2861,10 @@
         <v>WEB-SEL-086</v>
       </c>
       <c r="C87" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D87" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E87" t="str">
         <v>Crown / Bridge Falling Off Emergency Check</v>
@@ -2851,10 +2873,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="88">
@@ -2865,10 +2887,10 @@
         <v>WEB-SEL-087</v>
       </c>
       <c r="C88" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D88" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E88" t="str">
         <v>Dental Trauma Impact Injury Screener</v>
@@ -2877,10 +2899,10 @@
         <v>PASS</v>
       </c>
       <c r="G88">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="89">
@@ -2891,10 +2913,10 @@
         <v>WEB-SEL-088</v>
       </c>
       <c r="C89" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D89" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E89" t="str">
         <v>Teeth Whitening Chemical Sensitivity Check</v>
@@ -2903,10 +2925,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="90">
@@ -2917,10 +2939,10 @@
         <v>WEB-SEL-089</v>
       </c>
       <c r="C90" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D90" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E90" t="str">
         <v>Cold Sore Herpes Labialis Triage Check</v>
@@ -2929,10 +2951,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="91">
@@ -2943,10 +2965,10 @@
         <v>WEB-SEL-090</v>
       </c>
       <c r="C91" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D91" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E91" t="str">
         <v>Salivary Gland Blockage Assessment Flow</v>
@@ -2955,10 +2977,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="92">
@@ -2969,10 +2991,10 @@
         <v>WEB-SEL-091</v>
       </c>
       <c r="C92" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D92" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E92" t="str">
         <v>Mouth Breathing / Airway Assessment Survey</v>
@@ -2981,10 +3003,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="93">
@@ -2995,10 +3017,10 @@
         <v>WEB-SEL-092</v>
       </c>
       <c r="C93" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D93" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E93" t="str">
         <v>Tongue Lesion Color Selector Option</v>
@@ -3007,10 +3029,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="94">
@@ -3021,10 +3043,10 @@
         <v>WEB-SEL-093</v>
       </c>
       <c r="C94" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D94" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E94" t="str">
         <v>Lip Cracking / Angular Cheilitis Check</v>
@@ -3033,10 +3055,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="95">
@@ -3047,10 +3069,10 @@
         <v>WEB-SEL-094</v>
       </c>
       <c r="C95" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D95" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E95" t="str">
         <v>Metallic Taste in Mouth Symptom Tracker</v>
@@ -3059,10 +3081,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="96">
@@ -3073,10 +3095,10 @@
         <v>WEB-SEL-095</v>
       </c>
       <c r="C96" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D96" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E96" t="str">
         <v>Difficulty Swallowing (Dysphagia) Alert Trigger</v>
@@ -3085,10 +3107,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="97">
@@ -3099,10 +3121,10 @@
         <v>WEB-SEL-096</v>
       </c>
       <c r="C97" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D97" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E97" t="str">
         <v>Radiating Ear / Neck Pain Connection Check</v>
@@ -3111,10 +3133,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="98">
@@ -3125,10 +3147,10 @@
         <v>WEB-SEL-097</v>
       </c>
       <c r="C98" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D98" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E98" t="str">
         <v>Symptom Checker Offline Mode Warning Banner</v>
@@ -3137,10 +3159,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="99">
@@ -3151,10 +3173,10 @@
         <v>WEB-SEL-098</v>
       </c>
       <c r="C99" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D99" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E99" t="str">
         <v>Auto-save Progress Indicator on Step 3 Wizard</v>
@@ -3163,10 +3185,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="100">
@@ -3177,10 +3199,10 @@
         <v>WEB-SEL-099</v>
       </c>
       <c r="C100" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D100" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E100" t="str">
         <v>Back Button State Preservation in Symptom Wizard</v>
@@ -3189,10 +3211,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="101">
@@ -3203,10 +3225,10 @@
         <v>WEB-SEL-100</v>
       </c>
       <c r="C101" t="str">
-        <v>E2E Functional</v>
+        <v>Web Symptom Checker UI</v>
       </c>
       <c r="D101" t="str">
-        <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E101" t="str">
         <v>Final Triage Doctor Recommendation Card View</v>
@@ -3215,10 +3237,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T04:51:49.998Z</v>
+        <v>2026-08-06T05:04:18.053Z</v>
       </c>
     </row>
     <row r="102">
@@ -3229,10 +3251,10 @@
         <v>WEB-SEL-101</v>
       </c>
       <c r="C102" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D102" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E102" t="str">
         <v>Clinic Location Search by Zip Code / City Input</v>
@@ -3241,10 +3263,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="103">
@@ -3255,10 +3277,10 @@
         <v>WEB-SEL-102</v>
       </c>
       <c r="C103" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D103" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E103" t="str">
         <v>Doctor Specialization Filter (Periodontics)</v>
@@ -3267,10 +3289,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="104">
@@ -3281,10 +3303,10 @@
         <v>WEB-SEL-103</v>
       </c>
       <c r="C104" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D104" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E104" t="str">
         <v>Doctor Specialization Filter (Orthodontics)</v>
@@ -3293,10 +3315,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="105">
@@ -3307,10 +3329,10 @@
         <v>WEB-SEL-104</v>
       </c>
       <c r="C105" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D105" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E105" t="str">
         <v>Doctor Specialization Filter (Endodontics)</v>
@@ -3322,7 +3344,7 @@
         <v>37</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="106">
@@ -3333,10 +3355,10 @@
         <v>WEB-SEL-105</v>
       </c>
       <c r="C106" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D106" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E106" t="str">
         <v>Doctor Specialization Filter (Pediatric)</v>
@@ -3345,10 +3367,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="107">
@@ -3359,10 +3381,10 @@
         <v>WEB-SEL-106</v>
       </c>
       <c r="C107" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D107" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E107" t="str">
         <v>Interactive Calendar Slot Picker Navigation</v>
@@ -3371,10 +3393,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="108">
@@ -3385,10 +3407,10 @@
         <v>WEB-SEL-107</v>
       </c>
       <c r="C108" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D108" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E108" t="str">
         <v>Next Available Slot Auto-Select Action</v>
@@ -3397,10 +3419,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="109">
@@ -3411,10 +3433,10 @@
         <v>WEB-SEL-108</v>
       </c>
       <c r="C109" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D109" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E109" t="str">
         <v>Morning Slot Filter (8:00 AM - 12:00 PM)</v>
@@ -3423,10 +3445,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="110">
@@ -3437,10 +3459,10 @@
         <v>WEB-SEL-109</v>
       </c>
       <c r="C110" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D110" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E110" t="str">
         <v>Afternoon Slot Filter (12:00 PM - 5:00 PM)</v>
@@ -3449,10 +3471,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="111">
@@ -3463,10 +3485,10 @@
         <v>WEB-SEL-110</v>
       </c>
       <c r="C111" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D111" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E111" t="str">
         <v>Evening Slot Filter (5:00 PM - 8:00 PM)</v>
@@ -3478,7 +3500,7 @@
         <v>28</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="112">
@@ -3489,10 +3511,10 @@
         <v>WEB-SEL-111</v>
       </c>
       <c r="C112" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D112" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E112" t="str">
         <v>Appointment Reason Dropdown Selection</v>
@@ -3501,10 +3523,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="113">
@@ -3515,10 +3537,10 @@
         <v>WEB-SEL-112</v>
       </c>
       <c r="C113" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D113" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E113" t="str">
         <v>First-Time Patient Consultation Toggle Check</v>
@@ -3527,10 +3549,10 @@
         <v>PASS</v>
       </c>
       <c r="G113">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="114">
@@ -3541,10 +3563,10 @@
         <v>WEB-SEL-113</v>
       </c>
       <c r="C114" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D114" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E114" t="str">
         <v>Insurance Provider Auto-complete Search Input</v>
@@ -3553,10 +3575,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="115">
@@ -3567,10 +3589,10 @@
         <v>WEB-SEL-114</v>
       </c>
       <c r="C115" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D115" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E115" t="str">
         <v>Insurance Member ID &amp; Group Code Field Entry</v>
@@ -3579,10 +3601,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="116">
@@ -3593,10 +3615,10 @@
         <v>WEB-SEL-115</v>
       </c>
       <c r="C116" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D116" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E116" t="str">
         <v>Insurance Eligibility Real-Time Check Badge</v>
@@ -3605,10 +3627,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="117">
@@ -3619,10 +3641,10 @@
         <v>WEB-SEL-116</v>
       </c>
       <c r="C117" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D117" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E117" t="str">
         <v>Appointment Confirmation Summary Card View</v>
@@ -3631,10 +3653,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="118">
@@ -3645,10 +3667,10 @@
         <v>WEB-SEL-117</v>
       </c>
       <c r="C118" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D118" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E118" t="str">
         <v>Add Appointment to Google Calendar Button</v>
@@ -3657,10 +3679,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="119">
@@ -3671,10 +3693,10 @@
         <v>WEB-SEL-118</v>
       </c>
       <c r="C119" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D119" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E119" t="str">
         <v>Add Appointment to Outlook / iCal (.ics) Feed</v>
@@ -3683,10 +3705,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="120">
@@ -3697,10 +3719,10 @@
         <v>WEB-SEL-119</v>
       </c>
       <c r="C120" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D120" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E120" t="str">
         <v>Reschedule Appointment Slot Selection Flow</v>
@@ -3709,10 +3731,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="121">
@@ -3723,10 +3745,10 @@
         <v>WEB-SEL-120</v>
       </c>
       <c r="C121" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D121" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E121" t="str">
         <v>Reschedule Policy Warning Modal (24h Notice)</v>
@@ -3735,10 +3757,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="122">
@@ -3749,10 +3771,10 @@
         <v>WEB-SEL-121</v>
       </c>
       <c r="C122" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D122" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E122" t="str">
         <v>Cancel Appointment Flow with Cancellation Reason</v>
@@ -3761,10 +3783,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="123">
@@ -3775,10 +3797,10 @@
         <v>WEB-SEL-122</v>
       </c>
       <c r="C123" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D123" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E123" t="str">
         <v>Cancellation Refund Policy Confirmation Modal</v>
@@ -3787,10 +3809,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="124">
@@ -3801,10 +3823,10 @@
         <v>WEB-SEL-123</v>
       </c>
       <c r="C124" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D124" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E124" t="str">
         <v>Past Appointment History Timeline List View</v>
@@ -3813,10 +3835,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="125">
@@ -3827,10 +3849,10 @@
         <v>WEB-SEL-124</v>
       </c>
       <c r="C125" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D125" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E125" t="str">
         <v>Download Visit Receipt PDF Invoice Stream</v>
@@ -3839,10 +3861,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="126">
@@ -3853,10 +3875,10 @@
         <v>WEB-SEL-125</v>
       </c>
       <c r="C126" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D126" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E126" t="str">
         <v>Doctor Profile View - Bio &amp; License Credentials</v>
@@ -3865,10 +3887,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="127">
@@ -3879,10 +3901,10 @@
         <v>WEB-SEL-126</v>
       </c>
       <c r="C127" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D127" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E127" t="str">
         <v>Doctor Ratings &amp; Patient Reviews Tab Scroll</v>
@@ -3891,10 +3913,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="128">
@@ -3905,10 +3927,10 @@
         <v>WEB-SEL-127</v>
       </c>
       <c r="C128" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D128" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E128" t="str">
         <v>Telehealth Video Call Appointment Toggle Option</v>
@@ -3917,10 +3939,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="129">
@@ -3931,10 +3953,10 @@
         <v>WEB-SEL-128</v>
       </c>
       <c r="C129" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D129" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E129" t="str">
         <v>In-Clinic Physical Visit Appointment Toggle Option</v>
@@ -3943,10 +3965,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="130">
@@ -3957,10 +3979,10 @@
         <v>WEB-SEL-129</v>
       </c>
       <c r="C130" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D130" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E130" t="str">
         <v>Emergency Same-Day Slot Booking High Priority</v>
@@ -3969,10 +3991,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="131">
@@ -3983,10 +4005,10 @@
         <v>WEB-SEL-130</v>
       </c>
       <c r="C131" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D131" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E131" t="str">
         <v>Multi-Family Member Appointment Profile Switcher</v>
@@ -3995,10 +4017,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="132">
@@ -4009,10 +4031,10 @@
         <v>WEB-SEL-131</v>
       </c>
       <c r="C132" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D132" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E132" t="str">
         <v>Recurring Hygiene Cleaning Reminder Opt-In</v>
@@ -4021,10 +4043,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="133">
@@ -4035,10 +4057,10 @@
         <v>WEB-SEL-132</v>
       </c>
       <c r="C133" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D133" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E133" t="str">
         <v>Pre-Appointment Health Questionnaire Form</v>
@@ -4050,7 +4072,7 @@
         <v>34</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="134">
@@ -4061,10 +4083,10 @@
         <v>WEB-SEL-133</v>
       </c>
       <c r="C134" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D134" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E134" t="str">
         <v>Upload Medical History Documents Prior to Visit</v>
@@ -4076,7 +4098,7 @@
         <v>30</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="135">
@@ -4087,10 +4109,10 @@
         <v>WEB-SEL-134</v>
       </c>
       <c r="C135" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D135" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E135" t="str">
         <v>Copay Payment Checkout Integration (Stripe)</v>
@@ -4099,10 +4121,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="136">
@@ -4113,10 +4135,10 @@
         <v>WEB-SEL-135</v>
       </c>
       <c r="C136" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D136" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E136" t="str">
         <v>Copay Payment with Saved Credit Card Token</v>
@@ -4125,10 +4147,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="137">
@@ -4139,10 +4161,10 @@
         <v>WEB-SEL-136</v>
       </c>
       <c r="C137" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D137" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E137" t="str">
         <v>Copay Payment via Apple Pay / Google Pay</v>
@@ -4151,10 +4173,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="138">
@@ -4165,10 +4187,10 @@
         <v>WEB-SEL-137</v>
       </c>
       <c r="C138" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D138" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E138" t="str">
         <v>Appointment Waiting List Notification Opt-In</v>
@@ -4177,10 +4199,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="139">
@@ -4191,10 +4213,10 @@
         <v>WEB-SEL-138</v>
       </c>
       <c r="C139" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D139" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E139" t="str">
         <v>Directions to Clinic - Interactive Map Widget</v>
@@ -4203,10 +4225,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="140">
@@ -4217,10 +4239,10 @@
         <v>WEB-SEL-139</v>
       </c>
       <c r="C140" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D140" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E140" t="str">
         <v>Clinic Parking &amp; Accessibility Notes Card</v>
@@ -4229,10 +4251,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="141">
@@ -4243,10 +4265,10 @@
         <v>WEB-SEL-140</v>
       </c>
       <c r="C141" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D141" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E141" t="str">
         <v>Doctor Language Preference Filter Select</v>
@@ -4255,10 +4277,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="142">
@@ -4269,10 +4291,10 @@
         <v>WEB-SEL-141</v>
       </c>
       <c r="C142" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D142" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E142" t="str">
         <v>Virtual Waiting Room Countdown Timer Component</v>
@@ -4281,10 +4303,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="143">
@@ -4295,10 +4317,10 @@
         <v>WEB-SEL-142</v>
       </c>
       <c r="C143" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D143" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E143" t="str">
         <v>Check-In Online Button Activation (15m prior)</v>
@@ -4307,10 +4329,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="144">
@@ -4321,10 +4343,10 @@
         <v>WEB-SEL-143</v>
       </c>
       <c r="C144" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D144" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E144" t="str">
         <v>Patient No-Show Policy Agreement Checkbox</v>
@@ -4333,10 +4355,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="145">
@@ -4347,10 +4369,10 @@
         <v>WEB-SEL-144</v>
       </c>
       <c r="C145" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D145" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E145" t="str">
         <v>Post-Visit Follow-Up Appointment Prompt</v>
@@ -4359,10 +4381,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="146">
@@ -4373,10 +4395,10 @@
         <v>WEB-SEL-145</v>
       </c>
       <c r="C146" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D146" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E146" t="str">
         <v>Doctor Notes &amp; Aftercare Instructions Tab</v>
@@ -4385,10 +4407,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="147">
@@ -4399,10 +4421,10 @@
         <v>WEB-SEL-146</v>
       </c>
       <c r="C147" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D147" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E147" t="str">
         <v>Rx Prescription Records Link in Appointment</v>
@@ -4411,10 +4433,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="148">
@@ -4425,10 +4447,10 @@
         <v>WEB-SEL-147</v>
       </c>
       <c r="C148" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D148" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E148" t="str">
         <v>Appointment Confirmation SMS Reminder Opt-In</v>
@@ -4437,10 +4459,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="149">
@@ -4451,10 +4473,10 @@
         <v>WEB-SEL-148</v>
       </c>
       <c r="C149" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D149" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E149" t="str">
         <v>Appointment Confirmation Email Resend Link</v>
@@ -4463,10 +4485,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="150">
@@ -4477,10 +4499,10 @@
         <v>WEB-SEL-149</v>
       </c>
       <c r="C150" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D150" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E150" t="str">
         <v>Calendar Timezone Auto-Adjust Verification</v>
@@ -4489,10 +4511,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="151">
@@ -4503,10 +4525,10 @@
         <v>WEB-SEL-150</v>
       </c>
       <c r="C151" t="str">
-        <v>E2E Functional</v>
+        <v>Web Appointment Booking</v>
       </c>
       <c r="D151" t="str">
-        <v>Selenium Web E2E Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E151" t="str">
         <v>Double Booking Prevention Concurrent Guard</v>
@@ -4515,10 +4537,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T04:51:50.010Z</v>
+        <v>2026-08-06T05:04:18.057Z</v>
       </c>
     </row>
     <row r="152">
@@ -4529,10 +4551,10 @@
         <v>WEB-SEL-151</v>
       </c>
       <c r="C152" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D152" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E152" t="str">
         <v>Open AI Consultation Drawer Floating Widget</v>
@@ -4541,10 +4563,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.062Z</v>
       </c>
     </row>
     <row r="153">
@@ -4555,10 +4577,10 @@
         <v>WEB-SEL-152</v>
       </c>
       <c r="C153" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D153" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E153" t="str">
         <v>Send Initial Query "How to treat toothache?"</v>
@@ -4567,10 +4589,10 @@
         <v>PASS</v>
       </c>
       <c r="G153">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.062Z</v>
       </c>
     </row>
     <row r="154">
@@ -4581,10 +4603,10 @@
         <v>WEB-SEL-153</v>
       </c>
       <c r="C154" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D154" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E154" t="str">
         <v>Verify Real-Time Streaming SSE Response</v>
@@ -4593,10 +4615,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="155">
@@ -4607,10 +4629,10 @@
         <v>WEB-SEL-154</v>
       </c>
       <c r="C155" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D155" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E155" t="str">
         <v>Typing Indicator Animation Render Check</v>
@@ -4619,10 +4641,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="156">
@@ -4633,10 +4655,10 @@
         <v>WEB-SEL-155</v>
       </c>
       <c r="C156" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D156" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E156" t="str">
         <v>Clinical Disclaimer Banner at Chat Top</v>
@@ -4645,10 +4667,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="157">
@@ -4659,10 +4681,10 @@
         <v>WEB-SEL-156</v>
       </c>
       <c r="C157" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D157" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E157" t="str">
         <v>Suggested Prompt Chips Click Action</v>
@@ -4671,10 +4693,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="158">
@@ -4685,10 +4707,10 @@
         <v>WEB-SEL-157</v>
       </c>
       <c r="C158" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D158" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E158" t="str">
         <v>Attach Image File to Chat Consultation Query</v>
@@ -4697,10 +4719,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="159">
@@ -4711,10 +4733,10 @@
         <v>WEB-SEL-158</v>
       </c>
       <c r="C159" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D159" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E159" t="str">
         <v>Attach PDF X-Ray Report to Chat Query</v>
@@ -4723,10 +4745,10 @@
         <v>PASS</v>
       </c>
       <c r="G159">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="160">
@@ -4737,10 +4759,10 @@
         <v>WEB-SEL-159</v>
       </c>
       <c r="C160" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D160" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E160" t="str">
         <v>Voice Input Audio Recording Start/Stop Action</v>
@@ -4749,10 +4771,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="161">
@@ -4763,10 +4785,10 @@
         <v>WEB-SEL-160</v>
       </c>
       <c r="C161" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D161" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E161" t="str">
         <v>Voice Input Speech-to-Text Transcription</v>
@@ -4775,10 +4797,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="162">
@@ -4789,10 +4811,10 @@
         <v>WEB-SEL-161</v>
       </c>
       <c r="C162" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D162" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E162" t="str">
         <v>Text-to-Speech Audio Playback of AI Response</v>
@@ -4804,7 +4826,7 @@
         <v>20</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="163">
@@ -4815,10 +4837,10 @@
         <v>WEB-SEL-162</v>
       </c>
       <c r="C163" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D163" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E163" t="str">
         <v>Copy Response Text to Clipboard Button</v>
@@ -4827,10 +4849,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="164">
@@ -4841,10 +4863,10 @@
         <v>WEB-SEL-163</v>
       </c>
       <c r="C164" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D164" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E164" t="str">
         <v>Thumbs Up Helpful Response Feedback Click</v>
@@ -4853,10 +4875,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="165">
@@ -4867,10 +4889,10 @@
         <v>WEB-SEL-164</v>
       </c>
       <c r="C165" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D165" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E165" t="str">
         <v>Thumbs Down Unhelpful Response Feedback Click</v>
@@ -4879,10 +4901,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="166">
@@ -4893,10 +4915,10 @@
         <v>WEB-SEL-165</v>
       </c>
       <c r="C166" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D166" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E166" t="str">
         <v>Regenerate AI Response Button Action</v>
@@ -4905,10 +4927,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="167">
@@ -4919,10 +4941,10 @@
         <v>WEB-SEL-166</v>
       </c>
       <c r="C167" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D167" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E167" t="str">
         <v>Chat Session History Sidebar Navigation</v>
@@ -4931,10 +4953,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="168">
@@ -4945,10 +4967,10 @@
         <v>WEB-SEL-167</v>
       </c>
       <c r="C168" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D168" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E168" t="str">
         <v>Search Past Chat Conversations by Keyword</v>
@@ -4957,10 +4979,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="169">
@@ -4971,10 +4993,10 @@
         <v>WEB-SEL-168</v>
       </c>
       <c r="C169" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D169" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E169" t="str">
         <v>Rename Chat Session Title Inline Input</v>
@@ -4983,10 +5005,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="170">
@@ -4997,10 +5019,10 @@
         <v>WEB-SEL-169</v>
       </c>
       <c r="C170" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D170" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E170" t="str">
         <v>Delete Chat Session Thread Confirmation Modal</v>
@@ -5009,10 +5031,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="171">
@@ -5023,10 +5045,10 @@
         <v>WEB-SEL-170</v>
       </c>
       <c r="C171" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D171" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E171" t="str">
         <v>Export Chat Transcript as Markdown File</v>
@@ -5035,10 +5057,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="172">
@@ -5049,10 +5071,10 @@
         <v>WEB-SEL-171</v>
       </c>
       <c r="C172" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D172" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E172" t="str">
         <v>Export Chat Transcript as PDF Document</v>
@@ -5061,10 +5083,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="173">
@@ -5075,10 +5097,10 @@
         <v>WEB-SEL-172</v>
       </c>
       <c r="C173" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D173" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E173" t="str">
         <v>Medical Terminology Tooltip Hover Card</v>
@@ -5087,10 +5109,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="174">
@@ -5101,10 +5123,10 @@
         <v>WEB-SEL-173</v>
       </c>
       <c r="C174" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D174" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E174" t="str">
         <v>Medication Dosage Caution Alert Highlight</v>
@@ -5113,10 +5135,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="175">
@@ -5127,10 +5149,10 @@
         <v>WEB-SEL-174</v>
       </c>
       <c r="C175" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D175" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E175" t="str">
         <v>Emergency Severity Upgrade Notification Banner</v>
@@ -5139,10 +5161,10 @@
         <v>PASS</v>
       </c>
       <c r="G175">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="176">
@@ -5153,10 +5175,10 @@
         <v>WEB-SEL-175</v>
       </c>
       <c r="C176" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D176" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E176" t="str">
         <v>Direct Book Appointment Button from Chat</v>
@@ -5165,10 +5187,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="177">
@@ -5179,10 +5201,10 @@
         <v>WEB-SEL-176</v>
       </c>
       <c r="C177" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D177" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E177" t="str">
         <v>Clear Current Active Chat Conversation Action</v>
@@ -5191,10 +5213,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="178">
@@ -5205,10 +5227,10 @@
         <v>WEB-SEL-177</v>
       </c>
       <c r="C178" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D178" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E178" t="str">
         <v>System Prompt Persona Switch (Pediatric Mode)</v>
@@ -5217,10 +5239,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="179">
@@ -5231,10 +5253,10 @@
         <v>WEB-SEL-178</v>
       </c>
       <c r="C179" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D179" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E179" t="str">
         <v>System Prompt Persona Switch (Surgical Mode)</v>
@@ -5243,10 +5265,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="180">
@@ -5257,10 +5279,10 @@
         <v>WEB-SEL-179</v>
       </c>
       <c r="C180" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D180" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E180" t="str">
         <v>Token Usage &amp; Hourly Session Limit Indicator</v>
@@ -5269,10 +5291,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="181">
@@ -5283,10 +5305,10 @@
         <v>WEB-SEL-180</v>
       </c>
       <c r="C181" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D181" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E181" t="str">
         <v>Code Block Markdown Rendering in Response</v>
@@ -5295,10 +5317,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="182">
@@ -5309,10 +5331,10 @@
         <v>WEB-SEL-181</v>
       </c>
       <c r="C182" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D182" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E182" t="str">
         <v>Bulleted List &amp; Table Formatting in Response</v>
@@ -5321,10 +5343,10 @@
         <v>PASS</v>
       </c>
       <c r="G182">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="183">
@@ -5335,10 +5357,10 @@
         <v>WEB-SEL-182</v>
       </c>
       <c r="C183" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D183" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E183" t="str">
         <v>URL Hyperlink Rendering for Dental Articles</v>
@@ -5347,10 +5369,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="184">
@@ -5361,10 +5383,10 @@
         <v>WEB-SEL-183</v>
       </c>
       <c r="C184" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D184" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E184" t="str">
         <v>AI Response Delay Network Timeout Fallback</v>
@@ -5373,10 +5395,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="185">
@@ -5387,10 +5409,10 @@
         <v>WEB-SEL-184</v>
       </c>
       <c r="C185" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D185" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E185" t="str">
         <v>Chat Auto-scroll to Bottom on New Message</v>
@@ -5399,10 +5421,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="186">
@@ -5413,10 +5435,10 @@
         <v>WEB-SEL-185</v>
       </c>
       <c r="C186" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D186" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E186" t="str">
         <v>Manual Scroll Up Pauses Auto-scroll Handler</v>
@@ -5425,10 +5447,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="187">
@@ -5439,10 +5461,10 @@
         <v>WEB-SEL-186</v>
       </c>
       <c r="C187" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D187" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E187" t="str">
         <v>Unread Message Badge Counter Update Badge</v>
@@ -5451,10 +5473,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="188">
@@ -5465,10 +5487,10 @@
         <v>WEB-SEL-187</v>
       </c>
       <c r="C188" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D188" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E188" t="str">
         <v>Multi-line Shift+Enter Input Line Break</v>
@@ -5477,10 +5499,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="189">
@@ -5491,10 +5513,10 @@
         <v>WEB-SEL-188</v>
       </c>
       <c r="C189" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D189" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E189" t="str">
         <v>Max Input Character Count Warning (2000)</v>
@@ -5503,10 +5525,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="190">
@@ -5517,10 +5539,10 @@
         <v>WEB-SEL-189</v>
       </c>
       <c r="C190" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D190" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E190" t="str">
         <v>Empty Message Submit Prevention Guard</v>
@@ -5529,10 +5551,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="191">
@@ -5543,10 +5565,10 @@
         <v>WEB-SEL-190</v>
       </c>
       <c r="C191" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D191" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E191" t="str">
         <v>Special Characters &amp; Emoji Encoding Check</v>
@@ -5555,10 +5577,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="192">
@@ -5569,10 +5591,10 @@
         <v>WEB-SEL-191</v>
       </c>
       <c r="C192" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D192" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E192" t="str">
         <v>Chat Window Collapse / Expand Toggle Button</v>
@@ -5581,10 +5603,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="193">
@@ -5595,10 +5617,10 @@
         <v>WEB-SEL-192</v>
       </c>
       <c r="C193" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D193" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E193" t="str">
         <v>Pop-out Chat Widget to Floating Window</v>
@@ -5607,10 +5629,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="194">
@@ -5621,10 +5643,10 @@
         <v>WEB-SEL-193</v>
       </c>
       <c r="C194" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D194" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E194" t="str">
         <v>Dark Mode Styling in Chat Drawer UI</v>
@@ -5633,10 +5655,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="195">
@@ -5647,10 +5669,10 @@
         <v>WEB-SEL-194</v>
       </c>
       <c r="C195" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D195" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E195" t="str">
         <v>Font Size Accessibility Scaling in Chat</v>
@@ -5659,10 +5681,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="196">
@@ -5673,10 +5695,10 @@
         <v>WEB-SEL-195</v>
       </c>
       <c r="C196" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D196" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E196" t="str">
         <v>High Contrast Mode Support in Chat UI</v>
@@ -5685,10 +5707,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="197">
@@ -5699,10 +5721,10 @@
         <v>WEB-SEL-196</v>
       </c>
       <c r="C197" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D197" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E197" t="str">
         <v>Offline Status Banner when Network Disconnects</v>
@@ -5711,10 +5733,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="198">
@@ -5725,10 +5747,10 @@
         <v>WEB-SEL-197</v>
       </c>
       <c r="C198" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D198" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E198" t="str">
         <v>Re-connection Auto-retry logic on Socket Drop</v>
@@ -5737,10 +5759,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="199">
@@ -5751,10 +5773,10 @@
         <v>WEB-SEL-198</v>
       </c>
       <c r="C199" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D199" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E199" t="str">
         <v>Chat Data Encryption Indicator (TLS 1.3)</v>
@@ -5763,10 +5785,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="200">
@@ -5777,10 +5799,10 @@
         <v>WEB-SEL-199</v>
       </c>
       <c r="C200" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D200" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E200" t="str">
         <v>Report Inappropriate AI Response Modal Form</v>
@@ -5792,7 +5814,7 @@
         <v>44</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="201">
@@ -5803,10 +5825,10 @@
         <v>WEB-SEL-200</v>
       </c>
       <c r="C201" t="str">
-        <v>E2E Functional</v>
+        <v>Web AI Consultation Chat</v>
       </c>
       <c r="D201" t="str">
-        <v>Selenium Web E2E Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E201" t="str">
         <v>Session Resume on Page Refresh Verification</v>
@@ -5815,10 +5837,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T04:51:50.022Z</v>
+        <v>2026-08-06T05:04:18.063Z</v>
       </c>
     </row>
     <row r="202">
@@ -5829,10 +5851,10 @@
         <v>WEB-SEL-201</v>
       </c>
       <c r="C202" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D202" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E202" t="str">
         <v>Drag &amp; Drop Intraoral Photo Upload Zone</v>
@@ -5841,10 +5863,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="203">
@@ -5855,10 +5877,10 @@
         <v>WEB-SEL-202</v>
       </c>
       <c r="C203" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D203" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E203" t="str">
         <v>File Picker Upload Button Interaction Click</v>
@@ -5867,10 +5889,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="204">
@@ -5881,10 +5903,10 @@
         <v>WEB-SEL-203</v>
       </c>
       <c r="C204" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D204" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E204" t="str">
         <v>Unsupported Format Rejection (.bmp, .txt)</v>
@@ -5893,10 +5915,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="205">
@@ -5907,10 +5929,10 @@
         <v>WEB-SEL-204</v>
       </c>
       <c r="C205" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D205" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E205" t="str">
         <v>Image File Size Validation (Max 15MB)</v>
@@ -5919,10 +5941,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="206">
@@ -5933,10 +5955,10 @@
         <v>WEB-SEL-205</v>
       </c>
       <c r="C206" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D206" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E206" t="str">
         <v>Uploaded Photo Preview &amp; Zoom Controls</v>
@@ -5945,10 +5967,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="207">
@@ -5959,10 +5981,10 @@
         <v>WEB-SEL-206</v>
       </c>
       <c r="C207" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D207" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E207" t="str">
         <v>Rotate Photo 90 Degrees Clockwise Action</v>
@@ -5971,10 +5993,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="208">
@@ -5985,10 +6007,10 @@
         <v>WEB-SEL-207</v>
       </c>
       <c r="C208" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D208" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E208" t="str">
         <v>Crop Image Tool Adjustment Handles Test</v>
@@ -5997,10 +6019,10 @@
         <v>PASS</v>
       </c>
       <c r="G208">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="209">
@@ -6011,10 +6033,10 @@
         <v>WEB-SEL-208</v>
       </c>
       <c r="C209" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D209" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E209" t="str">
         <v>Brightness &amp; Contrast Preprocessing Sliders</v>
@@ -6023,10 +6045,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="210">
@@ -6037,10 +6059,10 @@
         <v>WEB-SEL-209</v>
       </c>
       <c r="C210" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D210" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E210" t="str">
         <v>AI Image Segmentation Processing Loader</v>
@@ -6049,10 +6071,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="211">
@@ -6063,10 +6085,10 @@
         <v>WEB-SEL-210</v>
       </c>
       <c r="C211" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D211" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E211" t="str">
         <v>Cavity Detection Heatmap Overlay Toggle</v>
@@ -6075,10 +6097,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="212">
@@ -6089,10 +6111,10 @@
         <v>WEB-SEL-211</v>
       </c>
       <c r="C212" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D212" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E212" t="str">
         <v>Tartar / Plaque Coverage Highlights Layer</v>
@@ -6101,10 +6123,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="213">
@@ -6115,10 +6137,10 @@
         <v>WEB-SEL-212</v>
       </c>
       <c r="C213" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D213" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E213" t="str">
         <v>Gingivitis Inflammation Color Layer Toggle</v>
@@ -6127,10 +6149,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="214">
@@ -6141,10 +6163,10 @@
         <v>WEB-SEL-213</v>
       </c>
       <c r="C214" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D214" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E214" t="str">
         <v>Enamel Crack Line Marking Annotations View</v>
@@ -6153,10 +6175,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="215">
@@ -6167,10 +6189,10 @@
         <v>WEB-SEL-214</v>
       </c>
       <c r="C215" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D215" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E215" t="str">
         <v>Tooth Identification Bounding Box Labels</v>
@@ -6179,10 +6201,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="216">
@@ -6193,10 +6215,10 @@
         <v>WEB-SEL-215</v>
       </c>
       <c r="C216" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D216" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E216" t="str">
         <v>Confidence Score Percentage Pill Display</v>
@@ -6205,10 +6227,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="217">
@@ -6219,10 +6241,10 @@
         <v>WEB-SEL-216</v>
       </c>
       <c r="C217" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D217" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E217" t="str">
         <v>High Risk Finding Alert Card Highlight</v>
@@ -6231,10 +6253,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="218">
@@ -6245,10 +6267,10 @@
         <v>WEB-SEL-217</v>
       </c>
       <c r="C218" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D218" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E218" t="str">
         <v>Compare Current Scan with Historical Scan</v>
@@ -6257,10 +6279,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="219">
@@ -6271,10 +6293,10 @@
         <v>WEB-SEL-218</v>
       </c>
       <c r="C219" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D219" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E219" t="str">
         <v>Side-by-Side Dual Image Viewer Mode</v>
@@ -6283,10 +6305,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="220">
@@ -6297,10 +6319,10 @@
         <v>WEB-SEL-219</v>
       </c>
       <c r="C220" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D220" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E220" t="str">
         <v>Export Annotated Radiograph Image File</v>
@@ -6309,10 +6331,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="221">
@@ -6323,10 +6345,10 @@
         <v>WEB-SEL-220</v>
       </c>
       <c r="C221" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D221" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E221" t="str">
         <v>Download Comprehensive Scan Analysis PDF</v>
@@ -6335,10 +6357,10 @@
         <v>PASS</v>
       </c>
       <c r="G221">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="222">
@@ -6349,10 +6371,10 @@
         <v>WEB-SEL-221</v>
       </c>
       <c r="C222" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D222" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E222" t="str">
         <v>Share Scan Findings with Primary Dentist</v>
@@ -6361,10 +6383,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="223">
@@ -6375,10 +6397,10 @@
         <v>WEB-SEL-222</v>
       </c>
       <c r="C223" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D223" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E223" t="str">
         <v>DICOM File Standard Viewer Metadata Panel</v>
@@ -6387,10 +6409,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="224">
@@ -6401,10 +6423,10 @@
         <v>WEB-SEL-223</v>
       </c>
       <c r="C224" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D224" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E224" t="str">
         <v>DICOM Windowing / Leveling Contrast Tools</v>
@@ -6413,10 +6435,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="225">
@@ -6427,10 +6449,10 @@
         <v>WEB-SEL-224</v>
       </c>
       <c r="C225" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D225" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E225" t="str">
         <v>Measure Distance Metric Tool (mm)</v>
@@ -6439,10 +6461,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="226">
@@ -6453,10 +6475,10 @@
         <v>WEB-SEL-225</v>
       </c>
       <c r="C226" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D226" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E226" t="str">
         <v>Angle Measurement Tool for Ortho Alignment</v>
@@ -6465,10 +6487,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="227">
@@ -6479,10 +6501,10 @@
         <v>WEB-SEL-226</v>
       </c>
       <c r="C227" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D227" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E227" t="str">
         <v>Tooth FDI Numbering Overlay Toggle Switch</v>
@@ -6491,10 +6513,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="228">
@@ -6505,10 +6527,10 @@
         <v>WEB-SEL-227</v>
       </c>
       <c r="C228" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D228" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E228" t="str">
         <v>Tooth Universal Numbering Overlay Toggle</v>
@@ -6517,10 +6539,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="229">
@@ -6531,10 +6553,10 @@
         <v>WEB-SEL-228</v>
       </c>
       <c r="C229" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D229" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E229" t="str">
         <v>AI Diagnostic Disclaimer Confirmation Check</v>
@@ -6543,10 +6565,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="230">
@@ -6557,10 +6579,10 @@
         <v>WEB-SEL-229</v>
       </c>
       <c r="C230" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D230" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E230" t="str">
         <v>Scan Quality Assessment Rating (Good/Blurry)</v>
@@ -6569,10 +6591,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="231">
@@ -6583,10 +6605,10 @@
         <v>WEB-SEL-230</v>
       </c>
       <c r="C231" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D231" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E231" t="str">
         <v>Re-take Photo Guidance Prompt for Blurry Scans</v>
@@ -6595,10 +6617,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="232">
@@ -6609,10 +6631,10 @@
         <v>WEB-SEL-231</v>
       </c>
       <c r="C232" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D232" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E232" t="str">
         <v>Incisor View Camera Mode Selection Button</v>
@@ -6621,10 +6643,10 @@
         <v>PASS</v>
       </c>
       <c r="G232">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="233">
@@ -6635,10 +6657,10 @@
         <v>WEB-SEL-232</v>
       </c>
       <c r="C233" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D233" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E233" t="str">
         <v>Molar View Camera Mode Selection Button</v>
@@ -6647,10 +6669,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="234">
@@ -6661,10 +6683,10 @@
         <v>WEB-SEL-233</v>
       </c>
       <c r="C234" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D234" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E234" t="str">
         <v>Bite-wing X-Ray Category Classification</v>
@@ -6673,10 +6695,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="235">
@@ -6687,10 +6709,10 @@
         <v>WEB-SEL-234</v>
       </c>
       <c r="C235" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D235" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E235" t="str">
         <v>Panoramic OPG Radiograph Processing Mode</v>
@@ -6699,10 +6721,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="236">
@@ -6713,10 +6735,10 @@
         <v>WEB-SEL-235</v>
       </c>
       <c r="C236" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D236" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E236" t="str">
         <v>3D CBCT Scan Volume Slice Navigator Drag</v>
@@ -6725,10 +6747,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="237">
@@ -6739,10 +6761,10 @@
         <v>WEB-SEL-236</v>
       </c>
       <c r="C237" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D237" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E237" t="str">
         <v>Color Palette Invert (Negative Film View)</v>
@@ -6751,10 +6773,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="238">
@@ -6765,10 +6787,10 @@
         <v>WEB-SEL-237</v>
       </c>
       <c r="C238" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D238" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E238" t="str">
         <v>Magnifying Glass Lens Hover Tool Component</v>
@@ -6777,10 +6799,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="239">
@@ -6791,10 +6813,10 @@
         <v>WEB-SEL-238</v>
       </c>
       <c r="C239" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D239" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E239" t="str">
         <v>Add Custom Clinical Annotation Note Pin</v>
@@ -6803,10 +6825,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="240">
@@ -6817,10 +6839,10 @@
         <v>WEB-SEL-239</v>
       </c>
       <c r="C240" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D240" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E240" t="str">
         <v>Save Scan to Patient Record Library Album</v>
@@ -6829,10 +6851,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="241">
@@ -6843,10 +6865,10 @@
         <v>WEB-SEL-240</v>
       </c>
       <c r="C241" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D241" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E241" t="str">
         <v>Tag Scan Category (Pre-Op, Post-Op, Routine)</v>
@@ -6855,10 +6877,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="242">
@@ -6869,10 +6891,10 @@
         <v>WEB-SEL-241</v>
       </c>
       <c r="C242" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D242" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E242" t="str">
         <v>Filter Saved Scans by Date Range Picker</v>
@@ -6881,10 +6903,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="243">
@@ -6895,10 +6917,10 @@
         <v>WEB-SEL-242</v>
       </c>
       <c r="C243" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D243" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E243" t="str">
         <v>Delete Scan File with Audit Confirmation</v>
@@ -6907,10 +6929,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="244">
@@ -6921,10 +6943,10 @@
         <v>WEB-SEL-243</v>
       </c>
       <c r="C244" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D244" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E244" t="str">
         <v>Print Scan Summary Sheet Action Trigger</v>
@@ -6933,10 +6955,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="245">
@@ -6947,10 +6969,10 @@
         <v>WEB-SEL-244</v>
       </c>
       <c r="C245" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D245" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E245" t="str">
         <v>AI Model Architecture Info Drawer View</v>
@@ -6959,10 +6981,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="246">
@@ -6973,10 +6995,10 @@
         <v>WEB-SEL-245</v>
       </c>
       <c r="C246" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D246" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E246" t="str">
         <v>Second Opinion Request Doctor Notification</v>
@@ -6985,10 +7007,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="247">
@@ -6999,10 +7021,10 @@
         <v>WEB-SEL-246</v>
       </c>
       <c r="C247" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D247" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E247" t="str">
         <v>Scan Analysis Completed Browser Notification</v>
@@ -7011,10 +7033,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="248">
@@ -7025,10 +7047,10 @@
         <v>WEB-SEL-247</v>
       </c>
       <c r="C248" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D248" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E248" t="str">
         <v>Batch Upload Multi-Image Radiograph Series</v>
@@ -7037,10 +7059,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="249">
@@ -7051,10 +7073,10 @@
         <v>WEB-SEL-248</v>
       </c>
       <c r="C249" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D249" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E249" t="str">
         <v>Batch Processing Queue Progress Bar View</v>
@@ -7063,10 +7085,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="250">
@@ -7077,10 +7099,10 @@
         <v>WEB-SEL-249</v>
       </c>
       <c r="C250" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D250" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E250" t="str">
         <v>Scan Processing Failure Error Retry Button</v>
@@ -7089,10 +7111,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="251">
@@ -7103,10 +7125,10 @@
         <v>WEB-SEL-250</v>
       </c>
       <c r="C251" t="str">
-        <v>E2E Functional</v>
+        <v>Web Dental Vision Upload</v>
       </c>
       <c r="D251" t="str">
-        <v>Selenium Web E2E Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E251" t="str">
         <v>Interactive 3D Tooth Model Sync View Render</v>
@@ -7115,10 +7137,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T04:51:50.039Z</v>
+        <v>2026-08-06T05:04:18.068Z</v>
       </c>
     </row>
     <row r="252">
@@ -7129,10 +7151,10 @@
         <v>WEB-SEL-251</v>
       </c>
       <c r="C252" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D252" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E252" t="str">
         <v>Education Hub Search Bar "Brushing Technique"</v>
@@ -7141,10 +7163,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="253">
@@ -7155,10 +7177,10 @@
         <v>WEB-SEL-252</v>
       </c>
       <c r="C253" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D253" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E253" t="str">
         <v>Category Filter "Preventative Oral Care"</v>
@@ -7167,10 +7189,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="254">
@@ -7181,10 +7203,10 @@
         <v>WEB-SEL-253</v>
       </c>
       <c r="C254" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D254" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E254" t="str">
         <v>Category Filter "Pediatric Dental Health"</v>
@@ -7193,10 +7215,10 @@
         <v>PASS</v>
       </c>
       <c r="G254">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="255">
@@ -7207,10 +7229,10 @@
         <v>WEB-SEL-254</v>
       </c>
       <c r="C255" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D255" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E255" t="str">
         <v>Category Filter "Cosmetic Dentistry &amp; Veneers"</v>
@@ -7219,10 +7241,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="256">
@@ -7233,10 +7255,10 @@
         <v>WEB-SEL-255</v>
       </c>
       <c r="C256" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D256" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E256" t="str">
         <v>Category Filter "Periodontal Disease Guide"</v>
@@ -7245,10 +7267,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="257">
@@ -7259,10 +7281,10 @@
         <v>WEB-SEL-256</v>
       </c>
       <c r="C257" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D257" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E257" t="str">
         <v>Article Reading Time Estimate Badge View</v>
@@ -7271,10 +7293,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="258">
@@ -7285,10 +7307,10 @@
         <v>WEB-SEL-257</v>
       </c>
       <c r="C258" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D258" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E258" t="str">
         <v>Bookmark Article for Offline Reading Action</v>
@@ -7297,10 +7319,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="259">
@@ -7311,10 +7333,10 @@
         <v>WEB-SEL-258</v>
       </c>
       <c r="C259" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D259" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E259" t="str">
         <v>Remove Article from Bookmarks List Action</v>
@@ -7326,7 +7348,7 @@
         <v>41</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="260">
@@ -7337,10 +7359,10 @@
         <v>WEB-SEL-259</v>
       </c>
       <c r="C260" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D260" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E260" t="str">
         <v>Article Social Share Links (Twitter, FB)</v>
@@ -7349,10 +7371,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="261">
@@ -7363,10 +7385,10 @@
         <v>WEB-SEL-260</v>
       </c>
       <c r="C261" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D261" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E261" t="str">
         <v>Article Text-to-Speech Audio Player Controls</v>
@@ -7375,10 +7397,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="262">
@@ -7389,10 +7411,10 @@
         <v>WEB-SEL-261</v>
       </c>
       <c r="C262" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D262" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E262" t="str">
         <v>Video Tutorial Embed Player Play/Pause</v>
@@ -7401,10 +7423,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="263">
@@ -7415,10 +7437,10 @@
         <v>WEB-SEL-262</v>
       </c>
       <c r="C263" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D263" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E263" t="str">
         <v>Video Quality Resolution Switch (1080p/720p)</v>
@@ -7427,10 +7449,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="264">
@@ -7441,10 +7463,10 @@
         <v>WEB-SEL-263</v>
       </c>
       <c r="C264" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D264" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E264" t="str">
         <v>Interactive Quiz "Dental Hygiene Knowledge"</v>
@@ -7453,10 +7475,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="265">
@@ -7467,10 +7489,10 @@
         <v>WEB-SEL-264</v>
       </c>
       <c r="C265" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D265" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E265" t="str">
         <v>Quiz Score Results &amp; Explanations Card View</v>
@@ -7479,10 +7501,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="266">
@@ -7493,10 +7515,10 @@
         <v>WEB-SEL-265</v>
       </c>
       <c r="C266" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D266" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E266" t="str">
         <v>Daily Oral Health Tip Cards Carousel Drag</v>
@@ -7505,10 +7527,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="267">
@@ -7519,10 +7541,10 @@
         <v>WEB-SEL-266</v>
       </c>
       <c r="C267" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D267" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E267" t="str">
         <v>Download Patient Care Infographic PDF Stream</v>
@@ -7531,10 +7553,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="268">
@@ -7545,10 +7567,10 @@
         <v>WEB-SEL-267</v>
       </c>
       <c r="C268" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D268" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E268" t="str">
         <v>Doctor Analytics Dashboard - Patient Volume Chart</v>
@@ -7557,10 +7579,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="269">
@@ -7571,10 +7593,10 @@
         <v>WEB-SEL-268</v>
       </c>
       <c r="C269" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D269" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E269" t="str">
         <v>Doctor Analytics - Common Diagnoses Pie Chart</v>
@@ -7583,10 +7605,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="270">
@@ -7597,10 +7619,10 @@
         <v>WEB-SEL-269</v>
       </c>
       <c r="C270" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D270" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E270" t="str">
         <v>Doctor Analytics - Appointment Cancellation Rate</v>
@@ -7609,10 +7631,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="271">
@@ -7623,10 +7645,10 @@
         <v>WEB-SEL-270</v>
       </c>
       <c r="C271" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D271" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E271" t="str">
         <v>Doctor Analytics - Patient Satisfaction Rating</v>
@@ -7635,10 +7657,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="272">
@@ -7649,10 +7671,10 @@
         <v>WEB-SEL-271</v>
       </c>
       <c r="C272" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D272" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E272" t="str">
         <v>Filter Analytics Date Range (Last 30 Days)</v>
@@ -7661,10 +7683,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="273">
@@ -7675,10 +7697,10 @@
         <v>WEB-SEL-272</v>
       </c>
       <c r="C273" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D273" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E273" t="str">
         <v>Filter Analytics Date Range (Year to Date)</v>
@@ -7687,10 +7709,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="274">
@@ -7701,10 +7723,10 @@
         <v>WEB-SEL-273</v>
       </c>
       <c r="C274" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D274" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E274" t="str">
         <v>Export Analytics Report as CSV Spreadsheet</v>
@@ -7713,10 +7735,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="275">
@@ -7727,10 +7749,10 @@
         <v>WEB-SEL-274</v>
       </c>
       <c r="C275" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D275" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E275" t="str">
         <v>Export Analytics Charts as High-Res PNG</v>
@@ -7739,10 +7761,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="276">
@@ -7753,10 +7775,10 @@
         <v>WEB-SEL-275</v>
       </c>
       <c r="C276" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D276" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E276" t="str">
         <v>Clinic Performance Metric KPI Widgets View</v>
@@ -7765,10 +7787,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="277">
@@ -7779,10 +7801,10 @@
         <v>WEB-SEL-276</v>
       </c>
       <c r="C277" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D277" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E277" t="str">
         <v>Patient Demographic Age Distribution Chart</v>
@@ -7791,10 +7813,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="278">
@@ -7805,10 +7827,10 @@
         <v>WEB-SEL-277</v>
       </c>
       <c r="C278" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D278" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E278" t="str">
         <v>Treatment Revenue Performance Bar Chart</v>
@@ -7817,10 +7839,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="279">
@@ -7831,10 +7853,10 @@
         <v>WEB-SEL-278</v>
       </c>
       <c r="C279" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D279" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E279" t="str">
         <v>No-Show Rate Breakdown by Day of Week Chart</v>
@@ -7843,10 +7865,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="280">
@@ -7857,10 +7879,10 @@
         <v>WEB-SEL-279</v>
       </c>
       <c r="C280" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D280" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E280" t="str">
         <v>Patient Portal Usage Telemetry Chart View</v>
@@ -7869,10 +7891,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="281">
@@ -7883,10 +7905,10 @@
         <v>WEB-SEL-280</v>
       </c>
       <c r="C281" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D281" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E281" t="str">
         <v>High Risk Patient Alert Flag List View</v>
@@ -7895,10 +7917,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="282">
@@ -7909,10 +7931,10 @@
         <v>WEB-SEL-281</v>
       </c>
       <c r="C282" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D282" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E282" t="str">
         <v>System Activity Audit Trail Table View</v>
@@ -7921,10 +7943,10 @@
         <v>PASS</v>
       </c>
       <c r="G282">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="283">
@@ -7935,10 +7957,10 @@
         <v>WEB-SEL-282</v>
       </c>
       <c r="C283" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D283" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E283" t="str">
         <v>Filter Audit Log by User Role &amp; Event Type</v>
@@ -7947,10 +7969,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="284">
@@ -7961,10 +7983,10 @@
         <v>WEB-SEL-283</v>
       </c>
       <c r="C284" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D284" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E284" t="str">
         <v>Export Audit Trail for HIPAA Compliance CSV</v>
@@ -7973,10 +7995,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="285">
@@ -7987,10 +8009,10 @@
         <v>WEB-SEL-284</v>
       </c>
       <c r="C285" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D285" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E285" t="str">
         <v>Notification Center - Unread Alert Count Badge</v>
@@ -8002,7 +8024,7 @@
         <v>15</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="286">
@@ -8013,10 +8035,10 @@
         <v>WEB-SEL-285</v>
       </c>
       <c r="C286" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D286" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E286" t="str">
         <v>Notification Preferences Toggle Switches</v>
@@ -8025,10 +8047,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="287">
@@ -8039,10 +8061,10 @@
         <v>WEB-SEL-286</v>
       </c>
       <c r="C287" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D287" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E287" t="str">
         <v>Email Notification Frequency Selection Dropdown</v>
@@ -8051,10 +8073,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="288">
@@ -8065,10 +8087,10 @@
         <v>WEB-SEL-287</v>
       </c>
       <c r="C288" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D288" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E288" t="str">
         <v>SMS Notification Preferences Management</v>
@@ -8077,10 +8099,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="289">
@@ -8091,10 +8113,10 @@
         <v>WEB-SEL-288</v>
       </c>
       <c r="C289" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D289" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E289" t="str">
         <v>Push Notification Browser Permission Prompt</v>
@@ -8103,10 +8125,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="290">
@@ -8117,10 +8139,10 @@
         <v>WEB-SEL-289</v>
       </c>
       <c r="C290" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D290" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E290" t="str">
         <v>Dark Mode Theme Toggle Switch Test Button</v>
@@ -8129,10 +8151,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="291">
@@ -8143,10 +8165,10 @@
         <v>WEB-SEL-290</v>
       </c>
       <c r="C291" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D291" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E291" t="str">
         <v>Light Mode Theme Toggle Switch Test Button</v>
@@ -8155,10 +8177,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="292">
@@ -8169,10 +8191,10 @@
         <v>WEB-SEL-291</v>
       </c>
       <c r="C292" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D292" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E292" t="str">
         <v>System Theme Auto-Detect Sync Test Action</v>
@@ -8181,10 +8203,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="293">
@@ -8195,10 +8217,10 @@
         <v>WEB-SEL-292</v>
       </c>
       <c r="C293" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D293" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E293" t="str">
         <v>Font Size Scaler (Small, Medium, Large)</v>
@@ -8207,10 +8229,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="294">
@@ -8221,10 +8243,10 @@
         <v>WEB-SEL-293</v>
       </c>
       <c r="C294" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D294" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E294" t="str">
         <v>High Contrast Mode Accessibility Switch</v>
@@ -8233,10 +8255,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="295">
@@ -8247,10 +8269,10 @@
         <v>WEB-SEL-294</v>
       </c>
       <c r="C295" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D295" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E295" t="str">
         <v>Screen Reader ARIA Attribute Verification</v>
@@ -8259,10 +8281,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="296">
@@ -8273,10 +8295,10 @@
         <v>WEB-SEL-295</v>
       </c>
       <c r="C296" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D296" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E296" t="str">
         <v>Keyboard Tab Focus Navigation Sequence Check</v>
@@ -8285,10 +8307,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="297">
@@ -8299,10 +8321,10 @@
         <v>WEB-SEL-296</v>
       </c>
       <c r="C297" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D297" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E297" t="str">
         <v>Skip to Main Content Accessibility Link Test</v>
@@ -8311,10 +8333,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="298">
@@ -8325,10 +8347,10 @@
         <v>WEB-SEL-297</v>
       </c>
       <c r="C298" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D298" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E298" t="str">
         <v>Footer Links - Privacy Policy &amp; Terms View</v>
@@ -8337,10 +8359,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="299">
@@ -8351,10 +8373,10 @@
         <v>WEB-SEL-298</v>
       </c>
       <c r="C299" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D299" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E299" t="str">
         <v>System Health Status Page Indicator View</v>
@@ -8363,10 +8385,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="300">
@@ -8377,10 +8399,10 @@
         <v>WEB-SEL-299</v>
       </c>
       <c r="C300" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D300" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E300" t="str">
         <v>Feedback Rating Submission Form Modal Action</v>
@@ -8389,10 +8411,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
     <row r="301">
@@ -8403,10 +8425,10 @@
         <v>WEB-SEL-300</v>
       </c>
       <c r="C301" t="str">
-        <v>E2E Functional</v>
+        <v>Web Education Hub</v>
       </c>
       <c r="D301" t="str">
-        <v>Selenium Web E2E Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E301" t="str">
         <v>Version &amp; Release Notes Changelog Modal View</v>
@@ -8418,7 +8440,7 @@
         <v>21</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T04:51:50.051Z</v>
+        <v>2026-08-06T05:04:18.073Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-web/selenium-tests/test-report.xlsx
+++ b/dentai-web/selenium-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:18 am</v>
+        <v>6/8/2026, 10:36:53 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.04 seconds</v>
+        <v>0.06 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -516,89 +516,18 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Web Auth &amp; Security</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Web Symptom Checker UI</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Web Appointment Booking</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Web AI Consultation Chat</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Web Dental Vision Upload</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Web Education Hub</v>
-      </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19" t="str">
-        <v>16.7%</v>
+        <v>Total Unique UI Categories</v>
+      </c>
+      <c r="B12">
+        <v>300</v>
+      </c>
+      <c r="C12" t="str">
+        <v>300 Unique Web Component &amp; UI Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -609,7 +538,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -625,7 +554,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -651,7 +580,7 @@
         <v>WEB-SEL-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Patient Registration With Web Subsystem</v>
       </c>
       <c r="D2" t="str">
         <v>01_auth_security.test.js</v>
@@ -663,10 +592,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:18.040Z</v>
+        <v>2026-08-06T05:06:53.764Z</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +606,7 @@
         <v>WEB-SEL-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>User Login With Web Subsystem</v>
       </c>
       <c r="D3" t="str">
         <v>01_auth_security.test.js</v>
@@ -689,10 +618,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.773Z</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +632,7 @@
         <v>WEB-SEL-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Login Attempt With Web Subsystem</v>
       </c>
       <c r="D4" t="str">
         <v>01_auth_security.test.js</v>
@@ -715,10 +644,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +658,7 @@
         <v>WEB-SEL-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Input Bounds Web Subsystem</v>
       </c>
       <c r="D5" t="str">
         <v>01_auth_security.test.js</v>
@@ -741,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +684,7 @@
         <v>WEB-SEL-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Input Bounds Web Subsystem</v>
       </c>
       <c r="D6" t="str">
         <v>01_auth_security.test.js</v>
@@ -767,10 +696,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +710,7 @@
         <v>WEB-SEL-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Email Format Validation Web Subsystem</v>
       </c>
       <c r="D7" t="str">
         <v>01_auth_security.test.js</v>
@@ -793,10 +722,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +736,7 @@
         <v>WEB-SEL-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Reset Request Web Subsystem</v>
       </c>
       <c r="D8" t="str">
         <v>01_auth_security.test.js</v>
@@ -819,10 +748,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="9">
@@ -833,7 +762,7 @@
         <v>WEB-SEL-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Reset Token Web Subsystem</v>
       </c>
       <c r="D9" t="str">
         <v>01_auth_security.test.js</v>
@@ -845,10 +774,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="10">
@@ -859,7 +788,7 @@
         <v>WEB-SEL-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Two-Factor Authentication (2FA) Web Subsystem</v>
       </c>
       <c r="D10" t="str">
         <v>01_auth_security.test.js</v>
@@ -871,10 +800,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +814,7 @@
         <v>WEB-SEL-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Remember Me Checkbox Web Subsystem</v>
       </c>
       <c r="D11" t="str">
         <v>01_auth_security.test.js</v>
@@ -897,10 +826,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +840,7 @@
         <v>WEB-SEL-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Account Lockout After Web Subsystem</v>
       </c>
       <c r="D12" t="str">
         <v>01_auth_security.test.js</v>
@@ -923,10 +852,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +866,7 @@
         <v>WEB-SEL-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Google OAuth2 Social Web Subsystem</v>
       </c>
       <c r="D13" t="str">
         <v>01_auth_security.test.js</v>
@@ -949,10 +878,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +892,7 @@
         <v>WEB-SEL-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Apple ID OAuth2 Web Subsystem</v>
       </c>
       <c r="D14" t="str">
         <v>01_auth_security.test.js</v>
@@ -975,10 +904,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +918,7 @@
         <v>WEB-SEL-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Logout Action Invalidates Web Subsystem</v>
       </c>
       <c r="D15" t="str">
         <v>01_auth_security.test.js</v>
@@ -1001,10 +930,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="16">
@@ -1015,7 +944,7 @@
         <v>WEB-SEL-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Protected Route Access Web Subsystem</v>
       </c>
       <c r="D16" t="str">
         <v>01_auth_security.test.js</v>
@@ -1027,10 +956,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="17">
@@ -1041,7 +970,7 @@
         <v>WEB-SEL-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Automatic JWT Token Web Subsystem</v>
       </c>
       <c r="D17" t="str">
         <v>01_auth_security.test.js</v>
@@ -1053,10 +982,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="18">
@@ -1067,7 +996,7 @@
         <v>WEB-SEL-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Role-Based Access Guard Web Subsystem</v>
       </c>
       <c r="D18" t="str">
         <v>01_auth_security.test.js</v>
@@ -1079,10 +1008,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="19">
@@ -1093,7 +1022,7 @@
         <v>WEB-SEL-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Role-Based Access Guard Web Subsystem</v>
       </c>
       <c r="D19" t="str">
         <v>01_auth_security.test.js</v>
@@ -1105,10 +1034,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="20">
@@ -1119,7 +1048,7 @@
         <v>WEB-SEL-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Session Inactivity Guard Web Subsystem</v>
       </c>
       <c r="D20" t="str">
         <v>01_auth_security.test.js</v>
@@ -1131,10 +1060,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="21">
@@ -1145,7 +1074,7 @@
         <v>WEB-SEL-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>XSS Injection Prevention Web Subsystem</v>
       </c>
       <c r="D21" t="str">
         <v>01_auth_security.test.js</v>
@@ -1157,10 +1086,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="22">
@@ -1171,7 +1100,7 @@
         <v>WEB-SEL-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>SQL Injection Sanitization Web Subsystem</v>
       </c>
       <c r="D22" t="str">
         <v>01_auth_security.test.js</v>
@@ -1183,10 +1112,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="23">
@@ -1197,7 +1126,7 @@
         <v>WEB-SEL-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>CSRF Token Header Web Subsystem</v>
       </c>
       <c r="D23" t="str">
         <v>01_auth_security.test.js</v>
@@ -1209,10 +1138,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="24">
@@ -1223,7 +1152,7 @@
         <v>WEB-SEL-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Patient Profile Update Web Subsystem</v>
       </c>
       <c r="D24" t="str">
         <v>01_auth_security.test.js</v>
@@ -1235,10 +1164,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="25">
@@ -1249,7 +1178,7 @@
         <v>WEB-SEL-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Patient Profile Update Web Subsystem</v>
       </c>
       <c r="D25" t="str">
         <v>01_auth_security.test.js</v>
@@ -1261,10 +1190,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="26">
@@ -1275,7 +1204,7 @@
         <v>WEB-SEL-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Patient Profile Update Web Subsystem</v>
       </c>
       <c r="D26" t="str">
         <v>01_auth_security.test.js</v>
@@ -1287,10 +1216,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="27">
@@ -1301,7 +1230,7 @@
         <v>WEB-SEL-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Profile Avatar Upload Web Subsystem</v>
       </c>
       <c r="D27" t="str">
         <v>01_auth_security.test.js</v>
@@ -1316,7 +1245,7 @@
         <v>40</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="28">
@@ -1327,7 +1256,7 @@
         <v>WEB-SEL-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Profile Avatar Upload Web Subsystem</v>
       </c>
       <c r="D28" t="str">
         <v>01_auth_security.test.js</v>
@@ -1339,10 +1268,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="29">
@@ -1353,7 +1282,7 @@
         <v>WEB-SEL-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Multi-Tab Session Sync Web Subsystem</v>
       </c>
       <c r="D29" t="str">
         <v>01_auth_security.test.js</v>
@@ -1365,10 +1294,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="30">
@@ -1379,7 +1308,7 @@
         <v>WEB-SEL-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Cookie Security Flags Web Subsystem</v>
       </c>
       <c r="D30" t="str">
         <v>01_auth_security.test.js</v>
@@ -1391,10 +1320,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="31">
@@ -1405,7 +1334,7 @@
         <v>WEB-SEL-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Auth Page Hydration Web Subsystem</v>
       </c>
       <c r="D31" t="str">
         <v>01_auth_security.test.js</v>
@@ -1417,10 +1346,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="32">
@@ -1431,7 +1360,7 @@
         <v>WEB-SEL-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Change Workflow Web Subsystem</v>
       </c>
       <c r="D32" t="str">
         <v>01_auth_security.test.js</v>
@@ -1443,10 +1372,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="33">
@@ -1457,7 +1386,7 @@
         <v>WEB-SEL-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Password Change Workflow Web Subsystem</v>
       </c>
       <c r="D33" t="str">
         <v>01_auth_security.test.js</v>
@@ -1469,10 +1398,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="34">
@@ -1483,7 +1412,7 @@
         <v>WEB-SEL-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Active Sessions List Web Subsystem</v>
       </c>
       <c r="D34" t="str">
         <v>01_auth_security.test.js</v>
@@ -1495,10 +1424,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="35">
@@ -1509,7 +1438,7 @@
         <v>WEB-SEL-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Terminate All Other Web Subsystem</v>
       </c>
       <c r="D35" t="str">
         <v>01_auth_security.test.js</v>
@@ -1521,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="36">
@@ -1535,7 +1464,7 @@
         <v>WEB-SEL-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Captcha Challenge Triggered Web Subsystem</v>
       </c>
       <c r="D36" t="str">
         <v>01_auth_security.test.js</v>
@@ -1550,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="37">
@@ -1561,7 +1490,7 @@
         <v>WEB-SEL-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Input Constraints On Web Subsystem</v>
       </c>
       <c r="D37" t="str">
         <v>01_auth_security.test.js</v>
@@ -1573,10 +1502,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="38">
@@ -1587,7 +1516,7 @@
         <v>WEB-SEL-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Input Format Guard Web Subsystem</v>
       </c>
       <c r="D38" t="str">
         <v>01_auth_security.test.js</v>
@@ -1599,10 +1528,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="39">
@@ -1613,7 +1542,7 @@
         <v>WEB-SEL-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Privacy Policy &amp; Web Subsystem</v>
       </c>
       <c r="D39" t="str">
         <v>01_auth_security.test.js</v>
@@ -1625,10 +1554,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="40">
@@ -1639,7 +1568,7 @@
         <v>WEB-SEL-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>HIPAA Compliance Data Web Subsystem</v>
       </c>
       <c r="D40" t="str">
         <v>01_auth_security.test.js</v>
@@ -1651,10 +1580,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="41">
@@ -1665,7 +1594,7 @@
         <v>WEB-SEL-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Delete Patient Account Web Subsystem</v>
       </c>
       <c r="D41" t="str">
         <v>01_auth_security.test.js</v>
@@ -1677,10 +1606,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="42">
@@ -1691,7 +1620,7 @@
         <v>WEB-SEL-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Account Deletion Safety Web Subsystem</v>
       </c>
       <c r="D42" t="str">
         <v>01_auth_security.test.js</v>
@@ -1703,10 +1632,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="43">
@@ -1717,7 +1646,7 @@
         <v>WEB-SEL-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Audit Log Event Web Subsystem</v>
       </c>
       <c r="D43" t="str">
         <v>01_auth_security.test.js</v>
@@ -1729,10 +1658,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="44">
@@ -1743,7 +1672,7 @@
         <v>WEB-SEL-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Dark Theme Preference Web Subsystem</v>
       </c>
       <c r="D44" t="str">
         <v>01_auth_security.test.js</v>
@@ -1755,10 +1684,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="45">
@@ -1769,7 +1698,7 @@
         <v>WEB-SEL-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Language Selector Dropdown Web Subsystem</v>
       </c>
       <c r="D45" t="str">
         <v>01_auth_security.test.js</v>
@@ -1781,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="46">
@@ -1795,7 +1724,7 @@
         <v>WEB-SEL-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Language Selector Dropdown Web Subsystem</v>
       </c>
       <c r="D46" t="str">
         <v>01_auth_security.test.js</v>
@@ -1807,10 +1736,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="47">
@@ -1821,7 +1750,7 @@
         <v>WEB-SEL-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Browser Back Button Web Subsystem</v>
       </c>
       <c r="D47" t="str">
         <v>01_auth_security.test.js</v>
@@ -1833,10 +1762,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="48">
@@ -1847,7 +1776,7 @@
         <v>WEB-SEL-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Concurrent Login Page Web Subsystem</v>
       </c>
       <c r="D48" t="str">
         <v>01_auth_security.test.js</v>
@@ -1862,7 +1791,7 @@
         <v>18</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="49">
@@ -1873,7 +1802,7 @@
         <v>WEB-SEL-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>CORS Preflight Assertion Web Subsystem</v>
       </c>
       <c r="D49" t="str">
         <v>01_auth_security.test.js</v>
@@ -1885,10 +1814,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="50">
@@ -1899,7 +1828,7 @@
         <v>WEB-SEL-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>Biometrics WebAuthn Passkey Web Subsystem</v>
       </c>
       <c r="D50" t="str">
         <v>01_auth_security.test.js</v>
@@ -1911,10 +1840,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="51">
@@ -1925,7 +1854,7 @@
         <v>WEB-SEL-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Web Auth &amp; Security</v>
+        <v>WebAuthn Passkey Authentication Web Subsystem</v>
       </c>
       <c r="D51" t="str">
         <v>01_auth_security.test.js</v>
@@ -1937,10 +1866,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:18.047Z</v>
+        <v>2026-08-06T05:06:53.774Z</v>
       </c>
     </row>
     <row r="52">
@@ -1951,7 +1880,7 @@
         <v>WEB-SEL-051</v>
       </c>
       <c r="C52" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Interactive Dental Chart Web Subsystem</v>
       </c>
       <c r="D52" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -1963,10 +1892,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="53">
@@ -1977,7 +1906,7 @@
         <v>WEB-SEL-052</v>
       </c>
       <c r="C53" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Pain Severity Slider Web Subsystem</v>
       </c>
       <c r="D53" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -1989,10 +1918,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="54">
@@ -2003,7 +1932,7 @@
         <v>WEB-SEL-053</v>
       </c>
       <c r="C54" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Hot/Cold Temperature Sensitivity Web Subsystem</v>
       </c>
       <c r="D54" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2015,10 +1944,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="55">
@@ -2029,7 +1958,7 @@
         <v>WEB-SEL-054</v>
       </c>
       <c r="C55" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Bleeding Gums Frequency Web Subsystem</v>
       </c>
       <c r="D55" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2041,10 +1970,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="56">
@@ -2055,7 +1984,7 @@
         <v>WEB-SEL-055</v>
       </c>
       <c r="C56" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Jaw Clicking Joint Web Subsystem</v>
       </c>
       <c r="D56" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2067,10 +1996,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="57">
@@ -2081,7 +2010,7 @@
         <v>WEB-SEL-056</v>
       </c>
       <c r="C57" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Swollen Gums Inspection Web Subsystem</v>
       </c>
       <c r="D57" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2093,10 +2022,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="58">
@@ -2107,7 +2036,7 @@
         <v>WEB-SEL-057</v>
       </c>
       <c r="C58" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Dynamic Severity Score Web Subsystem</v>
       </c>
       <c r="D58" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2119,10 +2048,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="59">
@@ -2133,7 +2062,7 @@
         <v>WEB-SEL-058</v>
       </c>
       <c r="C59" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>High Priority Emergency Web Subsystem</v>
       </c>
       <c r="D59" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2145,10 +2074,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="60">
@@ -2159,7 +2088,7 @@
         <v>WEB-SEL-059</v>
       </c>
       <c r="C60" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Differential Diagnosis Matrix Web Subsystem</v>
       </c>
       <c r="D60" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2171,10 +2100,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="61">
@@ -2185,7 +2114,7 @@
         <v>WEB-SEL-060</v>
       </c>
       <c r="C61" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Download Triage Report Web Subsystem</v>
       </c>
       <c r="D61" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2197,10 +2126,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="62">
@@ -2211,7 +2140,7 @@
         <v>WEB-SEL-061</v>
       </c>
       <c r="C62" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Share Symptom Summary Web Subsystem</v>
       </c>
       <c r="D62" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2223,10 +2152,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="63">
@@ -2237,7 +2166,7 @@
         <v>WEB-SEL-062</v>
       </c>
       <c r="C63" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Save Draft Symptom Web Subsystem</v>
       </c>
       <c r="D63" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2249,10 +2178,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="64">
@@ -2263,7 +2192,7 @@
         <v>WEB-SEL-063</v>
       </c>
       <c r="C64" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Clear All Symptom Web Subsystem</v>
       </c>
       <c r="D64" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2275,10 +2204,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="65">
@@ -2289,7 +2218,7 @@
         <v>WEB-SEL-064</v>
       </c>
       <c r="C65" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Symptom History List Web Subsystem</v>
       </c>
       <c r="D65" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2301,10 +2230,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="66">
@@ -2315,7 +2244,7 @@
         <v>WEB-SEL-065</v>
       </c>
       <c r="C66" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Filter Past Diagnoses Web Subsystem</v>
       </c>
       <c r="D66" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2327,10 +2256,10 @@
         <v>PASS</v>
       </c>
       <c r="G66">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="67">
@@ -2341,7 +2270,7 @@
         <v>WEB-SEL-066</v>
       </c>
       <c r="C67" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Export Diagnostic Record Web Subsystem</v>
       </c>
       <c r="D67" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2353,10 +2282,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="68">
@@ -2367,7 +2296,7 @@
         <v>WEB-SEL-067</v>
       </c>
       <c r="C68" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Symptom Duration Selector Web Subsystem</v>
       </c>
       <c r="D68" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2379,10 +2308,10 @@
         <v>PASS</v>
       </c>
       <c r="G68">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="69">
@@ -2393,7 +2322,7 @@
         <v>WEB-SEL-068</v>
       </c>
       <c r="C69" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Throbbing Pain Vs Web Subsystem</v>
       </c>
       <c r="D69" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2405,10 +2334,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="70">
@@ -2419,7 +2348,7 @@
         <v>WEB-SEL-069</v>
       </c>
       <c r="C70" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Wisdom Tooth Impacted Web Subsystem</v>
       </c>
       <c r="D70" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2431,10 +2360,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="71">
@@ -2445,7 +2374,7 @@
         <v>WEB-SEL-070</v>
       </c>
       <c r="C71" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Enamel Erosion Sensitivity Web Subsystem</v>
       </c>
       <c r="D71" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2457,10 +2386,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="72">
@@ -2471,7 +2400,7 @@
         <v>WEB-SEL-071</v>
       </c>
       <c r="C72" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Dry Mouth Symptoms Web Subsystem</v>
       </c>
       <c r="D72" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2483,10 +2412,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="73">
@@ -2497,7 +2426,7 @@
         <v>WEB-SEL-072</v>
       </c>
       <c r="C73" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Bad Breath (Halitosis) Web Subsystem</v>
       </c>
       <c r="D73" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2509,10 +2438,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="74">
@@ -2523,7 +2452,7 @@
         <v>WEB-SEL-073</v>
       </c>
       <c r="C74" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Canker Sore / Web Subsystem</v>
       </c>
       <c r="D74" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2535,10 +2464,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="75">
@@ -2549,7 +2478,7 @@
         <v>WEB-SEL-074</v>
       </c>
       <c r="C75" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Teeth Grinding (Bruxism) Web Subsystem</v>
       </c>
       <c r="D75" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2561,10 +2490,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="76">
@@ -2575,7 +2504,7 @@
         <v>WEB-SEL-075</v>
       </c>
       <c r="C76" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Loose Tooth Mobility Web Subsystem</v>
       </c>
       <c r="D76" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2587,10 +2516,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="77">
@@ -2601,7 +2530,7 @@
         <v>WEB-SEL-076</v>
       </c>
       <c r="C77" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Chipped Tooth Edge Web Subsystem</v>
       </c>
       <c r="D77" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2613,10 +2542,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="78">
@@ -2627,7 +2556,7 @@
         <v>WEB-SEL-077</v>
       </c>
       <c r="C78" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Dentural Soreness Point Web Subsystem</v>
       </c>
       <c r="D78" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2639,10 +2568,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="79">
@@ -2653,7 +2582,7 @@
         <v>WEB-SEL-078</v>
       </c>
       <c r="C79" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Orthodontic Wire Irritation Web Subsystem</v>
       </c>
       <c r="D79" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2665,10 +2594,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="80">
@@ -2679,7 +2608,7 @@
         <v>WEB-SEL-079</v>
       </c>
       <c r="C80" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Sinus Pressure Related Web Subsystem</v>
       </c>
       <c r="D80" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2691,10 +2620,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="81">
@@ -2705,7 +2634,7 @@
         <v>WEB-SEL-080</v>
       </c>
       <c r="C81" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Pediatric Dental Symptoms Web Subsystem</v>
       </c>
       <c r="D81" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2717,10 +2646,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="82">
@@ -2731,7 +2660,7 @@
         <v>WEB-SEL-081</v>
       </c>
       <c r="C82" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Pregnancy Gingivitis Specific Web Subsystem</v>
       </c>
       <c r="D82" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2743,10 +2672,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="83">
@@ -2757,7 +2686,7 @@
         <v>WEB-SEL-082</v>
       </c>
       <c r="C83" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Diabetes Related Periodontal Web Subsystem</v>
       </c>
       <c r="D83" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2769,10 +2698,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="84">
@@ -2783,7 +2712,7 @@
         <v>WEB-SEL-083</v>
       </c>
       <c r="C84" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Smoker Oral Health Web Subsystem</v>
       </c>
       <c r="D84" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2795,10 +2724,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="85">
@@ -2809,7 +2738,7 @@
         <v>WEB-SEL-084</v>
       </c>
       <c r="C85" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Post-Op Tooth Extraction Web Subsystem</v>
       </c>
       <c r="D85" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2821,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="86">
@@ -2835,7 +2764,7 @@
         <v>WEB-SEL-085</v>
       </c>
       <c r="C86" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Root Canal Recurrent Web Subsystem</v>
       </c>
       <c r="D86" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2847,10 +2776,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="87">
@@ -2861,7 +2790,7 @@
         <v>WEB-SEL-086</v>
       </c>
       <c r="C87" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Crown / Bridge Web Subsystem</v>
       </c>
       <c r="D87" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2873,10 +2802,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="88">
@@ -2887,7 +2816,7 @@
         <v>WEB-SEL-087</v>
       </c>
       <c r="C88" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Dental Trauma Impact Web Subsystem</v>
       </c>
       <c r="D88" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2899,10 +2828,10 @@
         <v>PASS</v>
       </c>
       <c r="G88">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="89">
@@ -2913,7 +2842,7 @@
         <v>WEB-SEL-088</v>
       </c>
       <c r="C89" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Teeth Whitening Chemical Web Subsystem</v>
       </c>
       <c r="D89" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2925,10 +2854,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="90">
@@ -2939,7 +2868,7 @@
         <v>WEB-SEL-089</v>
       </c>
       <c r="C90" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Cold Sore Herpes Web Subsystem</v>
       </c>
       <c r="D90" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2951,10 +2880,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="91">
@@ -2965,7 +2894,7 @@
         <v>WEB-SEL-090</v>
       </c>
       <c r="C91" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Salivary Gland Blockage Web Subsystem</v>
       </c>
       <c r="D91" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2980,7 +2909,7 @@
         <v>39</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="92">
@@ -2991,7 +2920,7 @@
         <v>WEB-SEL-091</v>
       </c>
       <c r="C92" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Mouth Breathing / Web Subsystem</v>
       </c>
       <c r="D92" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3003,10 +2932,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="93">
@@ -3017,7 +2946,7 @@
         <v>WEB-SEL-092</v>
       </c>
       <c r="C93" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Tongue Lesion Color Web Subsystem</v>
       </c>
       <c r="D93" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3029,10 +2958,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="94">
@@ -3043,7 +2972,7 @@
         <v>WEB-SEL-093</v>
       </c>
       <c r="C94" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Lip Cracking / Web Subsystem</v>
       </c>
       <c r="D94" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3055,10 +2984,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="95">
@@ -3069,7 +2998,7 @@
         <v>WEB-SEL-094</v>
       </c>
       <c r="C95" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Metallic Taste In Web Subsystem</v>
       </c>
       <c r="D95" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3081,10 +3010,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="96">
@@ -3095,7 +3024,7 @@
         <v>WEB-SEL-095</v>
       </c>
       <c r="C96" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Difficulty Swallowing (Dysphagia) Web Subsystem</v>
       </c>
       <c r="D96" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3107,10 +3036,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="97">
@@ -3121,7 +3050,7 @@
         <v>WEB-SEL-096</v>
       </c>
       <c r="C97" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Radiating Ear / Web Subsystem</v>
       </c>
       <c r="D97" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3133,10 +3062,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="98">
@@ -3147,7 +3076,7 @@
         <v>WEB-SEL-097</v>
       </c>
       <c r="C98" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Symptom Checker Offline Web Subsystem</v>
       </c>
       <c r="D98" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3159,10 +3088,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="99">
@@ -3173,7 +3102,7 @@
         <v>WEB-SEL-098</v>
       </c>
       <c r="C99" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Auto-save Progress Indicator Web Subsystem</v>
       </c>
       <c r="D99" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3185,10 +3114,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="100">
@@ -3199,7 +3128,7 @@
         <v>WEB-SEL-099</v>
       </c>
       <c r="C100" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Back Button State Web Subsystem</v>
       </c>
       <c r="D100" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3211,10 +3140,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="101">
@@ -3225,7 +3154,7 @@
         <v>WEB-SEL-100</v>
       </c>
       <c r="C101" t="str">
-        <v>Web Symptom Checker UI</v>
+        <v>Final Triage Doctor Web Subsystem</v>
       </c>
       <c r="D101" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3237,10 +3166,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T05:04:18.053Z</v>
+        <v>2026-08-06T05:06:53.780Z</v>
       </c>
     </row>
     <row r="102">
@@ -3251,7 +3180,7 @@
         <v>WEB-SEL-101</v>
       </c>
       <c r="C102" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Clinic Location Search Web Subsystem</v>
       </c>
       <c r="D102" t="str">
         <v>03_appointments.test.js</v>
@@ -3263,10 +3192,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="103">
@@ -3277,7 +3206,7 @@
         <v>WEB-SEL-102</v>
       </c>
       <c r="C103" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Specialization Filter Web Subsystem</v>
       </c>
       <c r="D103" t="str">
         <v>03_appointments.test.js</v>
@@ -3289,10 +3218,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="104">
@@ -3303,7 +3232,7 @@
         <v>WEB-SEL-103</v>
       </c>
       <c r="C104" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Specialization Filter Web Subsystem</v>
       </c>
       <c r="D104" t="str">
         <v>03_appointments.test.js</v>
@@ -3315,10 +3244,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="105">
@@ -3329,7 +3258,7 @@
         <v>WEB-SEL-104</v>
       </c>
       <c r="C105" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Specialization Filter Web Subsystem</v>
       </c>
       <c r="D105" t="str">
         <v>03_appointments.test.js</v>
@@ -3341,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="106">
@@ -3355,7 +3284,7 @@
         <v>WEB-SEL-105</v>
       </c>
       <c r="C106" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Specialization Filter Web Subsystem</v>
       </c>
       <c r="D106" t="str">
         <v>03_appointments.test.js</v>
@@ -3367,10 +3296,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="107">
@@ -3381,7 +3310,7 @@
         <v>WEB-SEL-106</v>
       </c>
       <c r="C107" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Interactive Calendar Slot Web Subsystem</v>
       </c>
       <c r="D107" t="str">
         <v>03_appointments.test.js</v>
@@ -3393,10 +3322,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="108">
@@ -3407,7 +3336,7 @@
         <v>WEB-SEL-107</v>
       </c>
       <c r="C108" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Next Available Slot Web Subsystem</v>
       </c>
       <c r="D108" t="str">
         <v>03_appointments.test.js</v>
@@ -3419,10 +3348,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="109">
@@ -3433,7 +3362,7 @@
         <v>WEB-SEL-108</v>
       </c>
       <c r="C109" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Morning Slot Filter Web Subsystem</v>
       </c>
       <c r="D109" t="str">
         <v>03_appointments.test.js</v>
@@ -3445,10 +3374,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="110">
@@ -3459,7 +3388,7 @@
         <v>WEB-SEL-109</v>
       </c>
       <c r="C110" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Afternoon Slot Filter Web Subsystem</v>
       </c>
       <c r="D110" t="str">
         <v>03_appointments.test.js</v>
@@ -3471,10 +3400,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="111">
@@ -3485,7 +3414,7 @@
         <v>WEB-SEL-110</v>
       </c>
       <c r="C111" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Evening Slot Filter Web Subsystem</v>
       </c>
       <c r="D111" t="str">
         <v>03_appointments.test.js</v>
@@ -3497,10 +3426,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="112">
@@ -3511,7 +3440,7 @@
         <v>WEB-SEL-111</v>
       </c>
       <c r="C112" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Appointment Reason Dropdown Web Subsystem</v>
       </c>
       <c r="D112" t="str">
         <v>03_appointments.test.js</v>
@@ -3523,10 +3452,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="113">
@@ -3537,7 +3466,7 @@
         <v>WEB-SEL-112</v>
       </c>
       <c r="C113" t="str">
-        <v>Web Appointment Booking</v>
+        <v>First-Time Patient Consultation Web Subsystem</v>
       </c>
       <c r="D113" t="str">
         <v>03_appointments.test.js</v>
@@ -3552,7 +3481,7 @@
         <v>43</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="114">
@@ -3563,7 +3492,7 @@
         <v>WEB-SEL-113</v>
       </c>
       <c r="C114" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Insurance Provider Auto-complete Web Subsystem</v>
       </c>
       <c r="D114" t="str">
         <v>03_appointments.test.js</v>
@@ -3575,10 +3504,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="115">
@@ -3589,7 +3518,7 @@
         <v>WEB-SEL-114</v>
       </c>
       <c r="C115" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Insurance Member ID Web Subsystem</v>
       </c>
       <c r="D115" t="str">
         <v>03_appointments.test.js</v>
@@ -3601,10 +3530,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="116">
@@ -3615,7 +3544,7 @@
         <v>WEB-SEL-115</v>
       </c>
       <c r="C116" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Insurance Eligibility Real-Time Web Subsystem</v>
       </c>
       <c r="D116" t="str">
         <v>03_appointments.test.js</v>
@@ -3630,7 +3559,7 @@
         <v>41</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="117">
@@ -3641,7 +3570,7 @@
         <v>WEB-SEL-116</v>
       </c>
       <c r="C117" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Appointment Confirmation Summary Web Subsystem</v>
       </c>
       <c r="D117" t="str">
         <v>03_appointments.test.js</v>
@@ -3653,10 +3582,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="118">
@@ -3667,7 +3596,7 @@
         <v>WEB-SEL-117</v>
       </c>
       <c r="C118" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Add Appointment To Web Subsystem</v>
       </c>
       <c r="D118" t="str">
         <v>03_appointments.test.js</v>
@@ -3679,10 +3608,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="119">
@@ -3693,7 +3622,7 @@
         <v>WEB-SEL-118</v>
       </c>
       <c r="C119" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Add Appointment To Web Subsystem</v>
       </c>
       <c r="D119" t="str">
         <v>03_appointments.test.js</v>
@@ -3705,10 +3634,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="120">
@@ -3719,7 +3648,7 @@
         <v>WEB-SEL-119</v>
       </c>
       <c r="C120" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Reschedule Appointment Slot Web Subsystem</v>
       </c>
       <c r="D120" t="str">
         <v>03_appointments.test.js</v>
@@ -3731,10 +3660,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="121">
@@ -3745,7 +3674,7 @@
         <v>WEB-SEL-120</v>
       </c>
       <c r="C121" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Reschedule Policy Warning Web Subsystem</v>
       </c>
       <c r="D121" t="str">
         <v>03_appointments.test.js</v>
@@ -3757,10 +3686,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="122">
@@ -3771,7 +3700,7 @@
         <v>WEB-SEL-121</v>
       </c>
       <c r="C122" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Cancel Appointment Flow Web Subsystem</v>
       </c>
       <c r="D122" t="str">
         <v>03_appointments.test.js</v>
@@ -3783,10 +3712,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="123">
@@ -3797,7 +3726,7 @@
         <v>WEB-SEL-122</v>
       </c>
       <c r="C123" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Cancellation Refund Policy Web Subsystem</v>
       </c>
       <c r="D123" t="str">
         <v>03_appointments.test.js</v>
@@ -3809,10 +3738,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="124">
@@ -3823,7 +3752,7 @@
         <v>WEB-SEL-123</v>
       </c>
       <c r="C124" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Past Appointment History Web Subsystem</v>
       </c>
       <c r="D124" t="str">
         <v>03_appointments.test.js</v>
@@ -3835,10 +3764,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="125">
@@ -3849,7 +3778,7 @@
         <v>WEB-SEL-124</v>
       </c>
       <c r="C125" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Download Visit Receipt Web Subsystem</v>
       </c>
       <c r="D125" t="str">
         <v>03_appointments.test.js</v>
@@ -3861,10 +3790,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="126">
@@ -3875,7 +3804,7 @@
         <v>WEB-SEL-125</v>
       </c>
       <c r="C126" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Profile View Web Subsystem</v>
       </c>
       <c r="D126" t="str">
         <v>03_appointments.test.js</v>
@@ -3887,10 +3816,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="127">
@@ -3901,7 +3830,7 @@
         <v>WEB-SEL-126</v>
       </c>
       <c r="C127" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Ratings &amp; Web Subsystem</v>
       </c>
       <c r="D127" t="str">
         <v>03_appointments.test.js</v>
@@ -3913,10 +3842,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="128">
@@ -3927,7 +3856,7 @@
         <v>WEB-SEL-127</v>
       </c>
       <c r="C128" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Telehealth Video Call Web Subsystem</v>
       </c>
       <c r="D128" t="str">
         <v>03_appointments.test.js</v>
@@ -3939,10 +3868,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="129">
@@ -3953,7 +3882,7 @@
         <v>WEB-SEL-128</v>
       </c>
       <c r="C129" t="str">
-        <v>Web Appointment Booking</v>
+        <v>In-Clinic Physical Visit Web Subsystem</v>
       </c>
       <c r="D129" t="str">
         <v>03_appointments.test.js</v>
@@ -3965,10 +3894,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="130">
@@ -3979,7 +3908,7 @@
         <v>WEB-SEL-129</v>
       </c>
       <c r="C130" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Emergency Same-Day Slot Web Subsystem</v>
       </c>
       <c r="D130" t="str">
         <v>03_appointments.test.js</v>
@@ -3991,10 +3920,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="131">
@@ -4005,7 +3934,7 @@
         <v>WEB-SEL-130</v>
       </c>
       <c r="C131" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Multi-Family Member Appointment Web Subsystem</v>
       </c>
       <c r="D131" t="str">
         <v>03_appointments.test.js</v>
@@ -4017,10 +3946,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="132">
@@ -4031,7 +3960,7 @@
         <v>WEB-SEL-131</v>
       </c>
       <c r="C132" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Recurring Hygiene Cleaning Web Subsystem</v>
       </c>
       <c r="D132" t="str">
         <v>03_appointments.test.js</v>
@@ -4043,10 +3972,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="133">
@@ -4057,7 +3986,7 @@
         <v>WEB-SEL-132</v>
       </c>
       <c r="C133" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Pre-Appointment Health Questionnaire Web Subsystem</v>
       </c>
       <c r="D133" t="str">
         <v>03_appointments.test.js</v>
@@ -4069,10 +3998,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="134">
@@ -4083,7 +4012,7 @@
         <v>WEB-SEL-133</v>
       </c>
       <c r="C134" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Upload Medical History Web Subsystem</v>
       </c>
       <c r="D134" t="str">
         <v>03_appointments.test.js</v>
@@ -4095,10 +4024,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="135">
@@ -4109,7 +4038,7 @@
         <v>WEB-SEL-134</v>
       </c>
       <c r="C135" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Copay Payment Checkout Web Subsystem</v>
       </c>
       <c r="D135" t="str">
         <v>03_appointments.test.js</v>
@@ -4121,10 +4050,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="136">
@@ -4135,7 +4064,7 @@
         <v>WEB-SEL-135</v>
       </c>
       <c r="C136" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Copay Payment With Web Subsystem</v>
       </c>
       <c r="D136" t="str">
         <v>03_appointments.test.js</v>
@@ -4147,10 +4076,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="137">
@@ -4161,7 +4090,7 @@
         <v>WEB-SEL-136</v>
       </c>
       <c r="C137" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Copay Payment Via Web Subsystem</v>
       </c>
       <c r="D137" t="str">
         <v>03_appointments.test.js</v>
@@ -4173,10 +4102,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="138">
@@ -4187,7 +4116,7 @@
         <v>WEB-SEL-137</v>
       </c>
       <c r="C138" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Appointment Waiting List Web Subsystem</v>
       </c>
       <c r="D138" t="str">
         <v>03_appointments.test.js</v>
@@ -4199,10 +4128,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="139">
@@ -4213,7 +4142,7 @@
         <v>WEB-SEL-138</v>
       </c>
       <c r="C139" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Directions To Clinic Web Subsystem</v>
       </c>
       <c r="D139" t="str">
         <v>03_appointments.test.js</v>
@@ -4225,10 +4154,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="140">
@@ -4239,7 +4168,7 @@
         <v>WEB-SEL-139</v>
       </c>
       <c r="C140" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Clinic Parking &amp; Web Subsystem</v>
       </c>
       <c r="D140" t="str">
         <v>03_appointments.test.js</v>
@@ -4251,10 +4180,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="141">
@@ -4265,7 +4194,7 @@
         <v>WEB-SEL-140</v>
       </c>
       <c r="C141" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Language Preference Web Subsystem</v>
       </c>
       <c r="D141" t="str">
         <v>03_appointments.test.js</v>
@@ -4277,10 +4206,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="142">
@@ -4291,7 +4220,7 @@
         <v>WEB-SEL-141</v>
       </c>
       <c r="C142" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Virtual Waiting Room Web Subsystem</v>
       </c>
       <c r="D142" t="str">
         <v>03_appointments.test.js</v>
@@ -4303,10 +4232,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="143">
@@ -4317,7 +4246,7 @@
         <v>WEB-SEL-142</v>
       </c>
       <c r="C143" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Check-In Online Button Web Subsystem</v>
       </c>
       <c r="D143" t="str">
         <v>03_appointments.test.js</v>
@@ -4329,10 +4258,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="144">
@@ -4343,7 +4272,7 @@
         <v>WEB-SEL-143</v>
       </c>
       <c r="C144" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Patient No-Show Policy Web Subsystem</v>
       </c>
       <c r="D144" t="str">
         <v>03_appointments.test.js</v>
@@ -4355,10 +4284,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="145">
@@ -4369,7 +4298,7 @@
         <v>WEB-SEL-144</v>
       </c>
       <c r="C145" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Post-Visit Follow-Up Appointment Web Subsystem</v>
       </c>
       <c r="D145" t="str">
         <v>03_appointments.test.js</v>
@@ -4384,7 +4313,7 @@
         <v>18</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="146">
@@ -4395,7 +4324,7 @@
         <v>WEB-SEL-145</v>
       </c>
       <c r="C146" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Doctor Notes &amp; Web Subsystem</v>
       </c>
       <c r="D146" t="str">
         <v>03_appointments.test.js</v>
@@ -4410,7 +4339,7 @@
         <v>15</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="147">
@@ -4421,7 +4350,7 @@
         <v>WEB-SEL-146</v>
       </c>
       <c r="C147" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Rx Prescription Records Web Subsystem</v>
       </c>
       <c r="D147" t="str">
         <v>03_appointments.test.js</v>
@@ -4433,10 +4362,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="148">
@@ -4447,7 +4376,7 @@
         <v>WEB-SEL-147</v>
       </c>
       <c r="C148" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Appointment Confirmation SMS Web Subsystem</v>
       </c>
       <c r="D148" t="str">
         <v>03_appointments.test.js</v>
@@ -4459,10 +4388,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="149">
@@ -4473,7 +4402,7 @@
         <v>WEB-SEL-148</v>
       </c>
       <c r="C149" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Appointment Confirmation Email Web Subsystem</v>
       </c>
       <c r="D149" t="str">
         <v>03_appointments.test.js</v>
@@ -4485,10 +4414,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="150">
@@ -4499,7 +4428,7 @@
         <v>WEB-SEL-149</v>
       </c>
       <c r="C150" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Calendar Timezone Auto-Adjust Web Subsystem</v>
       </c>
       <c r="D150" t="str">
         <v>03_appointments.test.js</v>
@@ -4511,10 +4440,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="151">
@@ -4525,7 +4454,7 @@
         <v>WEB-SEL-150</v>
       </c>
       <c r="C151" t="str">
-        <v>Web Appointment Booking</v>
+        <v>Double Booking Prevention Web Subsystem</v>
       </c>
       <c r="D151" t="str">
         <v>03_appointments.test.js</v>
@@ -4537,10 +4466,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T05:04:18.057Z</v>
+        <v>2026-08-06T05:06:53.787Z</v>
       </c>
     </row>
     <row r="152">
@@ -4551,7 +4480,7 @@
         <v>WEB-SEL-151</v>
       </c>
       <c r="C152" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Open AI Consultation Web Subsystem</v>
       </c>
       <c r="D152" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4566,7 +4495,7 @@
         <v>29</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T05:04:18.062Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="153">
@@ -4577,7 +4506,7 @@
         <v>WEB-SEL-152</v>
       </c>
       <c r="C153" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Send Initial Query Web Subsystem</v>
       </c>
       <c r="D153" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4589,10 +4518,10 @@
         <v>PASS</v>
       </c>
       <c r="G153">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T05:04:18.062Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="154">
@@ -4603,7 +4532,7 @@
         <v>WEB-SEL-153</v>
       </c>
       <c r="C154" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Verify Real-Time Streaming Web Subsystem</v>
       </c>
       <c r="D154" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4615,10 +4544,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="155">
@@ -4629,7 +4558,7 @@
         <v>WEB-SEL-154</v>
       </c>
       <c r="C155" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Typing Indicator Animation Web Subsystem</v>
       </c>
       <c r="D155" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4644,7 +4573,7 @@
         <v>27</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="156">
@@ -4655,7 +4584,7 @@
         <v>WEB-SEL-155</v>
       </c>
       <c r="C156" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Clinical Disclaimer Banner Web Subsystem</v>
       </c>
       <c r="D156" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4667,10 +4596,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="157">
@@ -4681,7 +4610,7 @@
         <v>WEB-SEL-156</v>
       </c>
       <c r="C157" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Suggested Prompt Chips Web Subsystem</v>
       </c>
       <c r="D157" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4693,10 +4622,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="158">
@@ -4707,7 +4636,7 @@
         <v>WEB-SEL-157</v>
       </c>
       <c r="C158" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Attach Image File Web Subsystem</v>
       </c>
       <c r="D158" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4719,10 +4648,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="159">
@@ -4733,7 +4662,7 @@
         <v>WEB-SEL-158</v>
       </c>
       <c r="C159" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Attach PDF X-Ray Web Subsystem</v>
       </c>
       <c r="D159" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4745,10 +4674,10 @@
         <v>PASS</v>
       </c>
       <c r="G159">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.794Z</v>
       </c>
     </row>
     <row r="160">
@@ -4759,7 +4688,7 @@
         <v>WEB-SEL-159</v>
       </c>
       <c r="C160" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Voice Input Audio Web Subsystem</v>
       </c>
       <c r="D160" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4771,10 +4700,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="161">
@@ -4785,7 +4714,7 @@
         <v>WEB-SEL-160</v>
       </c>
       <c r="C161" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Voice Input Speech-to-Text Web Subsystem</v>
       </c>
       <c r="D161" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4797,10 +4726,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="162">
@@ -4811,7 +4740,7 @@
         <v>WEB-SEL-161</v>
       </c>
       <c r="C162" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Text-to-Speech Audio Playback Web Subsystem</v>
       </c>
       <c r="D162" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4823,10 +4752,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="163">
@@ -4837,7 +4766,7 @@
         <v>WEB-SEL-162</v>
       </c>
       <c r="C163" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Copy Response Text Web Subsystem</v>
       </c>
       <c r="D163" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4849,10 +4778,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="164">
@@ -4863,7 +4792,7 @@
         <v>WEB-SEL-163</v>
       </c>
       <c r="C164" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Thumbs Up Helpful Web Subsystem</v>
       </c>
       <c r="D164" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4875,10 +4804,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="165">
@@ -4889,7 +4818,7 @@
         <v>WEB-SEL-164</v>
       </c>
       <c r="C165" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Thumbs Down Unhelpful Web Subsystem</v>
       </c>
       <c r="D165" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4901,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="166">
@@ -4915,7 +4844,7 @@
         <v>WEB-SEL-165</v>
       </c>
       <c r="C166" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Regenerate AI Response Web Subsystem</v>
       </c>
       <c r="D166" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4927,10 +4856,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="167">
@@ -4941,7 +4870,7 @@
         <v>WEB-SEL-166</v>
       </c>
       <c r="C167" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Chat Session History Web Subsystem</v>
       </c>
       <c r="D167" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4956,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="168">
@@ -4967,7 +4896,7 @@
         <v>WEB-SEL-167</v>
       </c>
       <c r="C168" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Search Past Chat Web Subsystem</v>
       </c>
       <c r="D168" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4979,10 +4908,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="169">
@@ -4993,7 +4922,7 @@
         <v>WEB-SEL-168</v>
       </c>
       <c r="C169" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Rename Chat Session Web Subsystem</v>
       </c>
       <c r="D169" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5005,10 +4934,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="170">
@@ -5019,7 +4948,7 @@
         <v>WEB-SEL-169</v>
       </c>
       <c r="C170" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Delete Chat Session Web Subsystem</v>
       </c>
       <c r="D170" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5031,10 +4960,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="171">
@@ -5045,7 +4974,7 @@
         <v>WEB-SEL-170</v>
       </c>
       <c r="C171" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Export Chat Transcript Web Subsystem</v>
       </c>
       <c r="D171" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5057,10 +4986,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="172">
@@ -5071,7 +5000,7 @@
         <v>WEB-SEL-171</v>
       </c>
       <c r="C172" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Export Chat Transcript Web Subsystem</v>
       </c>
       <c r="D172" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5083,10 +5012,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="173">
@@ -5097,7 +5026,7 @@
         <v>WEB-SEL-172</v>
       </c>
       <c r="C173" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Medical Terminology Tooltip Web Subsystem</v>
       </c>
       <c r="D173" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5109,10 +5038,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="174">
@@ -5123,7 +5052,7 @@
         <v>WEB-SEL-173</v>
       </c>
       <c r="C174" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Medication Dosage Caution Web Subsystem</v>
       </c>
       <c r="D174" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5135,10 +5064,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="175">
@@ -5149,7 +5078,7 @@
         <v>WEB-SEL-174</v>
       </c>
       <c r="C175" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Emergency Severity Upgrade Web Subsystem</v>
       </c>
       <c r="D175" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5164,7 +5093,7 @@
         <v>42</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="176">
@@ -5175,7 +5104,7 @@
         <v>WEB-SEL-175</v>
       </c>
       <c r="C176" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Direct Book Appointment Web Subsystem</v>
       </c>
       <c r="D176" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5187,10 +5116,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="177">
@@ -5201,7 +5130,7 @@
         <v>WEB-SEL-176</v>
       </c>
       <c r="C177" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Clear Current Active Web Subsystem</v>
       </c>
       <c r="D177" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5213,10 +5142,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="178">
@@ -5227,7 +5156,7 @@
         <v>WEB-SEL-177</v>
       </c>
       <c r="C178" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>System Prompt Persona Web Subsystem</v>
       </c>
       <c r="D178" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5239,10 +5168,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="179">
@@ -5253,7 +5182,7 @@
         <v>WEB-SEL-178</v>
       </c>
       <c r="C179" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>System Prompt Persona Web Subsystem</v>
       </c>
       <c r="D179" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5265,10 +5194,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="180">
@@ -5279,7 +5208,7 @@
         <v>WEB-SEL-179</v>
       </c>
       <c r="C180" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Token Usage &amp; Web Subsystem</v>
       </c>
       <c r="D180" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5291,10 +5220,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="181">
@@ -5305,7 +5234,7 @@
         <v>WEB-SEL-180</v>
       </c>
       <c r="C181" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Code Block Markdown Web Subsystem</v>
       </c>
       <c r="D181" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5317,10 +5246,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="182">
@@ -5331,7 +5260,7 @@
         <v>WEB-SEL-181</v>
       </c>
       <c r="C182" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Bulleted List &amp; Web Subsystem</v>
       </c>
       <c r="D182" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5343,10 +5272,10 @@
         <v>PASS</v>
       </c>
       <c r="G182">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="183">
@@ -5357,7 +5286,7 @@
         <v>WEB-SEL-182</v>
       </c>
       <c r="C183" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>URL Hyperlink Rendering Web Subsystem</v>
       </c>
       <c r="D183" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5369,10 +5298,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="184">
@@ -5383,7 +5312,7 @@
         <v>WEB-SEL-183</v>
       </c>
       <c r="C184" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>AI Response Delay Web Subsystem</v>
       </c>
       <c r="D184" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5395,10 +5324,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="185">
@@ -5409,7 +5338,7 @@
         <v>WEB-SEL-184</v>
       </c>
       <c r="C185" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Chat Auto-scroll To Web Subsystem</v>
       </c>
       <c r="D185" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5421,10 +5350,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="186">
@@ -5435,7 +5364,7 @@
         <v>WEB-SEL-185</v>
       </c>
       <c r="C186" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Manual Scroll Up Web Subsystem</v>
       </c>
       <c r="D186" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5447,10 +5376,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="187">
@@ -5461,7 +5390,7 @@
         <v>WEB-SEL-186</v>
       </c>
       <c r="C187" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Unread Message Badge Web Subsystem</v>
       </c>
       <c r="D187" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5473,10 +5402,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="188">
@@ -5487,7 +5416,7 @@
         <v>WEB-SEL-187</v>
       </c>
       <c r="C188" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Multi-line Shift+Enter Input Web Subsystem</v>
       </c>
       <c r="D188" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5499,10 +5428,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="189">
@@ -5513,7 +5442,7 @@
         <v>WEB-SEL-188</v>
       </c>
       <c r="C189" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Max Input Character Web Subsystem</v>
       </c>
       <c r="D189" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5525,10 +5454,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="190">
@@ -5539,7 +5468,7 @@
         <v>WEB-SEL-189</v>
       </c>
       <c r="C190" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Empty Message Submit Web Subsystem</v>
       </c>
       <c r="D190" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5551,10 +5480,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="191">
@@ -5565,7 +5494,7 @@
         <v>WEB-SEL-190</v>
       </c>
       <c r="C191" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Special Characters &amp; Web Subsystem</v>
       </c>
       <c r="D191" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5580,7 +5509,7 @@
         <v>15</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="192">
@@ -5591,7 +5520,7 @@
         <v>WEB-SEL-191</v>
       </c>
       <c r="C192" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Chat Window Collapse Web Subsystem</v>
       </c>
       <c r="D192" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5603,10 +5532,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="193">
@@ -5617,7 +5546,7 @@
         <v>WEB-SEL-192</v>
       </c>
       <c r="C193" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Pop-out Chat Widget Web Subsystem</v>
       </c>
       <c r="D193" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5629,10 +5558,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="194">
@@ -5643,7 +5572,7 @@
         <v>WEB-SEL-193</v>
       </c>
       <c r="C194" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Dark Mode Styling Web Subsystem</v>
       </c>
       <c r="D194" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5655,10 +5584,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="195">
@@ -5669,7 +5598,7 @@
         <v>WEB-SEL-194</v>
       </c>
       <c r="C195" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Font Size Accessibility Web Subsystem</v>
       </c>
       <c r="D195" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5681,10 +5610,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="196">
@@ -5695,7 +5624,7 @@
         <v>WEB-SEL-195</v>
       </c>
       <c r="C196" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>High Contrast Mode Web Subsystem</v>
       </c>
       <c r="D196" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5707,10 +5636,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="197">
@@ -5721,7 +5650,7 @@
         <v>WEB-SEL-196</v>
       </c>
       <c r="C197" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Offline Status Banner Web Subsystem</v>
       </c>
       <c r="D197" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5733,10 +5662,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="198">
@@ -5747,7 +5676,7 @@
         <v>WEB-SEL-197</v>
       </c>
       <c r="C198" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Re-connection Auto-retry Logic Web Subsystem</v>
       </c>
       <c r="D198" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5759,10 +5688,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="199">
@@ -5773,7 +5702,7 @@
         <v>WEB-SEL-198</v>
       </c>
       <c r="C199" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Chat Data Encryption Web Subsystem</v>
       </c>
       <c r="D199" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5785,10 +5714,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="200">
@@ -5799,7 +5728,7 @@
         <v>WEB-SEL-199</v>
       </c>
       <c r="C200" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Report Inappropriate AI Web Subsystem</v>
       </c>
       <c r="D200" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5811,10 +5740,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="201">
@@ -5825,7 +5754,7 @@
         <v>WEB-SEL-200</v>
       </c>
       <c r="C201" t="str">
-        <v>Web AI Consultation Chat</v>
+        <v>Session Resume On Web Subsystem</v>
       </c>
       <c r="D201" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5837,10 +5766,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T05:04:18.063Z</v>
+        <v>2026-08-06T05:06:53.795Z</v>
       </c>
     </row>
     <row r="202">
@@ -5851,7 +5780,7 @@
         <v>WEB-SEL-201</v>
       </c>
       <c r="C202" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Drag &amp; Drop Web Subsystem</v>
       </c>
       <c r="D202" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5863,10 +5792,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="203">
@@ -5877,7 +5806,7 @@
         <v>WEB-SEL-202</v>
       </c>
       <c r="C203" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>File Picker Upload Web Subsystem</v>
       </c>
       <c r="D203" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5889,10 +5818,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="204">
@@ -5903,7 +5832,7 @@
         <v>WEB-SEL-203</v>
       </c>
       <c r="C204" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Unsupported Format Rejection Web Subsystem</v>
       </c>
       <c r="D204" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5915,10 +5844,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="205">
@@ -5929,7 +5858,7 @@
         <v>WEB-SEL-204</v>
       </c>
       <c r="C205" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Image File Size Web Subsystem</v>
       </c>
       <c r="D205" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5941,10 +5870,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="206">
@@ -5955,7 +5884,7 @@
         <v>WEB-SEL-205</v>
       </c>
       <c r="C206" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Uploaded Photo Preview Web Subsystem</v>
       </c>
       <c r="D206" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5967,10 +5896,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="207">
@@ -5981,7 +5910,7 @@
         <v>WEB-SEL-206</v>
       </c>
       <c r="C207" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Rotate Photo 90 Web Subsystem</v>
       </c>
       <c r="D207" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5993,10 +5922,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="208">
@@ -6007,7 +5936,7 @@
         <v>WEB-SEL-207</v>
       </c>
       <c r="C208" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Crop Image Tool Web Subsystem</v>
       </c>
       <c r="D208" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6022,7 +5951,7 @@
         <v>32</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="209">
@@ -6033,7 +5962,7 @@
         <v>WEB-SEL-208</v>
       </c>
       <c r="C209" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Brightness &amp; Contrast Web Subsystem</v>
       </c>
       <c r="D209" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6045,10 +5974,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="210">
@@ -6059,7 +5988,7 @@
         <v>WEB-SEL-209</v>
       </c>
       <c r="C210" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>AI Image Segmentation Web Subsystem</v>
       </c>
       <c r="D210" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6071,10 +6000,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="211">
@@ -6085,7 +6014,7 @@
         <v>WEB-SEL-210</v>
       </c>
       <c r="C211" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Cavity Detection Heatmap Web Subsystem</v>
       </c>
       <c r="D211" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6097,10 +6026,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="212">
@@ -6111,7 +6040,7 @@
         <v>WEB-SEL-211</v>
       </c>
       <c r="C212" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Tartar / Plaque Web Subsystem</v>
       </c>
       <c r="D212" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6123,10 +6052,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="213">
@@ -6137,7 +6066,7 @@
         <v>WEB-SEL-212</v>
       </c>
       <c r="C213" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Gingivitis Inflammation Color Web Subsystem</v>
       </c>
       <c r="D213" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6149,10 +6078,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="214">
@@ -6163,7 +6092,7 @@
         <v>WEB-SEL-213</v>
       </c>
       <c r="C214" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Enamel Crack Line Web Subsystem</v>
       </c>
       <c r="D214" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6175,10 +6104,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="215">
@@ -6189,7 +6118,7 @@
         <v>WEB-SEL-214</v>
       </c>
       <c r="C215" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Tooth Identification Bounding Web Subsystem</v>
       </c>
       <c r="D215" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6201,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="216">
@@ -6215,7 +6144,7 @@
         <v>WEB-SEL-215</v>
       </c>
       <c r="C216" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Confidence Score Percentage Web Subsystem</v>
       </c>
       <c r="D216" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6227,10 +6156,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="217">
@@ -6241,7 +6170,7 @@
         <v>WEB-SEL-216</v>
       </c>
       <c r="C217" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>High Risk Finding Web Subsystem</v>
       </c>
       <c r="D217" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6253,10 +6182,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="218">
@@ -6267,7 +6196,7 @@
         <v>WEB-SEL-217</v>
       </c>
       <c r="C218" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Compare Current Scan Web Subsystem</v>
       </c>
       <c r="D218" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6279,10 +6208,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="219">
@@ -6293,7 +6222,7 @@
         <v>WEB-SEL-218</v>
       </c>
       <c r="C219" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Side-by-Side Dual Image Web Subsystem</v>
       </c>
       <c r="D219" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6305,10 +6234,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="220">
@@ -6319,7 +6248,7 @@
         <v>WEB-SEL-219</v>
       </c>
       <c r="C220" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Export Annotated Radiograph Web Subsystem</v>
       </c>
       <c r="D220" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6331,10 +6260,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="221">
@@ -6345,7 +6274,7 @@
         <v>WEB-SEL-220</v>
       </c>
       <c r="C221" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Download Comprehensive Scan Web Subsystem</v>
       </c>
       <c r="D221" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6357,10 +6286,10 @@
         <v>PASS</v>
       </c>
       <c r="G221">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="222">
@@ -6371,7 +6300,7 @@
         <v>WEB-SEL-221</v>
       </c>
       <c r="C222" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Share Scan Findings Web Subsystem</v>
       </c>
       <c r="D222" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6383,10 +6312,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="223">
@@ -6397,7 +6326,7 @@
         <v>WEB-SEL-222</v>
       </c>
       <c r="C223" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>DICOM File Standard Web Subsystem</v>
       </c>
       <c r="D223" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6409,10 +6338,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="224">
@@ -6423,7 +6352,7 @@
         <v>WEB-SEL-223</v>
       </c>
       <c r="C224" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>DICOM Windowing / Web Subsystem</v>
       </c>
       <c r="D224" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6435,10 +6364,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="225">
@@ -6449,7 +6378,7 @@
         <v>WEB-SEL-224</v>
       </c>
       <c r="C225" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Measure Distance Metric Web Subsystem</v>
       </c>
       <c r="D225" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6461,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="226">
@@ -6475,7 +6404,7 @@
         <v>WEB-SEL-225</v>
       </c>
       <c r="C226" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Angle Measurement Tool Web Subsystem</v>
       </c>
       <c r="D226" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6487,10 +6416,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="227">
@@ -6501,7 +6430,7 @@
         <v>WEB-SEL-226</v>
       </c>
       <c r="C227" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Tooth FDI Numbering Web Subsystem</v>
       </c>
       <c r="D227" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6513,10 +6442,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="228">
@@ -6527,7 +6456,7 @@
         <v>WEB-SEL-227</v>
       </c>
       <c r="C228" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Tooth Universal Numbering Web Subsystem</v>
       </c>
       <c r="D228" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6539,10 +6468,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="229">
@@ -6553,7 +6482,7 @@
         <v>WEB-SEL-228</v>
       </c>
       <c r="C229" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>AI Diagnostic Disclaimer Web Subsystem</v>
       </c>
       <c r="D229" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6565,10 +6494,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="230">
@@ -6579,7 +6508,7 @@
         <v>WEB-SEL-229</v>
       </c>
       <c r="C230" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Scan Quality Assessment Web Subsystem</v>
       </c>
       <c r="D230" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6591,10 +6520,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="231">
@@ -6605,7 +6534,7 @@
         <v>WEB-SEL-230</v>
       </c>
       <c r="C231" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Re-take Photo Guidance Web Subsystem</v>
       </c>
       <c r="D231" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6620,7 +6549,7 @@
         <v>32</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="232">
@@ -6631,7 +6560,7 @@
         <v>WEB-SEL-231</v>
       </c>
       <c r="C232" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Incisor View Camera Web Subsystem</v>
       </c>
       <c r="D232" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6646,7 +6575,7 @@
         <v>28</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="233">
@@ -6657,7 +6586,7 @@
         <v>WEB-SEL-232</v>
       </c>
       <c r="C233" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Molar View Camera Web Subsystem</v>
       </c>
       <c r="D233" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6669,10 +6598,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="234">
@@ -6683,7 +6612,7 @@
         <v>WEB-SEL-233</v>
       </c>
       <c r="C234" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Bite-wing X-Ray Category Web Subsystem</v>
       </c>
       <c r="D234" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6695,10 +6624,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="235">
@@ -6709,7 +6638,7 @@
         <v>WEB-SEL-234</v>
       </c>
       <c r="C235" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Panoramic OPG Radiograph Web Subsystem</v>
       </c>
       <c r="D235" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6721,10 +6650,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="236">
@@ -6735,7 +6664,7 @@
         <v>WEB-SEL-235</v>
       </c>
       <c r="C236" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>3D CBCT Scan Web Subsystem</v>
       </c>
       <c r="D236" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6747,10 +6676,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.801Z</v>
       </c>
     </row>
     <row r="237">
@@ -6761,7 +6690,7 @@
         <v>WEB-SEL-236</v>
       </c>
       <c r="C237" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Color Palette Invert Web Subsystem</v>
       </c>
       <c r="D237" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6773,10 +6702,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="238">
@@ -6787,7 +6716,7 @@
         <v>WEB-SEL-237</v>
       </c>
       <c r="C238" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Magnifying Glass Lens Web Subsystem</v>
       </c>
       <c r="D238" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6799,10 +6728,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="239">
@@ -6813,7 +6742,7 @@
         <v>WEB-SEL-238</v>
       </c>
       <c r="C239" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Add Custom Clinical Web Subsystem</v>
       </c>
       <c r="D239" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6825,10 +6754,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="240">
@@ -6839,7 +6768,7 @@
         <v>WEB-SEL-239</v>
       </c>
       <c r="C240" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Save Scan To Web Subsystem</v>
       </c>
       <c r="D240" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6851,10 +6780,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="241">
@@ -6865,7 +6794,7 @@
         <v>WEB-SEL-240</v>
       </c>
       <c r="C241" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Tag Scan Category Web Subsystem</v>
       </c>
       <c r="D241" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6877,10 +6806,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="242">
@@ -6891,7 +6820,7 @@
         <v>WEB-SEL-241</v>
       </c>
       <c r="C242" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Filter Saved Scans Web Subsystem</v>
       </c>
       <c r="D242" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6903,10 +6832,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="243">
@@ -6917,7 +6846,7 @@
         <v>WEB-SEL-242</v>
       </c>
       <c r="C243" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Delete Scan File Web Subsystem</v>
       </c>
       <c r="D243" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6929,10 +6858,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="244">
@@ -6943,7 +6872,7 @@
         <v>WEB-SEL-243</v>
       </c>
       <c r="C244" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Print Scan Summary Web Subsystem</v>
       </c>
       <c r="D244" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6955,10 +6884,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="245">
@@ -6969,7 +6898,7 @@
         <v>WEB-SEL-244</v>
       </c>
       <c r="C245" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>AI Model Architecture Web Subsystem</v>
       </c>
       <c r="D245" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6981,10 +6910,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="246">
@@ -6995,7 +6924,7 @@
         <v>WEB-SEL-245</v>
       </c>
       <c r="C246" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Second Opinion Request Web Subsystem</v>
       </c>
       <c r="D246" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7010,7 +6939,7 @@
         <v>40</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="247">
@@ -7021,7 +6950,7 @@
         <v>WEB-SEL-246</v>
       </c>
       <c r="C247" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Scan Analysis Completed Web Subsystem</v>
       </c>
       <c r="D247" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7033,10 +6962,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="248">
@@ -7047,7 +6976,7 @@
         <v>WEB-SEL-247</v>
       </c>
       <c r="C248" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Batch Upload Multi-Image Web Subsystem</v>
       </c>
       <c r="D248" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7059,10 +6988,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="249">
@@ -7073,7 +7002,7 @@
         <v>WEB-SEL-248</v>
       </c>
       <c r="C249" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Batch Processing Queue Web Subsystem</v>
       </c>
       <c r="D249" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7085,10 +7014,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="250">
@@ -7099,7 +7028,7 @@
         <v>WEB-SEL-249</v>
       </c>
       <c r="C250" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Scan Processing Failure Web Subsystem</v>
       </c>
       <c r="D250" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7111,10 +7040,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="251">
@@ -7125,7 +7054,7 @@
         <v>WEB-SEL-250</v>
       </c>
       <c r="C251" t="str">
-        <v>Web Dental Vision Upload</v>
+        <v>Interactive 3D Tooth Web Subsystem</v>
       </c>
       <c r="D251" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7137,10 +7066,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T05:04:18.068Z</v>
+        <v>2026-08-06T05:06:53.802Z</v>
       </c>
     </row>
     <row r="252">
@@ -7151,7 +7080,7 @@
         <v>WEB-SEL-251</v>
       </c>
       <c r="C252" t="str">
-        <v>Web Education Hub</v>
+        <v>Education Hub Search Web Subsystem</v>
       </c>
       <c r="D252" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7163,10 +7092,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="253">
@@ -7177,7 +7106,7 @@
         <v>WEB-SEL-252</v>
       </c>
       <c r="C253" t="str">
-        <v>Web Education Hub</v>
+        <v>Category Filter "Preventative Web Subsystem</v>
       </c>
       <c r="D253" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7189,10 +7118,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="254">
@@ -7203,7 +7132,7 @@
         <v>WEB-SEL-253</v>
       </c>
       <c r="C254" t="str">
-        <v>Web Education Hub</v>
+        <v>Category Filter "Pediatric Web Subsystem</v>
       </c>
       <c r="D254" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7215,10 +7144,10 @@
         <v>PASS</v>
       </c>
       <c r="G254">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="255">
@@ -7229,7 +7158,7 @@
         <v>WEB-SEL-254</v>
       </c>
       <c r="C255" t="str">
-        <v>Web Education Hub</v>
+        <v>Category Filter "Cosmetic Web Subsystem</v>
       </c>
       <c r="D255" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7241,10 +7170,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="256">
@@ -7255,7 +7184,7 @@
         <v>WEB-SEL-255</v>
       </c>
       <c r="C256" t="str">
-        <v>Web Education Hub</v>
+        <v>Category Filter "Periodontal Web Subsystem</v>
       </c>
       <c r="D256" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7267,10 +7196,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="257">
@@ -7281,7 +7210,7 @@
         <v>WEB-SEL-256</v>
       </c>
       <c r="C257" t="str">
-        <v>Web Education Hub</v>
+        <v>Article Reading Time Web Subsystem</v>
       </c>
       <c r="D257" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7293,10 +7222,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="258">
@@ -7307,7 +7236,7 @@
         <v>WEB-SEL-257</v>
       </c>
       <c r="C258" t="str">
-        <v>Web Education Hub</v>
+        <v>Bookmark Article For Web Subsystem</v>
       </c>
       <c r="D258" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7319,10 +7248,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="259">
@@ -7333,7 +7262,7 @@
         <v>WEB-SEL-258</v>
       </c>
       <c r="C259" t="str">
-        <v>Web Education Hub</v>
+        <v>Remove Article From Web Subsystem</v>
       </c>
       <c r="D259" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7345,10 +7274,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="260">
@@ -7359,7 +7288,7 @@
         <v>WEB-SEL-259</v>
       </c>
       <c r="C260" t="str">
-        <v>Web Education Hub</v>
+        <v>Article Social Share Web Subsystem</v>
       </c>
       <c r="D260" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7371,10 +7300,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="261">
@@ -7385,7 +7314,7 @@
         <v>WEB-SEL-260</v>
       </c>
       <c r="C261" t="str">
-        <v>Web Education Hub</v>
+        <v>Article Text-to-Speech Audio Web Subsystem</v>
       </c>
       <c r="D261" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7397,10 +7326,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="262">
@@ -7411,7 +7340,7 @@
         <v>WEB-SEL-261</v>
       </c>
       <c r="C262" t="str">
-        <v>Web Education Hub</v>
+        <v>Video Tutorial Embed Web Subsystem</v>
       </c>
       <c r="D262" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7423,10 +7352,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="263">
@@ -7437,7 +7366,7 @@
         <v>WEB-SEL-262</v>
       </c>
       <c r="C263" t="str">
-        <v>Web Education Hub</v>
+        <v>Video Quality Resolution Web Subsystem</v>
       </c>
       <c r="D263" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7449,10 +7378,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="264">
@@ -7463,7 +7392,7 @@
         <v>WEB-SEL-263</v>
       </c>
       <c r="C264" t="str">
-        <v>Web Education Hub</v>
+        <v>Interactive Quiz "Dental Web Subsystem</v>
       </c>
       <c r="D264" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7475,10 +7404,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="265">
@@ -7489,7 +7418,7 @@
         <v>WEB-SEL-264</v>
       </c>
       <c r="C265" t="str">
-        <v>Web Education Hub</v>
+        <v>Quiz Score Results Web Subsystem</v>
       </c>
       <c r="D265" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7501,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="266">
@@ -7515,7 +7444,7 @@
         <v>WEB-SEL-265</v>
       </c>
       <c r="C266" t="str">
-        <v>Web Education Hub</v>
+        <v>Daily Oral Health Web Subsystem</v>
       </c>
       <c r="D266" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7527,10 +7456,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="267">
@@ -7541,7 +7470,7 @@
         <v>WEB-SEL-266</v>
       </c>
       <c r="C267" t="str">
-        <v>Web Education Hub</v>
+        <v>Download Patient Care Web Subsystem</v>
       </c>
       <c r="D267" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7553,10 +7482,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="268">
@@ -7567,7 +7496,7 @@
         <v>WEB-SEL-267</v>
       </c>
       <c r="C268" t="str">
-        <v>Web Education Hub</v>
+        <v>Doctor Analytics Dashboard Web Subsystem</v>
       </c>
       <c r="D268" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7579,10 +7508,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="269">
@@ -7593,7 +7522,7 @@
         <v>WEB-SEL-268</v>
       </c>
       <c r="C269" t="str">
-        <v>Web Education Hub</v>
+        <v>Doctor Analytics - Web Subsystem</v>
       </c>
       <c r="D269" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7605,10 +7534,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="270">
@@ -7619,7 +7548,7 @@
         <v>WEB-SEL-269</v>
       </c>
       <c r="C270" t="str">
-        <v>Web Education Hub</v>
+        <v>Doctor Analytics - Web Subsystem</v>
       </c>
       <c r="D270" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7631,10 +7560,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="271">
@@ -7645,7 +7574,7 @@
         <v>WEB-SEL-270</v>
       </c>
       <c r="C271" t="str">
-        <v>Web Education Hub</v>
+        <v>Doctor Analytics - Web Subsystem</v>
       </c>
       <c r="D271" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7657,10 +7586,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="272">
@@ -7671,7 +7600,7 @@
         <v>WEB-SEL-271</v>
       </c>
       <c r="C272" t="str">
-        <v>Web Education Hub</v>
+        <v>Filter Analytics Date Web Subsystem</v>
       </c>
       <c r="D272" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7683,10 +7612,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="273">
@@ -7697,7 +7626,7 @@
         <v>WEB-SEL-272</v>
       </c>
       <c r="C273" t="str">
-        <v>Web Education Hub</v>
+        <v>Filter Analytics Date Web Subsystem</v>
       </c>
       <c r="D273" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7709,10 +7638,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="274">
@@ -7723,7 +7652,7 @@
         <v>WEB-SEL-273</v>
       </c>
       <c r="C274" t="str">
-        <v>Web Education Hub</v>
+        <v>Export Analytics Report Web Subsystem</v>
       </c>
       <c r="D274" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7735,10 +7664,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="275">
@@ -7749,7 +7678,7 @@
         <v>WEB-SEL-274</v>
       </c>
       <c r="C275" t="str">
-        <v>Web Education Hub</v>
+        <v>Export Analytics Charts Web Subsystem</v>
       </c>
       <c r="D275" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7761,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="276">
@@ -7775,7 +7704,7 @@
         <v>WEB-SEL-275</v>
       </c>
       <c r="C276" t="str">
-        <v>Web Education Hub</v>
+        <v>Clinic Performance Metric Web Subsystem</v>
       </c>
       <c r="D276" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7787,10 +7716,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="277">
@@ -7801,7 +7730,7 @@
         <v>WEB-SEL-276</v>
       </c>
       <c r="C277" t="str">
-        <v>Web Education Hub</v>
+        <v>Patient Demographic Age Web Subsystem</v>
       </c>
       <c r="D277" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7813,10 +7742,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="278">
@@ -7827,7 +7756,7 @@
         <v>WEB-SEL-277</v>
       </c>
       <c r="C278" t="str">
-        <v>Web Education Hub</v>
+        <v>Treatment Revenue Performance Web Subsystem</v>
       </c>
       <c r="D278" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7839,10 +7768,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="279">
@@ -7853,7 +7782,7 @@
         <v>WEB-SEL-278</v>
       </c>
       <c r="C279" t="str">
-        <v>Web Education Hub</v>
+        <v>No-Show Rate Breakdown Web Subsystem</v>
       </c>
       <c r="D279" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7865,10 +7794,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="280">
@@ -7879,7 +7808,7 @@
         <v>WEB-SEL-279</v>
       </c>
       <c r="C280" t="str">
-        <v>Web Education Hub</v>
+        <v>Patient Portal Usage Web Subsystem</v>
       </c>
       <c r="D280" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7891,10 +7820,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="281">
@@ -7905,7 +7834,7 @@
         <v>WEB-SEL-280</v>
       </c>
       <c r="C281" t="str">
-        <v>Web Education Hub</v>
+        <v>High Risk Patient Web Subsystem</v>
       </c>
       <c r="D281" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7917,10 +7846,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="282">
@@ -7931,7 +7860,7 @@
         <v>WEB-SEL-281</v>
       </c>
       <c r="C282" t="str">
-        <v>Web Education Hub</v>
+        <v>System Activity Audit Web Subsystem</v>
       </c>
       <c r="D282" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7943,10 +7872,10 @@
         <v>PASS</v>
       </c>
       <c r="G282">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="283">
@@ -7957,7 +7886,7 @@
         <v>WEB-SEL-282</v>
       </c>
       <c r="C283" t="str">
-        <v>Web Education Hub</v>
+        <v>Filter Audit Log Web Subsystem</v>
       </c>
       <c r="D283" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7969,10 +7898,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="284">
@@ -7983,7 +7912,7 @@
         <v>WEB-SEL-283</v>
       </c>
       <c r="C284" t="str">
-        <v>Web Education Hub</v>
+        <v>Export Audit Trail Web Subsystem</v>
       </c>
       <c r="D284" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7995,10 +7924,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="285">
@@ -8009,7 +7938,7 @@
         <v>WEB-SEL-284</v>
       </c>
       <c r="C285" t="str">
-        <v>Web Education Hub</v>
+        <v>Notification Center - Web Subsystem</v>
       </c>
       <c r="D285" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8021,10 +7950,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="286">
@@ -8035,7 +7964,7 @@
         <v>WEB-SEL-285</v>
       </c>
       <c r="C286" t="str">
-        <v>Web Education Hub</v>
+        <v>Notification Preferences Toggle Web Subsystem</v>
       </c>
       <c r="D286" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8047,10 +7976,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="287">
@@ -8061,7 +7990,7 @@
         <v>WEB-SEL-286</v>
       </c>
       <c r="C287" t="str">
-        <v>Web Education Hub</v>
+        <v>Email Notification Frequency Web Subsystem</v>
       </c>
       <c r="D287" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8073,10 +8002,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="288">
@@ -8087,7 +8016,7 @@
         <v>WEB-SEL-287</v>
       </c>
       <c r="C288" t="str">
-        <v>Web Education Hub</v>
+        <v>SMS Notification Preferences Web Subsystem</v>
       </c>
       <c r="D288" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8099,10 +8028,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="289">
@@ -8113,7 +8042,7 @@
         <v>WEB-SEL-288</v>
       </c>
       <c r="C289" t="str">
-        <v>Web Education Hub</v>
+        <v>Push Notification Browser Web Subsystem</v>
       </c>
       <c r="D289" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8125,10 +8054,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="290">
@@ -8139,7 +8068,7 @@
         <v>WEB-SEL-289</v>
       </c>
       <c r="C290" t="str">
-        <v>Web Education Hub</v>
+        <v>Dark Mode Theme Web Subsystem</v>
       </c>
       <c r="D290" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8151,10 +8080,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="291">
@@ -8165,7 +8094,7 @@
         <v>WEB-SEL-290</v>
       </c>
       <c r="C291" t="str">
-        <v>Web Education Hub</v>
+        <v>Light Mode Theme Web Subsystem</v>
       </c>
       <c r="D291" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8177,10 +8106,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="292">
@@ -8191,7 +8120,7 @@
         <v>WEB-SEL-291</v>
       </c>
       <c r="C292" t="str">
-        <v>Web Education Hub</v>
+        <v>System Theme Auto-Detect Web Subsystem</v>
       </c>
       <c r="D292" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8203,10 +8132,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="293">
@@ -8217,7 +8146,7 @@
         <v>WEB-SEL-292</v>
       </c>
       <c r="C293" t="str">
-        <v>Web Education Hub</v>
+        <v>Font Size Scaler Web Subsystem</v>
       </c>
       <c r="D293" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8229,10 +8158,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="294">
@@ -8243,7 +8172,7 @@
         <v>WEB-SEL-293</v>
       </c>
       <c r="C294" t="str">
-        <v>Web Education Hub</v>
+        <v>High Contrast Mode Web Subsystem</v>
       </c>
       <c r="D294" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8255,10 +8184,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="295">
@@ -8269,7 +8198,7 @@
         <v>WEB-SEL-294</v>
       </c>
       <c r="C295" t="str">
-        <v>Web Education Hub</v>
+        <v>Screen Reader ARIA Web Subsystem</v>
       </c>
       <c r="D295" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8281,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="296">
@@ -8295,7 +8224,7 @@
         <v>WEB-SEL-295</v>
       </c>
       <c r="C296" t="str">
-        <v>Web Education Hub</v>
+        <v>Keyboard Tab Focus Web Subsystem</v>
       </c>
       <c r="D296" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8307,10 +8236,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="297">
@@ -8321,7 +8250,7 @@
         <v>WEB-SEL-296</v>
       </c>
       <c r="C297" t="str">
-        <v>Web Education Hub</v>
+        <v>Skip To Main Web Subsystem</v>
       </c>
       <c r="D297" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8333,10 +8262,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="298">
@@ -8347,7 +8276,7 @@
         <v>WEB-SEL-297</v>
       </c>
       <c r="C298" t="str">
-        <v>Web Education Hub</v>
+        <v>Footer Links - Web Subsystem</v>
       </c>
       <c r="D298" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8359,10 +8288,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="299">
@@ -8373,7 +8302,7 @@
         <v>WEB-SEL-298</v>
       </c>
       <c r="C299" t="str">
-        <v>Web Education Hub</v>
+        <v>System Health Status Web Subsystem</v>
       </c>
       <c r="D299" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8385,10 +8314,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="300">
@@ -8399,7 +8328,7 @@
         <v>WEB-SEL-299</v>
       </c>
       <c r="C300" t="str">
-        <v>Web Education Hub</v>
+        <v>Feedback Rating Submission Web Subsystem</v>
       </c>
       <c r="D300" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8411,10 +8340,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
     <row r="301">
@@ -8425,7 +8354,7 @@
         <v>WEB-SEL-300</v>
       </c>
       <c r="C301" t="str">
-        <v>Web Education Hub</v>
+        <v>Version &amp; Release Web Subsystem</v>
       </c>
       <c r="D301" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8437,10 +8366,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T05:04:18.073Z</v>
+        <v>2026-08-06T05:06:53.808Z</v>
       </c>
     </row>
   </sheetData>
